--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43407-2022</t>
+          <t>A 21111-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44834</v>
+        <v>45777</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,19 +845,14 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -887,151 +882,156 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 43407-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Orre</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44895</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 21111-2025</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45777</v>
+        <v>45197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1175,20 +1175,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1199,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1211,39 +1211,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45329</v>
+        <v>44536</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45468</v>
+        <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45593</v>
+        <v>45669</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2171,7 +2166,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45520</v>
+        <v>45396</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2243,8 +2238,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>9.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44938</v>
+        <v>45660</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2316,13 +2316,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2365,7 +2360,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45453</v>
+        <v>45688</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2395,7 +2390,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2438,7 +2433,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44939</v>
+        <v>45799</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2469,11 +2464,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2516,7 +2511,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2530,10 +2525,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44897</v>
+        <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2545,8 +2540,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45545</v>
+        <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2618,8 +2618,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2662,7 +2667,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45232</v>
+        <v>45988</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2691,8 +2696,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2735,7 +2745,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2745,14 +2755,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45588</v>
+        <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2764,8 +2774,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2808,7 +2823,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2822,10 +2837,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45588</v>
+        <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2837,8 +2852,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2881,7 +2901,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,10 +2915,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45680</v>
+        <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2910,8 +2930,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>10.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2971,7 +2996,7 @@
         <v>45890</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3027,7 +3052,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3041,10 +3066,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45468</v>
+        <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3056,13 +3081,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3105,7 +3125,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3119,10 +3139,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45614</v>
+        <v>45818</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3135,7 +3155,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3178,7 +3198,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3192,10 +3212,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45168</v>
+        <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3208,7 +3228,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3251,7 +3271,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3265,10 +3285,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45355</v>
+        <v>45686</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3280,13 +3300,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3344,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3358,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45711</v>
+        <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3359,7 +3374,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>10.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3402,7 +3417,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3416,10 +3431,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45840</v>
+        <v>45232</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3431,13 +3446,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3480,7 +3490,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3494,10 +3504,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45840</v>
+        <v>45468</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3515,7 +3525,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3568,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3582,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45875</v>
+        <v>46057</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3588,7 +3598,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3641,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,10 +3655,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44747</v>
+        <v>46059</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3661,7 +3671,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3704,7 +3714,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46612-2025</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3728,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45926</v>
+        <v>44692</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,13 +3743,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>11.1</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3782,7 +3787,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 46612-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3796,10 +3801,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45058</v>
+        <v>45926</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3817,7 +3822,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>14.9</v>
+        <v>11.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3860,7 +3865,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3874,10 +3879,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45881</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3890,7 +3895,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3938,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3952,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44930</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3963,7 +3968,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4006,7 +4011,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4020,10 +4025,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45204</v>
+        <v>45560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4037,11 +4042,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4084,7 +4089,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4098,10 +4103,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46093</v>
+        <v>45104</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4114,7 +4119,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4157,7 +4162,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4171,10 +4176,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46098</v>
+        <v>45355</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,11 +4193,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4235,7 +4240,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4249,10 +4254,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46100</v>
+        <v>44658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4265,7 +4270,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4308,7 +4313,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4322,10 +4327,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45957</v>
+        <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4337,8 +4342,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4381,7 +4391,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4395,10 +4405,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45957</v>
+        <v>45588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4411,7 +4421,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4454,7 +4464,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4468,10 +4478,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45961</v>
+        <v>45840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4485,11 +4495,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4532,7 +4542,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4546,10 +4556,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46111</v>
+        <v>45875</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4561,13 +4571,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4610,7 +4615,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45968</v>
+        <v>45881</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4639,13 +4644,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45972</v>
+        <v>45680</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45975</v>
+        <v>45700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4792,11 +4792,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45028</v>
+        <v>45153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4868,8 +4868,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4912,7 +4917,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45203</v>
+        <v>45401</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4942,7 +4947,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4985,7 +4990,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4999,10 +5004,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46128</v>
+        <v>46093</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5014,13 +5019,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>14.1</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45995</v>
+        <v>46098</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5092,8 +5092,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45669</v>
+        <v>46100</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46000</v>
+        <v>45957</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5238,13 +5243,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46000</v>
+        <v>45058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5318,11 +5318,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>14.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46013</v>
+        <v>46111</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5396,11 +5396,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46140</v>
+        <v>45961</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5474,11 +5474,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46009</v>
+        <v>45957</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5550,13 +5550,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5599,7 +5594,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5613,10 +5608,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5628,8 +5623,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46009</v>
+        <v>45968</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5703,11 +5703,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45915</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5781,11 +5781,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5828,7 +5828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45988</v>
+        <v>45468</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.9</v>
+        <v>25.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45939</v>
+        <v>45972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5935,13 +5935,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5979,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45226</v>
+        <v>45975</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46140</v>
+        <v>44969</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6097,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6140,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6154,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46140</v>
+        <v>45726</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6169,13 +6164,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6218,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6232,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46139</v>
+        <v>44938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6247,13 +6237,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6296,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6310,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44536</v>
+        <v>45995</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6326,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46048</v>
+        <v>45390</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6456,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46045</v>
+        <v>45226</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6471,8 +6456,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6505,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6519,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46140</v>
+        <v>46000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6546,11 +6536,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6593,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6607,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46140</v>
+        <v>46000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6624,11 +6614,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10.7</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6671,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6685,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45153</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6706,7 +6696,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6749,7 +6739,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6763,10 +6753,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46057</v>
+        <v>45168</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6779,7 +6769,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6822,7 +6812,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6836,10 +6826,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6853,11 +6843,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6900,7 +6890,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6914,10 +6904,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46059</v>
+        <v>45236</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6929,8 +6919,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45386</v>
+        <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7004,11 +6999,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7051,7 +7046,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7065,10 +7060,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7080,8 +7075,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45104</v>
+        <v>46140</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7226,8 +7231,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7270,7 +7280,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7284,10 +7294,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45635</v>
+        <v>46140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7305,7 +7315,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7348,7 +7358,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7362,10 +7372,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44938</v>
+        <v>44900</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7378,7 +7388,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7421,7 +7431,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7435,10 +7445,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45068</v>
+        <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7450,8 +7460,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7494,7 +7509,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7508,10 +7523,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45401</v>
+        <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7523,8 +7538,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7567,7 +7587,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7581,10 +7601,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46141</v>
+        <v>45681</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7596,13 +7616,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7645,7 +7660,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7659,10 +7674,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7674,8 +7689,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7718,7 +7738,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7732,10 +7752,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45700</v>
+        <v>45329</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7747,13 +7767,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7796,7 +7811,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7810,10 +7825,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45681</v>
+        <v>46146</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7826,7 +7841,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7869,7 +7884,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7879,14 +7894,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45072</v>
+        <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7898,8 +7913,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7942,7 +7962,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7956,10 +7976,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45614</v>
+        <v>44938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7972,7 +7992,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8015,7 +8035,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8029,10 +8049,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44938</v>
+        <v>44747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8045,7 +8065,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8105,7 +8125,7 @@
         <v>45985</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8166,7 +8186,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8176,14 +8196,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46002</v>
+        <v>45520</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8195,13 +8215,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8244,7 +8259,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8254,14 +8269,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45203</v>
+        <v>45588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8273,13 +8288,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8322,7 +8332,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8332,14 +8342,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45708</v>
+        <v>46169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8351,8 +8361,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8395,7 +8410,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8409,10 +8424,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45560</v>
+        <v>46170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8424,13 +8439,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8473,7 +8483,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8487,10 +8497,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45686</v>
+        <v>46181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8513,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8546,7 +8556,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8560,10 +8570,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45236</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8575,13 +8585,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8624,7 +8629,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8638,10 +8643,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45174</v>
+        <v>46195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8659,7 +8664,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>23.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8702,7 +8707,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8712,14 +8717,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46169</v>
+        <v>45203</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8737,7 +8742,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8780,7 +8785,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8794,10 +8799,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46170</v>
+        <v>46196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8810,7 +8815,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8853,7 +8858,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8863,14 +8868,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45229</v>
+        <v>46244</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8883,7 +8888,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8926,7 +8931,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8940,10 +8945,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46181</v>
+        <v>46203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8955,8 +8960,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8999,7 +9009,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9013,10 +9023,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46181</v>
+        <v>46203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9028,8 +9038,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9072,7 +9087,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9086,10 +9101,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45468</v>
+        <v>44939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9103,11 +9118,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>25.4</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9150,7 +9165,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9164,10 +9179,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45726</v>
+        <v>45068</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9180,7 +9195,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9223,7 +9238,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9237,10 +9252,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45372</v>
+        <v>44907</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,13 +9267,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9301,7 +9311,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9311,14 +9321,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45037</v>
+        <v>46209</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9330,8 +9340,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9374,7 +9389,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9388,10 +9403,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44747</v>
+        <v>45037</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9404,7 +9419,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9447,7 +9462,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9461,10 +9476,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44969</v>
+        <v>46255</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9482,7 +9497,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.4</v>
+        <v>24.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9525,7 +9540,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9539,10 +9554,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46195</v>
+        <v>45028</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9554,13 +9569,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>23.6</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9603,7 +9613,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9613,14 +9623,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44900</v>
+        <v>46199</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9634,11 +9644,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9681,7 +9691,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9695,10 +9705,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46196</v>
+        <v>46258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9711,7 +9721,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9754,7 +9764,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9768,10 +9778,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9783,8 +9793,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9827,7 +9842,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9841,10 +9856,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44728</v>
+        <v>46220</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9856,8 +9871,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9900,7 +9920,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9914,10 +9934,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,13 +9949,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9978,7 +9993,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9992,10 +10007,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44938</v>
+        <v>46265</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10007,8 +10022,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10051,7 +10071,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10061,14 +10081,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46203</v>
+        <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10080,13 +10100,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10129,7 +10144,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10139,14 +10154,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10164,7 +10179,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10207,7 +10222,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10221,10 +10236,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45007</v>
+        <v>46268</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10242,7 +10257,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10285,7 +10300,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10299,10 +10314,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44692</v>
+        <v>45635</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10314,8 +10329,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10358,7 +10378,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10368,14 +10388,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46199</v>
+        <v>46227</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10389,11 +10409,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10436,7 +10456,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10450,10 +10470,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46258</v>
+        <v>46232</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10466,7 +10486,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10509,7 +10529,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10523,10 +10543,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46255</v>
+        <v>44938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10538,13 +10558,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>24.1</v>
+        <v>1.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10587,7 +10602,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10601,10 +10616,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44900</v>
+        <v>44930</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10617,7 +10632,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10660,7 +10675,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10674,10 +10689,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46261</v>
+        <v>44938</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10691,11 +10706,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10738,7 +10753,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10752,10 +10767,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46205</v>
+        <v>45593</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10768,7 +10783,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10811,7 +10826,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10825,10 +10840,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44907</v>
+        <v>45112</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10841,7 +10856,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10884,7 +10899,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10898,10 +10913,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46220</v>
+        <v>45614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10913,13 +10928,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10962,7 +10972,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10976,10 +10986,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46265</v>
+        <v>45372</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10997,7 +11007,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11040,7 +11050,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11054,10 +11064,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46268</v>
+        <v>44728</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11069,13 +11079,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11118,7 +11123,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11132,10 +11137,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45390</v>
+        <v>45708</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11148,7 +11153,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11191,7 +11196,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11205,10 +11210,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46227</v>
+        <v>45174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11226,7 +11231,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>51.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11283,10 +11288,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46268</v>
+        <v>45468</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11300,11 +11305,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11347,7 +11352,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11361,10 +11366,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44658</v>
+        <v>45711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11377,7 +11382,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11420,7 +11425,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11437,7 +11442,7 @@
         <v>45174</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11455,7 +11460,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>51.6</v>
+        <v>3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11498,7 +11503,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11512,10 +11517,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45163</v>
+        <v>45204</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11529,11 +11534,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11576,7 +11581,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11590,10 +11595,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46232</v>
+        <v>44897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11606,7 +11611,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11649,7 +11654,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11663,10 +11668,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45615</v>
+        <v>45163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11678,8 +11683,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11722,7 +11732,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11736,10 +11746,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45146</v>
+        <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11751,13 +11761,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11800,7 +11805,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11814,10 +11819,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45596</v>
+        <v>45614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11829,13 +11834,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11878,7 +11878,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45396</v>
+        <v>45453</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11907,13 +11907,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>9.6</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11956,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11970,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45660</v>
+        <v>45146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11985,8 +11980,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12029,7 +12029,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12043,10 +12043,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45799</v>
+        <v>45615</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12058,13 +12058,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12107,7 +12102,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12121,10 +12116,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45818</v>
+        <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12136,8 +12131,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12197,7 +12197,7 @@
         <v>45247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45716</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>46182</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE157"/>
+  <dimension ref="A1:AE158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 21111-2025</t>
+          <t>A 43407-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45777</v>
+        <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,14 +845,19 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -882,371 +887,366 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Knölspindel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Korallblylav</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 43407-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 57209-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Knölspindel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45072</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44536</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45203</v>
+        <v>45329</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45669</v>
+        <v>45881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45396</v>
+        <v>45229</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2238,13 +2238,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2287,7 +2282,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45660</v>
+        <v>45468</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2316,8 +2311,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>25.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45688</v>
+        <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45799</v>
+        <v>45468</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46013</v>
+        <v>45372</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2542,11 +2542,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46009</v>
+        <v>45593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2618,13 +2618,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2667,7 +2662,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45988</v>
+        <v>45520</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2696,13 +2691,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2745,7 +2735,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2759,10 +2749,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45939</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2774,13 +2764,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2823,7 +2808,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2837,10 +2822,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46009</v>
+        <v>45680</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2852,13 +2837,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2901,7 +2881,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2915,10 +2895,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45915</v>
+        <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2932,11 +2912,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2976,7 @@
         <v>45890</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3052,7 +3032,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3066,10 +3046,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45545</v>
+        <v>46093</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3082,7 +3062,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3125,7 +3105,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3139,10 +3119,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45818</v>
+        <v>46098</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3154,8 +3134,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3198,7 +3183,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3212,10 +3197,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46045</v>
+        <v>45453</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3228,7 +3213,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3271,7 +3256,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3285,10 +3270,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45686</v>
+        <v>45037</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3301,7 +3286,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3344,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3358,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46048</v>
+        <v>46100</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3374,7 +3359,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3417,7 +3402,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3431,10 +3416,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45232</v>
+        <v>44939</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3446,8 +3431,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3490,7 +3480,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3504,10 +3494,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45468</v>
+        <v>46111</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3525,7 +3515,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3568,7 +3558,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3582,10 +3572,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46057</v>
+        <v>44897</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3598,7 +3588,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3641,7 +3631,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3655,10 +3645,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46059</v>
+        <v>44747</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3671,7 +3661,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3714,7 +3704,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3728,10 +3718,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44692</v>
+        <v>44969</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3743,8 +3733,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
         <v>45926</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3865,7 +3860,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3879,10 +3874,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46059</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3895,7 +3890,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3938,7 +3933,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3952,10 +3947,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>44900</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3967,8 +3962,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45560</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>14.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4089,7 +4089,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4099,14 +4099,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45104</v>
+        <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4162,7 +4162,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45355</v>
+        <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4191,13 +4191,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4240,7 +4235,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4254,10 +4249,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44658</v>
+        <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4270,7 +4265,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4313,7 +4308,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4327,10 +4322,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45840</v>
+        <v>46140</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4348,7 +4343,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4391,7 +4386,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4405,10 +4400,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45588</v>
+        <v>45168</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4421,7 +4416,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4464,7 +4459,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4478,10 +4473,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45840</v>
+        <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4499,7 +4494,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4542,7 +4537,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4556,10 +4551,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45875</v>
+        <v>44728</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4572,7 +4567,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4615,7 +4610,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4629,10 +4624,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45881</v>
+        <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4645,7 +4640,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4688,7 +4683,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4702,10 +4697,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45680</v>
+        <v>46140</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4717,8 +4712,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45700</v>
+        <v>45711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4790,13 +4790,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4839,7 +4834,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45153</v>
+        <v>46140</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4870,11 +4865,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4917,7 +4912,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45401</v>
+        <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4947,7 +4942,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4990,7 +4985,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5004,10 +4999,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46093</v>
+        <v>45961</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5019,8 +5014,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46098</v>
+        <v>46139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5094,11 +5094,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46100</v>
+        <v>45968</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5170,8 +5170,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5214,7 +5219,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45957</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5244,7 +5249,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5287,7 +5292,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45058</v>
+        <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5316,13 +5321,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>14.9</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46111</v>
+        <v>45058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>14.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45961</v>
+        <v>46140</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5474,11 +5474,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>16.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45957</v>
+        <v>46140</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5550,8 +5550,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>10.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5594,7 +5599,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5608,10 +5613,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45007</v>
+        <v>45975</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5625,11 +5630,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5672,7 +5677,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5686,10 +5691,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45968</v>
+        <v>46140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5707,7 +5712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5750,7 +5755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5764,10 +5769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>45386</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5781,11 +5786,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>14.1</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5828,7 +5833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45468</v>
+        <v>44938</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5857,13 +5862,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>25.4</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45972</v>
+        <v>44930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45975</v>
+        <v>45204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44969</v>
+        <v>46141</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45726</v>
+        <v>44938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44938</v>
+        <v>46146</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>9.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>45995</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45390</v>
+        <v>46000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6383,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6432,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45226</v>
+        <v>46000</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,11 +6463,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46000</v>
+        <v>44938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6534,13 +6539,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46000</v>
+        <v>45985</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>14.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6692,11 +6692,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45168</v>
+        <v>46013</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6768,8 +6768,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6812,7 +6817,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6826,10 +6831,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46139</v>
+        <v>46009</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6843,11 +6848,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6890,7 +6895,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6904,10 +6909,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45236</v>
+        <v>46009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44900</v>
+        <v>45915</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6999,11 +7004,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>10.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7046,7 +7051,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46140</v>
+        <v>45988</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7081,7 +7086,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>16.1</v>
+        <v>9.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7124,7 +7129,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7138,10 +7143,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46140</v>
+        <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7159,7 +7164,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7216,10 +7221,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46140</v>
+        <v>45028</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7231,13 +7236,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46140</v>
+        <v>45203</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7309,13 +7309,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7358,7 +7353,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7368,14 +7363,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44900</v>
+        <v>46169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7387,8 +7382,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7460,13 +7460,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>10.7</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7509,7 +7504,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7523,10 +7518,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46141</v>
+        <v>45669</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7538,13 +7533,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7587,7 +7577,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7601,10 +7591,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45681</v>
+        <v>46048</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7617,7 +7607,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>10.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7660,7 +7650,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7674,10 +7664,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46140</v>
+        <v>46045</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7689,13 +7679,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7738,7 +7723,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7752,10 +7737,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45329</v>
+        <v>46181</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7768,7 +7753,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7811,7 +7796,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7825,10 +7810,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46146</v>
+        <v>46057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7841,7 +7826,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.1</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7884,7 +7869,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7894,14 +7879,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46002</v>
+        <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7913,13 +7898,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7962,7 +7942,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7976,10 +7956,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44938</v>
+        <v>45007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7991,8 +7971,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8035,7 +8020,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8049,10 +8034,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44747</v>
+        <v>46059</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8065,7 +8050,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8108,7 +8093,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8122,10 +8107,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45985</v>
+        <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8137,13 +8122,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>14.1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8186,7 +8166,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8200,10 +8180,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45520</v>
+        <v>46181</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8216,7 +8196,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8259,7 +8239,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8269,14 +8249,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45588</v>
+        <v>45112</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8289,7 +8269,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8332,7 +8312,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8342,14 +8322,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46169</v>
+        <v>44536</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8361,13 +8341,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8410,7 +8385,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8424,10 +8399,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46170</v>
+        <v>44692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8440,7 +8415,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8483,7 +8458,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8497,10 +8472,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8512,8 +8487,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>4.4</v>
+        <v>23.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8556,7 +8536,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8570,10 +8550,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>46196</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8586,7 +8566,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8629,7 +8609,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8643,10 +8623,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46195</v>
+        <v>45153</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8660,11 +8640,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>23.6</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8707,7 +8687,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8721,10 +8701,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45203</v>
+        <v>46244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8736,13 +8716,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8785,7 +8760,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8799,10 +8774,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46196</v>
+        <v>44900</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8815,7 +8790,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8858,7 +8833,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8872,10 +8847,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46244</v>
+        <v>45104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8888,7 +8863,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8931,7 +8906,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8945,10 +8920,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46203</v>
+        <v>45635</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8966,7 +8941,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9026,7 +9001,7 @@
         <v>46203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9087,7 +9062,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9101,10 +9076,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44939</v>
+        <v>45068</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9116,13 +9091,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9165,7 +9135,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9179,10 +9149,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45068</v>
+        <v>45401</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9195,7 +9165,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9238,7 +9208,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9252,10 +9222,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44907</v>
+        <v>46203</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9267,8 +9237,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9311,7 +9286,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9321,14 +9296,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46209</v>
+        <v>44907</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9340,13 +9315,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9389,7 +9359,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9403,10 +9373,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45037</v>
+        <v>45700</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9418,8 +9388,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9462,7 +9437,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9476,10 +9451,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46255</v>
+        <v>45681</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9491,13 +9466,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>24.1</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9540,7 +9510,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9554,10 +9524,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45028</v>
+        <v>45072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9570,7 +9540,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9613,7 +9583,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9623,14 +9593,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46199</v>
+        <v>45614</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9642,13 +9612,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9691,7 +9656,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9701,14 +9666,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46258</v>
+        <v>46209</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9720,8 +9685,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9764,7 +9734,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9774,14 +9744,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46261</v>
+        <v>46199</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9795,11 +9765,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9842,7 +9812,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9856,10 +9826,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46220</v>
+        <v>46258</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9871,13 +9841,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9920,7 +9885,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9934,10 +9899,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46205</v>
+        <v>46255</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9949,8 +9914,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>24.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9993,7 +9963,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10007,10 +9977,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46265</v>
+        <v>45203</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10024,11 +9994,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10071,7 +10041,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10081,14 +10051,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45229</v>
+        <v>45708</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10101,7 +10071,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10144,7 +10114,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10158,10 +10128,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46268</v>
+        <v>45560</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10175,11 +10145,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10222,7 +10192,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10236,10 +10206,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46268</v>
+        <v>45686</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10251,13 +10221,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10300,7 +10265,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10314,10 +10279,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45635</v>
+        <v>45236</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10331,11 +10296,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10378,7 +10343,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10392,10 +10357,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46227</v>
+        <v>45174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10413,7 +10378,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10456,7 +10421,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10470,10 +10435,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46232</v>
+        <v>46261</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10485,8 +10450,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10529,7 +10499,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10543,10 +10513,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44938</v>
+        <v>46205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10559,7 +10529,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10602,7 +10572,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10616,10 +10586,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44930</v>
+        <v>45390</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10632,7 +10602,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10675,7 +10645,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10689,10 +10659,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44938</v>
+        <v>46220</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10706,11 +10676,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10753,7 +10723,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10767,10 +10737,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45593</v>
+        <v>46265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10782,8 +10752,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10826,7 +10801,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10840,10 +10815,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45112</v>
+        <v>46268</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10855,8 +10830,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10899,7 +10879,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10913,10 +10893,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45614</v>
+        <v>44658</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10929,7 +10909,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10972,7 +10952,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10986,10 +10966,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45372</v>
+        <v>45174</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11007,7 +10987,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>51.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11050,7 +11030,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11064,10 +11044,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44728</v>
+        <v>45163</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11079,8 +11059,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11123,7 +11108,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11137,10 +11122,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45708</v>
+        <v>46227</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11152,8 +11137,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11196,7 +11186,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11210,10 +11200,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45174</v>
+        <v>46268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11227,11 +11217,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>51.6</v>
+        <v>6.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11274,7 +11264,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11288,10 +11278,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45468</v>
+        <v>46232</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11303,13 +11293,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11352,7 +11337,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11366,10 +11351,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45711</v>
+        <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11382,7 +11367,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11425,7 +11410,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11439,10 +11424,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45174</v>
+        <v>45615</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11454,13 +11439,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11503,7 +11483,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11517,10 +11497,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45204</v>
+        <v>45146</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11534,11 +11514,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11581,7 +11561,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11595,10 +11575,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44897</v>
+        <v>45596</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11610,8 +11590,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11654,7 +11639,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11668,10 +11653,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45163</v>
+        <v>45396</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11685,11 +11670,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>9.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11732,7 +11717,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11746,10 +11731,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44747</v>
+        <v>45660</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11762,7 +11747,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11805,7 +11790,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11819,10 +11804,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45614</v>
+        <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11834,8 +11819,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11878,7 +11868,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11892,10 +11882,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45453</v>
+        <v>45818</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11908,7 +11898,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11951,7 +11941,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +11955,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45146</v>
+        <v>45468</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11982,11 +11972,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12029,7 +12019,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12043,10 +12033,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45615</v>
+        <v>45355</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12058,8 +12048,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12102,7 +12097,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12116,10 +12111,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45596</v>
+        <v>45840</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12137,7 +12132,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12180,24 +12175,24 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45247</v>
+        <v>45840</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12215,7 +12210,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12258,7 +12253,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>S 4139-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12275,7 +12270,7 @@
         <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12289,11 +12284,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12336,7 +12331,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>S 4141-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12350,10 +12345,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45716</v>
+        <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12367,11 +12362,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>33.7</v>
+        <v>20.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12414,153 +12409,231 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
+          <t>S 733-2025</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="E156" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>S 98-2026</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D156" s="1" t="n">
+      <c r="D157" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E156" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
+      <c r="E157" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I156" t="n">
+      <c r="I157" t="n">
         <v>72.5</v>
       </c>
-      <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>S 1683-2026</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D157" s="1" t="n">
+      <c r="D158" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="E157" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I157" t="n">
+      <c r="E158" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
         <v>37.1</v>
       </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" s="2" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE158"/>
+  <dimension ref="A1:AE159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44895</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45197</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45777</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>44536</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45329</v>
+        <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45881</v>
+        <v>45669</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45229</v>
+        <v>45688</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45468</v>
+        <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,13 +2311,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>25.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2360,7 +2355,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45726</v>
+        <v>45799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2389,8 +2384,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45468</v>
+        <v>45686</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2462,13 +2462,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2506,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2525,10 +2520,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45372</v>
+        <v>45890</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2540,13 +2535,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2589,7 +2579,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2603,10 +2593,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45593</v>
+        <v>45818</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2609,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2662,7 +2652,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2676,10 +2666,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45520</v>
+        <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2682,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2735,7 +2725,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2749,10 +2739,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>44692</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2808,7 +2798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2822,10 +2812,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45680</v>
+        <v>45560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2837,8 +2827,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2881,7 +2876,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44938</v>
+        <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2910,13 +2905,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2959,7 +2949,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2973,10 +2963,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45890</v>
+        <v>44658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2989,7 +2979,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3032,7 +3022,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3046,10 +3036,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46093</v>
+        <v>45588</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3062,7 +3052,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3105,7 +3095,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3119,10 +3109,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46098</v>
+        <v>45468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3140,7 +3130,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3183,7 +3173,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 46612-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3197,10 +3187,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45453</v>
+        <v>45926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3212,8 +3202,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>11.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3256,7 +3251,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,10 +3265,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45037</v>
+        <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3285,8 +3280,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>5.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46100</v>
+        <v>45700</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3358,8 +3358,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3402,7 +3407,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44939</v>
+        <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3433,11 +3438,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3480,7 +3485,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3494,10 +3499,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46111</v>
+        <v>45840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3515,7 +3520,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3563,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3577,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44897</v>
+        <v>46045</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3588,7 +3593,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3636,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,10 +3650,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44747</v>
+        <v>45153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3660,8 +3665,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3704,7 +3714,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3728,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44969</v>
+        <v>45875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,13 +3743,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3782,7 +3787,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 46612-2025</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3796,10 +3801,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45926</v>
+        <v>45881</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3811,13 +3816,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>11.1</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44900</v>
+        <v>46048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3962,13 +3962,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4011,7 +4006,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4025,10 +4020,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>45680</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4040,13 +4035,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>14.1</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4089,7 +4079,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4099,14 +4089,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45588</v>
+        <v>45058</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4118,8 +4108,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>14.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4162,7 +4157,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4176,10 +4171,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45588</v>
+        <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4192,7 +4187,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4235,7 +4230,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4249,10 +4244,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45614</v>
+        <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4265,7 +4260,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4308,7 +4303,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4322,10 +4317,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46140</v>
+        <v>46059</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4337,13 +4332,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4386,7 +4376,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4400,10 +4390,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45168</v>
+        <v>45007</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4415,8 +4405,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4459,7 +4454,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4473,10 +4468,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>45961</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,11 +4485,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4537,7 +4532,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44728</v>
+        <v>46059</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4567,7 +4562,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4610,7 +4605,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4624,10 +4619,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>46059</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4640,7 +4635,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4683,7 +4678,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4697,10 +4692,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46140</v>
+        <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4712,13 +4707,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4761,7 +4751,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45711</v>
+        <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4790,8 +4780,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4834,7 +4829,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4848,10 +4843,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46140</v>
+        <v>45468</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4869,7 +4864,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.9</v>
+        <v>25.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4912,7 +4907,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4926,10 +4921,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45957</v>
+        <v>45972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4942,7 +4937,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4985,7 +4980,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4999,10 +4994,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45961</v>
+        <v>44969</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5016,11 +5011,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5063,7 +5058,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5077,10 +5072,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46139</v>
+        <v>45975</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5094,11 +5089,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45968</v>
+        <v>45726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5170,13 +5165,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5219,7 +5209,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5233,10 +5223,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>45390</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5249,7 +5239,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5292,7 +5282,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5306,10 +5296,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44747</v>
+        <v>45168</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5322,7 +5312,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5365,7 +5355,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5379,10 +5369,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45058</v>
+        <v>45995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5394,13 +5384,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>14.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5443,7 +5428,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5457,10 +5442,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46140</v>
+        <v>45236</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5474,11 +5459,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>16.1</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5521,7 +5506,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5535,10 +5520,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46140</v>
+        <v>46000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5552,11 +5537,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5599,7 +5584,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5613,10 +5598,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,11 +5615,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5677,7 +5662,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5691,10 +5676,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46140</v>
+        <v>44900</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5708,11 +5693,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5755,7 +5740,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5769,10 +5754,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45386</v>
+        <v>44900</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5784,13 +5769,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5833,7 +5813,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5847,10 +5827,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44938</v>
+        <v>45681</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5863,7 +5843,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5906,7 +5886,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5920,10 +5900,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44930</v>
+        <v>46013</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5935,8 +5915,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5979,7 +5964,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5993,10 +5978,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45204</v>
+        <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6008,13 +5993,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6037,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6051,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46141</v>
+        <v>46009</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6088,11 +6068,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6115,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6129,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44938</v>
+        <v>45988</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6164,8 +6144,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>9.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6193,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6207,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46146</v>
+        <v>45939</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6237,8 +6222,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>9.1</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6271,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6285,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45995</v>
+        <v>46009</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6310,8 +6300,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46000</v>
+        <v>45915</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6385,11 +6380,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6432,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46000</v>
+        <v>46098</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6463,11 +6458,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6505,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6519,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44938</v>
+        <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6535,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6578,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6592,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45985</v>
+        <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6612,13 +6607,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6651,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6671,14 +6661,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>46111</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6696,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6739,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6753,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46013</v>
+        <v>44747</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6768,13 +6758,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6817,7 +6802,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6831,10 +6816,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46009</v>
+        <v>45520</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6846,13 +6831,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6895,7 +6875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6905,14 +6885,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46009</v>
+        <v>45588</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6924,13 +6904,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6973,7 +6948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6987,10 +6962,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45915</v>
+        <v>46128</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7004,11 +6979,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7051,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7065,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45988</v>
+        <v>45203</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7082,11 +7057,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.9</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7129,7 +7104,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7143,10 +7118,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45939</v>
+        <v>44939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7160,11 +7135,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7207,7 +7182,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7221,10 +7196,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45028</v>
+        <v>45068</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7237,7 +7212,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7280,7 +7255,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7294,10 +7269,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45203</v>
+        <v>44907</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7310,7 +7285,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7353,7 +7328,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7363,14 +7338,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46169</v>
+        <v>45037</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7382,13 +7357,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7431,7 +7401,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7445,10 +7415,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46170</v>
+        <v>45028</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7461,7 +7431,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7504,7 +7474,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7518,10 +7488,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45669</v>
+        <v>44938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7534,7 +7504,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7577,7 +7547,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7591,10 +7561,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46048</v>
+        <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7606,8 +7576,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>10.8</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7650,7 +7625,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7660,14 +7635,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46045</v>
+        <v>45229</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7680,7 +7655,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7723,7 +7698,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7737,10 +7712,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46181</v>
+        <v>45386</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7752,8 +7727,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7796,7 +7776,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7810,10 +7790,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46057</v>
+        <v>46139</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7825,8 +7805,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7869,7 +7854,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7883,10 +7868,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46059</v>
+        <v>45635</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7898,8 +7883,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7942,7 +7932,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7956,10 +7946,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45007</v>
+        <v>46140</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7973,11 +7963,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>16.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8020,7 +8010,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8034,10 +8024,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8049,8 +8039,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8093,7 +8088,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8107,10 +8102,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8122,8 +8117,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46181</v>
+        <v>46140</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8195,8 +8195,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8239,7 +8244,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8253,10 +8258,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45112</v>
+        <v>46140</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8268,8 +8273,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8312,7 +8322,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8326,10 +8336,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44536</v>
+        <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8341,8 +8351,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8385,7 +8400,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8399,10 +8414,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44692</v>
+        <v>46140</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8414,8 +8429,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8458,7 +8478,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8472,10 +8492,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46195</v>
+        <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8487,13 +8507,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>23.6</v>
+        <v>9.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8536,7 +8551,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8550,10 +8565,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46196</v>
+        <v>44938</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8566,7 +8581,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8609,7 +8624,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8623,10 +8638,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45153</v>
+        <v>44930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8638,13 +8653,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8687,7 +8697,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8697,14 +8707,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46244</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8716,8 +8726,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8760,7 +8775,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8774,10 +8789,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44900</v>
+        <v>44938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8790,7 +8805,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8833,7 +8848,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8847,10 +8862,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45104</v>
+        <v>45985</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8862,8 +8877,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8906,7 +8926,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8916,14 +8936,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45635</v>
+        <v>46169</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8937,11 +8957,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8984,7 +9004,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8998,10 +9018,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46203</v>
+        <v>46170</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9013,13 +9033,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9062,7 +9077,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9076,10 +9091,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45068</v>
+        <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9091,8 +9106,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9135,7 +9155,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9149,10 +9169,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45401</v>
+        <v>45593</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9165,7 +9185,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9208,7 +9228,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9222,10 +9242,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46203</v>
+        <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9237,13 +9257,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9286,7 +9301,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9300,10 +9315,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44907</v>
+        <v>46181</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9316,7 +9331,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9359,7 +9374,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9373,10 +9388,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45700</v>
+        <v>45112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9388,13 +9403,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9437,7 +9447,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9451,10 +9461,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45681</v>
+        <v>45614</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9467,7 +9477,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9510,7 +9520,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9524,10 +9534,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45072</v>
+        <v>46195</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9539,8 +9549,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>23.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9583,7 +9598,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9597,10 +9612,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45614</v>
+        <v>45372</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9612,8 +9627,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9656,7 +9676,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9666,14 +9686,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46209</v>
+        <v>46196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9685,13 +9705,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9734,7 +9749,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9744,14 +9759,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46199</v>
+        <v>44728</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9763,13 +9778,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9812,7 +9822,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9826,10 +9836,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46258</v>
+        <v>45708</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9842,7 +9852,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9885,7 +9895,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9899,10 +9909,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9914,13 +9924,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>24.1</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9963,7 +9968,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9977,10 +9982,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45203</v>
+        <v>46203</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9994,11 +9999,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10041,7 +10046,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10055,10 +10060,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45708</v>
+        <v>46203</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10070,8 +10075,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10114,7 +10124,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10124,14 +10134,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45560</v>
+        <v>46209</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10145,11 +10155,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10192,7 +10202,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10206,10 +10216,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45686</v>
+        <v>46255</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10221,8 +10231,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>24.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10265,7 +10280,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10275,14 +10290,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45236</v>
+        <v>46199</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10296,11 +10311,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10343,7 +10358,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10360,7 +10375,7 @@
         <v>45174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10378,7 +10393,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>51.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10421,7 +10436,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10435,10 +10450,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46261</v>
+        <v>45468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10456,7 +10471,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10499,7 +10514,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10513,10 +10528,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46205</v>
+        <v>46258</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10529,7 +10544,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10572,7 +10587,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10586,10 +10601,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45390</v>
+        <v>45711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10602,7 +10617,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10645,7 +10660,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10659,10 +10674,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46220</v>
+        <v>46261</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10680,7 +10695,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10723,7 +10738,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10737,10 +10752,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46265</v>
+        <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10758,7 +10773,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10801,7 +10816,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10815,10 +10830,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46268</v>
+        <v>46220</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10832,11 +10847,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10879,7 +10894,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10893,10 +10908,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44658</v>
+        <v>46205</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10909,7 +10924,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10952,7 +10967,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10966,10 +10981,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45174</v>
+        <v>46265</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10987,7 +11002,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>51.6</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11030,7 +11045,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11044,10 +11059,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45163</v>
+        <v>45204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11061,11 +11076,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11108,7 +11123,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11122,10 +11137,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46227</v>
+        <v>44897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11137,13 +11152,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11186,7 +11196,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11200,10 +11210,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46268</v>
+        <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11221,7 +11231,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11264,7 +11274,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11278,10 +11288,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46232</v>
+        <v>46268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11293,8 +11303,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11337,7 +11352,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11351,10 +11366,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11366,8 +11381,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11410,7 +11430,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11424,10 +11444,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45615</v>
+        <v>44747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11440,7 +11460,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11483,7 +11503,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11497,10 +11517,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45146</v>
+        <v>46227</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11514,11 +11534,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11561,7 +11581,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11575,10 +11595,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45596</v>
+        <v>46232</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11590,13 +11610,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11639,7 +11654,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11653,10 +11668,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45396</v>
+        <v>45614</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11668,13 +11683,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>9.6</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11717,7 +11727,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11731,10 +11741,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45660</v>
+        <v>45453</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11747,7 +11757,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11790,7 +11800,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11804,10 +11814,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45799</v>
+        <v>46280</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11819,13 +11829,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11868,7 +11873,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11882,10 +11887,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45818</v>
+        <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11897,8 +11902,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11941,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11955,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45468</v>
+        <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11970,13 +11980,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12019,7 +12024,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12033,10 +12038,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45355</v>
+        <v>46281</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12050,11 +12055,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.5</v>
+        <v>35.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12097,7 +12102,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12111,10 +12116,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45840</v>
+        <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12132,7 +12137,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12175,7 +12180,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12189,10 +12194,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45840</v>
+        <v>45396</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12210,7 +12215,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>9.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12253,24 +12258,24 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45247</v>
+        <v>45660</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12282,13 +12287,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>S 4139-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12409,7 +12409,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>S 4141-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12423,10 +12423,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45716</v>
+        <v>45247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12440,11 +12440,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>33.7</v>
+        <v>20.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12487,153 +12487,231 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
+          <t>S 733-2025</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>S 98-2026</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D157" s="1" t="n">
+      <c r="D158" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E157" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
+      <c r="E158" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I157" t="n">
+      <c r="I158" t="n">
         <v>72.5</v>
       </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>S 1683-2026</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D158" s="1" t="n">
+      <c r="D159" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="E158" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I158" t="n">
+      <c r="E159" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
         <v>37.1</v>
       </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="2" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 57209-2022</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44895</v>
+        <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -959,13 +959,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -974,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1001,147 +996,152 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45777</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44536</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45203</v>
+        <v>45329</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45072</v>
+        <v>45468</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45669</v>
+        <v>45593</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2166,7 +2171,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2209,7 +2214,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45688</v>
+        <v>45520</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2239,7 +2244,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2282,7 +2287,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45545</v>
+        <v>44938</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,8 +2316,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2355,7 +2365,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2369,10 +2379,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45799</v>
+        <v>45453</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2384,13 +2394,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2433,7 +2438,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45686</v>
+        <v>45545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2463,7 +2468,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2506,7 +2511,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2520,10 +2525,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45890</v>
+        <v>44939</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2535,8 +2540,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2579,7 +2589,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2593,10 +2603,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45818</v>
+        <v>44897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2609,7 +2619,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2669,7 +2679,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2725,7 +2735,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2735,14 +2745,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44692</v>
+        <v>45588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45560</v>
+        <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2827,13 +2837,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2876,7 +2881,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45104</v>
+        <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2906,7 +2911,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2949,7 +2954,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2963,10 +2968,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44658</v>
+        <v>45168</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2979,7 +2984,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3022,7 +3027,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3036,10 +3041,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45588</v>
+        <v>46093</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3052,7 +3057,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3095,7 +3100,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3109,10 +3114,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45468</v>
+        <v>45680</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3124,13 +3129,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46612-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45926</v>
+        <v>45468</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45355</v>
+        <v>45711</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3280,13 +3280,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3324,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45700</v>
+        <v>46098</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3360,11 +3355,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3407,7 +3402,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45840</v>
+        <v>46100</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3436,13 +3431,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3485,7 +3475,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3499,10 +3489,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45840</v>
+        <v>45355</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3516,11 +3506,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3563,7 +3553,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3577,10 +3567,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46045</v>
+        <v>46111</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3592,8 +3582,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3636,7 +3631,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45153</v>
+        <v>44747</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3665,13 +3660,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3714,7 +3704,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3728,10 +3718,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>45890</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3787,7 +3777,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3801,10 +3791,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45881</v>
+        <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3816,8 +3806,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3860,7 +3855,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3874,10 +3869,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45401</v>
+        <v>45058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3889,8 +3884,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>14.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46048</v>
+        <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3962,8 +3962,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4006,7 +4011,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4020,10 +4025,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45680</v>
+        <v>45875</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4036,7 +4041,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4079,7 +4084,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4093,10 +4098,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45058</v>
+        <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4108,13 +4113,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>14.9</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45957</v>
+        <v>45204</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4186,8 +4186,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4230,7 +4235,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4244,10 +4249,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46057</v>
+        <v>45881</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4260,7 +4265,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4303,7 +4308,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4317,10 +4322,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46059</v>
+        <v>46128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4332,8 +4337,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4376,7 +4386,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4390,10 +4400,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45007</v>
+        <v>46140</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,11 +4417,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4454,7 +4464,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4468,10 +4478,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45961</v>
+        <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4485,11 +4495,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4532,7 +4542,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4546,10 +4556,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4561,8 +4571,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4605,7 +4620,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4619,10 +4634,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46059</v>
+        <v>46140</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4634,8 +4649,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4678,7 +4698,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4692,10 +4712,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45957</v>
+        <v>46139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4707,8 +4727,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4751,7 +4776,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 46612-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4765,10 +4790,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45968</v>
+        <v>45926</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4786,7 +4811,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>11.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4829,7 +4854,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4843,10 +4868,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45468</v>
+        <v>46140</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4864,7 +4889,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>25.4</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4907,7 +4932,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4921,10 +4946,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45972</v>
+        <v>46140</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4936,8 +4961,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4980,7 +5010,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4994,10 +5024,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44969</v>
+        <v>46140</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5015,7 +5045,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5058,7 +5088,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5072,10 +5102,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45975</v>
+        <v>45386</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5089,11 +5119,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5136,7 +5166,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5150,10 +5180,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45726</v>
+        <v>44938</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5166,7 +5196,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5209,7 +5239,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5223,10 +5253,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45390</v>
+        <v>45028</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5239,7 +5269,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5282,7 +5312,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5296,10 +5326,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45168</v>
+        <v>45203</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5312,7 +5342,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5355,7 +5385,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5369,10 +5399,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45995</v>
+        <v>46141</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5384,8 +5414,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5428,7 +5463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5442,10 +5477,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45236</v>
+        <v>45669</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5457,13 +5492,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5506,7 +5536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5520,10 +5550,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46000</v>
+        <v>46146</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5535,13 +5565,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>9.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5584,7 +5609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5598,10 +5623,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46000</v>
+        <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5613,13 +5638,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5662,7 +5682,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5676,10 +5696,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44900</v>
+        <v>44938</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5691,13 +5711,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5740,7 +5755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5754,10 +5769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44900</v>
+        <v>45985</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5769,8 +5784,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>14.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5813,7 +5833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5823,14 +5843,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45681</v>
+        <v>46002</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5842,8 +5862,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5886,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5900,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46013</v>
+        <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5913,11 +5938,6 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5964,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5974,14 +5994,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46093</v>
+        <v>46169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5993,8 +6013,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6037,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6051,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46009</v>
+        <v>45153</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6068,11 +6093,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6115,7 +6140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6129,10 +6154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45988</v>
+        <v>46170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6144,13 +6169,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6193,7 +6213,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6207,10 +6227,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45939</v>
+        <v>45104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6222,13 +6242,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6271,7 +6286,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6285,10 +6300,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46009</v>
+        <v>45635</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6302,11 +6317,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6349,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6363,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45915</v>
+        <v>45068</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6378,13 +6393,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46098</v>
+        <v>45401</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6456,13 +6466,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46100</v>
+        <v>46181</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45329</v>
+        <v>46181</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6608,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6651,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6665,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46111</v>
+        <v>45957</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6680,13 +6685,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44747</v>
+        <v>45700</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6758,8 +6758,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6802,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6816,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45520</v>
+        <v>45681</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6832,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6875,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6885,14 +6890,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45588</v>
+        <v>45072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6905,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6948,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6962,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46128</v>
+        <v>45614</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6977,13 +6982,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>14.1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45203</v>
+        <v>45957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7055,13 +7055,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7104,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7118,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44939</v>
+        <v>45961</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7135,11 +7130,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7182,7 +7177,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7196,10 +7191,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45068</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7211,8 +7206,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>23.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44907</v>
+        <v>46196</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45037</v>
+        <v>45968</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7357,8 +7357,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7401,7 +7406,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7415,10 +7420,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45028</v>
+        <v>46244</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7431,7 +7436,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7474,7 +7479,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7488,10 +7493,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44938</v>
+        <v>45972</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7504,7 +7509,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7547,7 +7552,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7561,10 +7566,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45226</v>
+        <v>45975</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7582,7 +7587,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7625,7 +7630,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7635,14 +7640,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45229</v>
+        <v>46203</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7654,8 +7659,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7698,7 +7708,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7712,10 +7722,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45386</v>
+        <v>45203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7733,7 +7743,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7776,7 +7786,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7790,10 +7800,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46139</v>
+        <v>45708</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7805,13 +7815,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7854,7 +7859,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7868,10 +7873,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45635</v>
+        <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7885,11 +7890,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7932,7 +7937,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7946,10 +7951,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46140</v>
+        <v>46203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7967,7 +7972,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>16.1</v>
+        <v>7.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8010,7 +8015,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8024,10 +8029,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46140</v>
+        <v>45686</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8039,13 +8044,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8102,10 +8102,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46140</v>
+        <v>45236</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8119,11 +8119,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46140</v>
+        <v>45174</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8254,14 +8254,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46140</v>
+        <v>46209</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8275,11 +8275,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.7</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8332,14 +8332,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46141</v>
+        <v>46199</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8353,11 +8353,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8410,14 +8410,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46140</v>
+        <v>45229</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8429,13 +8429,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8478,7 +8473,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8492,10 +8487,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46146</v>
+        <v>46258</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8508,7 +8503,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8551,7 +8546,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8565,10 +8560,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44938</v>
+        <v>46255</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8580,8 +8575,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>24.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8624,7 +8624,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44930</v>
+        <v>45468</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8653,8 +8653,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>7.3</v>
+        <v>25.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8697,7 +8702,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8707,14 +8712,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>45726</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8726,13 +8731,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44938</v>
+        <v>45995</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45985</v>
+        <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8879,11 +8879,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>14.1</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8926,7 +8926,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8936,14 +8936,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46169</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8957,11 +8957,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46170</v>
+        <v>46261</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,8 +9033,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9077,7 +9082,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9091,10 +9096,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44938</v>
+        <v>46205</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9104,11 +9109,6 @@
       <c r="G112" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -9155,7 +9155,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9169,10 +9169,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45593</v>
+        <v>45372</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9184,8 +9184,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9228,7 +9233,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9242,10 +9247,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46181</v>
+        <v>46220</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9257,8 +9262,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9301,7 +9311,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9315,10 +9325,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46181</v>
+        <v>46265</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9330,8 +9340,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9374,7 +9389,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9388,10 +9403,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45112</v>
+        <v>46268</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9403,8 +9418,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9447,7 +9467,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9461,10 +9481,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45614</v>
+        <v>46227</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9476,8 +9496,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9520,7 +9545,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9534,10 +9559,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46195</v>
+        <v>45037</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9549,13 +9574,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>23.6</v>
+        <v>8.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9598,7 +9618,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9612,10 +9632,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45372</v>
+        <v>46268</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9629,11 +9649,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9676,7 +9696,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9690,10 +9710,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46196</v>
+        <v>44747</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9706,7 +9726,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9749,7 +9769,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9763,10 +9783,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44728</v>
+        <v>44969</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9778,8 +9798,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9847,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9836,10 +9861,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45708</v>
+        <v>46013</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9851,8 +9876,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9895,7 +9925,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9909,10 +9939,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46244</v>
+        <v>44900</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9924,8 +9954,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9968,7 +10003,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9982,10 +10017,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46203</v>
+        <v>46009</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9999,11 +10034,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10046,7 +10081,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10060,10 +10095,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46203</v>
+        <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10081,7 +10116,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10124,7 +10159,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10134,14 +10169,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46209</v>
+        <v>45915</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10155,11 +10190,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>10.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10202,7 +10237,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10216,10 +10251,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46255</v>
+        <v>45988</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10237,7 +10272,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>24.1</v>
+        <v>9.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10280,7 +10315,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10290,14 +10325,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46199</v>
+        <v>45939</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10311,11 +10346,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10358,7 +10393,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10372,10 +10407,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45174</v>
+        <v>46232</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10387,13 +10422,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>51.6</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10436,7 +10466,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10450,10 +10480,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45468</v>
+        <v>44728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10465,13 +10495,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10514,7 +10539,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10528,10 +10553,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10544,7 +10569,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10587,7 +10612,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10601,10 +10626,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45711</v>
+        <v>44938</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10617,7 +10642,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10660,7 +10685,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10674,10 +10699,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10695,7 +10720,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.800000000000001</v>
+        <v>35.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10738,7 +10763,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10752,10 +10777,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45174</v>
+        <v>46048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10767,13 +10792,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>10.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10816,7 +10836,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10830,10 +10850,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46220</v>
+        <v>45007</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10847,11 +10867,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10894,7 +10914,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10908,10 +10928,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46205</v>
+        <v>46045</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10924,7 +10944,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10967,7 +10987,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10981,10 +11001,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46265</v>
+        <v>44692</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10996,13 +11016,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11045,7 +11060,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11059,10 +11074,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45204</v>
+        <v>46057</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11074,13 +11089,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11123,7 +11133,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11137,10 +11147,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44897</v>
+        <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11153,7 +11163,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11196,7 +11206,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45163</v>
+        <v>46059</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11225,13 +11235,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11274,7 +11279,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11288,10 +11293,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46268</v>
+        <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11303,13 +11308,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11352,7 +11352,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11366,10 +11366,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46268</v>
+        <v>44900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11381,13 +11381,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11430,7 +11425,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11444,10 +11439,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44747</v>
+        <v>44907</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11460,7 +11455,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11503,7 +11498,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11517,10 +11512,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46227</v>
+        <v>45390</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11532,13 +11527,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11581,7 +11571,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11595,10 +11585,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46232</v>
+        <v>44658</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11654,7 +11644,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11668,10 +11658,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45614</v>
+        <v>45174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11683,8 +11673,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>51.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11727,7 +11722,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11741,10 +11736,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45453</v>
+        <v>45163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11756,8 +11751,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11800,7 +11800,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46280</v>
+        <v>45615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11890,7 +11890,7 @@
         <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45615</v>
+        <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11980,8 +11980,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12024,7 +12029,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12038,10 +12043,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46281</v>
+        <v>45396</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12059,7 +12064,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>35.1</v>
+        <v>9.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12102,7 +12107,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12116,10 +12121,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45596</v>
+        <v>45660</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12131,13 +12136,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12180,7 +12180,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45396</v>
+        <v>45799</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12258,7 +12258,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12272,10 +12272,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45660</v>
+        <v>45818</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45716</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>46182</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 46376-2023</t>
+          <t>A 57209-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45197</v>
+        <v>44895</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -959,8 +959,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -969,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -987,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -996,152 +1001,147 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Knölspindel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 57209-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Knölspindel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45777</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45329</v>
+        <v>44536</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45468</v>
+        <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45593</v>
+        <v>45669</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2171,7 +2166,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45520</v>
+        <v>45688</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2244,7 +2239,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2287,7 +2282,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44938</v>
+        <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2316,13 +2311,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2365,7 +2355,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2379,10 +2369,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45453</v>
+        <v>45686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2395,7 +2385,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2438,7 +2428,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45545</v>
+        <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2468,7 +2458,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2501,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2525,10 +2515,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44939</v>
+        <v>45560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2542,11 +2532,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2589,7 +2579,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2603,10 +2593,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44897</v>
+        <v>44692</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2619,7 +2609,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2662,7 +2652,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2676,10 +2666,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45232</v>
+        <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2682,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2735,7 +2725,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2745,14 +2735,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45588</v>
+        <v>44658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2825,7 +2815,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2881,7 +2871,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,10 +2885,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45614</v>
+        <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2910,8 +2900,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2954,7 +2949,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2968,10 +2963,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45168</v>
+        <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2983,8 +2978,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46093</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45680</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3129,8 +3129,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>14.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3173,7 +3178,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45468</v>
+        <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3204,11 +3209,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3251,7 +3256,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3265,10 +3270,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45711</v>
+        <v>45680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3281,7 +3286,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3324,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46098</v>
+        <v>45468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3359,7 +3364,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.7</v>
+        <v>25.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3402,7 +3407,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46100</v>
+        <v>44969</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3431,8 +3436,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3475,7 +3485,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3489,10 +3499,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45355</v>
+        <v>44938</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3504,13 +3514,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3553,7 +3558,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3567,10 +3572,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46111</v>
+        <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3582,13 +3587,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44747</v>
+        <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45890</v>
+        <v>45390</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3777,7 +3777,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45840</v>
+        <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3855,7 +3855,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45058</v>
+        <v>45168</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3884,13 +3884,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>14.9</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3928,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3942,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45840</v>
+        <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3964,11 +3959,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4011,7 +4006,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4025,10 +4020,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45875</v>
+        <v>45386</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4040,8 +4035,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44930</v>
+        <v>44900</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4113,8 +4113,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4157,7 +4162,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4171,10 +4176,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45204</v>
+        <v>46139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,11 +4193,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4235,7 +4240,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4249,10 +4254,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45881</v>
+        <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4264,8 +4269,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>16.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4308,7 +4318,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4322,10 +4332,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46128</v>
+        <v>44900</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4337,13 +4347,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>14.1</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4386,7 +4391,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4403,7 +4408,7 @@
         <v>46140</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4421,7 +4426,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4464,7 +4469,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4478,10 +4483,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>46140</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4499,7 +4504,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4542,7 +4547,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4559,7 +4564,7 @@
         <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4577,7 +4582,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4620,7 +4625,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4637,7 +4642,7 @@
         <v>46140</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.9</v>
+        <v>10.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4729,11 +4734,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4776,7 +4781,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46612-2025</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4790,10 +4795,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45926</v>
+        <v>46140</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>11.1</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4854,7 +4859,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46140</v>
+        <v>45681</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4883,13 +4888,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46140</v>
+        <v>45329</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4961,13 +4961,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>10.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5010,7 +5005,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 46612-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46140</v>
+        <v>45926</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5045,7 +5040,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5088,7 +5083,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5102,10 +5097,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>46146</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5117,13 +5112,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5166,7 +5156,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5180,10 +5170,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44938</v>
+        <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5196,7 +5186,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5239,7 +5229,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5253,10 +5243,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45028</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5312,7 +5302,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5322,14 +5312,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45203</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5342,7 +5332,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5385,7 +5375,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5399,10 +5389,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46141</v>
+        <v>45203</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5416,11 +5406,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5463,7 +5453,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5477,10 +5467,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45669</v>
+        <v>45957</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5493,7 +5483,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5536,7 +5526,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5550,10 +5540,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46146</v>
+        <v>44939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5565,8 +5555,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>9.1</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5609,7 +5604,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5623,10 +5618,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>45068</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5639,7 +5634,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5682,7 +5677,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5696,10 +5691,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44938</v>
+        <v>45961</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5711,8 +5706,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5755,7 +5755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45985</v>
+        <v>44907</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5784,13 +5784,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>14.1</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5833,7 +5828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5843,14 +5838,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46002</v>
+        <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5862,13 +5857,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5915,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44536</v>
+        <v>45037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5931,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5998,10 +5988,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46169</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6015,11 +6005,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6052,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6066,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45153</v>
+        <v>44938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6091,13 +6081,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6140,7 +6125,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6154,10 +6139,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46170</v>
+        <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6169,8 +6154,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45104</v>
+        <v>45028</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6286,7 +6276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6300,10 +6290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45635</v>
+        <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>14.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45068</v>
+        <v>45972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45401</v>
+        <v>45975</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6466,8 +6456,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6505,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6520,14 +6515,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46181</v>
+        <v>45229</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6535,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6578,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6592,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46181</v>
+        <v>45635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6612,8 +6607,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45957</v>
+        <v>45995</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45700</v>
+        <v>46000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6760,11 +6760,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45681</v>
+        <v>46000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6836,8 +6836,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6885,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6899,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45072</v>
+        <v>46013</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6909,8 +6914,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6963,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6977,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45614</v>
+        <v>44938</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6993,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7036,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7050,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45957</v>
+        <v>44930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7066,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7109,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7109,14 +7119,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45961</v>
+        <v>46169</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7130,11 +7140,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7177,7 +7187,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7208,11 +7218,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>23.6</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7255,7 +7265,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7269,10 +7279,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46196</v>
+        <v>45988</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7284,8 +7294,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>9.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7328,7 +7343,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7342,10 +7357,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45968</v>
+        <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7363,7 +7378,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7406,7 +7421,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7420,10 +7435,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46244</v>
+        <v>46009</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7435,8 +7450,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7479,7 +7499,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7493,10 +7513,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45972</v>
+        <v>45915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7508,8 +7528,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>10.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7552,7 +7577,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7566,10 +7591,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45975</v>
+        <v>46170</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7581,13 +7606,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7630,7 +7650,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7644,10 +7664,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46203</v>
+        <v>46045</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7659,13 +7679,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7708,7 +7723,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7722,10 +7737,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45203</v>
+        <v>46048</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7737,13 +7752,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7786,7 +7796,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7800,10 +7810,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45708</v>
+        <v>46057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7816,7 +7826,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7859,7 +7869,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7873,10 +7883,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45560</v>
+        <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7890,11 +7900,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7937,7 +7947,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7951,10 +7961,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46203</v>
+        <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7966,13 +7976,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8015,7 +8020,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8029,10 +8034,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45686</v>
+        <v>46059</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8045,7 +8050,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8088,7 +8093,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8102,10 +8107,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45236</v>
+        <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8117,13 +8122,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45174</v>
+        <v>46181</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8195,13 +8195,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8244,7 +8239,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8254,14 +8249,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46209</v>
+        <v>46181</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8273,13 +8268,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8322,7 +8312,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8332,14 +8322,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46199</v>
+        <v>45593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8351,13 +8341,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8400,7 +8385,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8410,14 +8395,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45229</v>
+        <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8430,7 +8415,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8473,7 +8458,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8487,10 +8472,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46258</v>
+        <v>46093</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8488,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8546,7 +8531,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8560,10 +8545,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46255</v>
+        <v>46098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8581,7 +8566,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>24.1</v>
+        <v>7.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8624,7 +8609,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8638,10 +8623,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45468</v>
+        <v>45614</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8653,13 +8638,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>25.4</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8702,7 +8682,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8716,10 +8696,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45726</v>
+        <v>46100</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8732,7 +8712,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8775,7 +8755,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8789,10 +8769,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45995</v>
+        <v>46195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8804,8 +8784,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>23.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8848,7 +8833,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8862,10 +8847,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46000</v>
+        <v>46196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8877,13 +8862,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8926,7 +8906,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8940,10 +8920,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>45372</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8957,11 +8937,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9004,7 +8984,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9018,10 +8998,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46261</v>
+        <v>44728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9033,13 +9013,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9082,7 +9057,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9096,10 +9071,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46205</v>
+        <v>45708</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9112,7 +9087,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9155,7 +9130,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9169,10 +9144,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45372</v>
+        <v>46111</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9190,7 +9165,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9233,7 +9208,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9247,10 +9222,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46220</v>
+        <v>46244</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9262,13 +9237,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9311,7 +9281,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9325,10 +9295,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46265</v>
+        <v>46128</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9342,11 +9312,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9389,7 +9359,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9403,10 +9373,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46268</v>
+        <v>46203</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9420,11 +9390,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9467,7 +9437,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9481,10 +9451,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46227</v>
+        <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9502,7 +9472,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.8</v>
+        <v>51.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9545,7 +9515,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9559,10 +9529,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45037</v>
+        <v>45468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9574,8 +9544,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9618,7 +9593,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9632,10 +9607,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46268</v>
+        <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9649,11 +9624,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9696,7 +9671,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9710,10 +9685,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44747</v>
+        <v>45711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9726,7 +9701,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9769,7 +9744,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9783,10 +9758,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44969</v>
+        <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9804,7 +9779,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9847,7 +9822,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9857,14 +9832,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46013</v>
+        <v>46209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9882,7 +9857,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9925,7 +9900,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9939,10 +9914,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44900</v>
+        <v>45204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9956,11 +9931,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10003,7 +9978,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10017,10 +9992,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46009</v>
+        <v>46255</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10034,11 +10009,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>24.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10081,7 +10056,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10091,14 +10066,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46009</v>
+        <v>46199</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10112,11 +10087,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10159,7 +10134,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10173,10 +10148,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45915</v>
+        <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10188,13 +10163,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>10.6</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10237,7 +10207,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10251,10 +10221,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45988</v>
+        <v>45163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10268,11 +10238,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>9.9</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10315,7 +10285,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10329,10 +10299,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45939</v>
+        <v>46258</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10344,13 +10314,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10393,7 +10358,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10407,10 +10372,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46232</v>
+        <v>46261</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10422,8 +10387,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10466,7 +10436,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10480,10 +10450,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44728</v>
+        <v>44747</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10496,7 +10466,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10539,7 +10509,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10553,10 +10523,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46280</v>
+        <v>46220</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10568,8 +10538,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10612,7 +10587,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10626,10 +10601,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44938</v>
+        <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10642,7 +10617,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10685,7 +10660,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10699,10 +10674,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10720,7 +10695,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>35.1</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10763,7 +10738,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10777,10 +10752,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46048</v>
+        <v>45614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10793,7 +10768,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10836,7 +10811,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10850,10 +10825,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45007</v>
+        <v>45453</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10865,13 +10840,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10914,7 +10884,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10928,10 +10898,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46045</v>
+        <v>46268</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10943,8 +10913,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10987,7 +10962,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11001,10 +10976,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44692</v>
+        <v>46268</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11016,8 +10991,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11060,7 +11040,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11074,10 +11054,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46057</v>
+        <v>46227</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11089,8 +11069,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11133,7 +11118,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11147,10 +11132,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46059</v>
+        <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11162,8 +11147,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11206,7 +11196,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11220,10 +11210,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46059</v>
+        <v>46232</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11236,7 +11226,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11279,7 +11269,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11293,10 +11283,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46059</v>
+        <v>45615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11309,7 +11299,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11352,7 +11342,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11366,10 +11356,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44900</v>
+        <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11382,7 +11372,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11425,7 +11415,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11439,10 +11429,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44907</v>
+        <v>45596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11454,8 +11444,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11498,7 +11493,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11512,10 +11507,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45390</v>
+        <v>46281</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11527,8 +11522,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>35.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44658</v>
+        <v>45396</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11600,8 +11600,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11644,7 +11649,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11658,10 +11663,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45174</v>
+        <v>45660</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11673,13 +11678,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>51.6</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11722,7 +11722,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11736,10 +11736,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45163</v>
+        <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11753,11 +11753,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11800,7 +11800,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45615</v>
+        <v>45818</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11873,7 +11873,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45146</v>
+        <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11904,11 +11904,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11951,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45596</v>
+        <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11982,11 +11982,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12029,7 +12029,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12043,10 +12043,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45396</v>
+        <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>9.6</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12107,7 +12107,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12121,10 +12121,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45660</v>
+        <v>45840</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12136,8 +12136,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12180,7 +12185,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12194,10 +12199,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45799</v>
+        <v>45875</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12209,13 +12214,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12258,7 +12258,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12272,10 +12272,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45818</v>
+        <v>45881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45716</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>46182</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44895</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45197</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45777</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44536</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45669</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45688</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>44692</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>44658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>44969</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>44938</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>45390</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45168</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45386</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44900</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>46139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44900</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46140</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>46140</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46140</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46140</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45681</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45329</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45926</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>46146</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45203</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45957</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45068</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45961</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44907</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45968</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45028</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45975</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45229</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45995</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>46000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46013</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44938</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>46169</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45988</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>46009</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>45915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>46170</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>46045</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>46048</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>46059</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>46181</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>46181</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>45593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>46093</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>46098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45614</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>46100</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>46195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>46196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45372</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>45708</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>46111</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>46244</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46128</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>46203</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>46209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>46255</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>46199</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46258</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>46261</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44747</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46220</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46265</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45453</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>46268</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46268</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>46227</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46232</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>46281</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45396</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45660</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45818</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45840</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45875</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45716</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>46182</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE159"/>
+  <dimension ref="A1:AE158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44895</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45197</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45777</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45072</v>
+        <v>44536</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44536</v>
+        <v>45203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45203</v>
+        <v>45669</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45669</v>
+        <v>45072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>45688</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45560</v>
+        <v>44692</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2530,13 +2530,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2579,7 +2574,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2593,10 +2588,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44692</v>
+        <v>45560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2608,8 +2603,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>44658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>14.9</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45007</v>
+        <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3209,11 +3209,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45680</v>
+        <v>45875</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45468</v>
+        <v>45058</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>25.4</v>
+        <v>14.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44969</v>
+        <v>45881</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3436,13 +3436,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3485,7 +3480,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44938</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,8 +3509,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45726</v>
+        <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45390</v>
+        <v>45468</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,8 +3733,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>25.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3777,7 +3782,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3791,10 +3796,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45226</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,13 +3811,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3855,7 +3855,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45168</v>
+        <v>44969</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3884,8 +3884,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3928,7 +3933,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3942,10 +3947,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45236</v>
+        <v>45226</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3959,11 +3964,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4006,7 +4011,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4020,10 +4025,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45386</v>
+        <v>45726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4035,13 +4040,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44900</v>
+        <v>45386</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>46139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46140</v>
+        <v>45390</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4269,13 +4269,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4318,7 +4313,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4332,10 +4327,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44900</v>
+        <v>46140</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4347,8 +4342,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>16.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46140</v>
+        <v>45168</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4420,13 +4420,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4469,7 +4464,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4486,7 +4481,7 @@
         <v>46140</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4504,7 +4499,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4547,7 +4542,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4564,7 +4559,7 @@
         <v>46140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4582,7 +4577,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4625,7 +4620,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4642,7 +4637,7 @@
         <v>46140</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.7</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46141</v>
+        <v>45236</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4734,11 +4729,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4781,7 +4776,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4798,7 +4793,7 @@
         <v>46140</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.9</v>
+        <v>10.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4859,7 +4854,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45681</v>
+        <v>46141</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4888,8 +4883,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45329</v>
+        <v>46140</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4961,8 +4961,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5005,7 +5010,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46612-2025</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5019,10 +5024,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45926</v>
+        <v>46146</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5034,13 +5039,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46146</v>
+        <v>44900</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5112,8 +5112,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5156,7 +5161,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5166,14 +5171,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44747</v>
+        <v>46002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5185,8 +5190,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5229,7 +5239,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5243,10 +5253,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>44938</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5259,7 +5269,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5302,7 +5312,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5312,14 +5322,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>44900</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5332,7 +5342,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5375,7 +5385,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5389,10 +5399,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45203</v>
+        <v>45985</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5406,11 +5416,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>14.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5453,7 +5463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5467,10 +5477,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45957</v>
+        <v>45681</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5483,7 +5493,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5526,7 +5536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5540,10 +5550,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44939</v>
+        <v>45957</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5555,13 +5565,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5604,7 +5609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5618,10 +5623,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45068</v>
+        <v>45329</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5634,7 +5639,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5694,7 +5699,7 @@
         <v>45961</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5755,7 +5760,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5769,10 +5774,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44907</v>
+        <v>45957</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5785,7 +5790,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5828,7 +5833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45957</v>
+        <v>45968</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5857,8 +5862,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5901,7 +5911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5915,10 +5925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45037</v>
+        <v>45972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5931,7 +5941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5974,7 +5984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5984,14 +5994,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>45975</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6009,7 +6019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6052,7 +6062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6066,10 +6076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44938</v>
+        <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6082,7 +6092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6125,7 +6135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6139,10 +6149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45968</v>
+        <v>45520</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6154,13 +6164,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6213,14 +6218,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45028</v>
+        <v>45588</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6286,14 +6291,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45985</v>
+        <v>46169</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6307,11 +6312,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6359,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45972</v>
+        <v>45203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6388,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6441,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45975</v>
+        <v>46170</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6456,13 +6466,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6515,14 +6520,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45229</v>
+        <v>45995</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45635</v>
+        <v>46000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6609,11 +6614,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45995</v>
+        <v>44939</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6685,8 +6690,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6739,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6746,7 +6756,7 @@
         <v>46000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6774,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6817,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6831,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46000</v>
+        <v>45068</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6836,13 +6846,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6885,7 +6890,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6899,10 +6904,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46013</v>
+        <v>44907</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6914,13 +6919,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6963,7 +6963,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44938</v>
+        <v>45037</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44930</v>
+        <v>45028</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46169</v>
+        <v>46013</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
         <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45988</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>46009</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>45915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7650,7 +7650,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7660,14 +7660,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46045</v>
+        <v>45229</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7723,7 +7723,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46048</v>
+        <v>46181</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46057</v>
+        <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7825,8 +7825,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7869,7 +7874,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7883,10 +7888,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44938</v>
+        <v>46045</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7898,13 +7903,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7947,7 +7947,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7961,10 +7961,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46059</v>
+        <v>46048</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8020,7 +8020,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46059</v>
+        <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8049,8 +8049,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>23.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8093,7 +8098,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8107,10 +8112,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8123,7 +8128,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8166,7 +8171,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8180,10 +8185,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46181</v>
+        <v>46059</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8196,7 +8201,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8239,7 +8244,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8253,10 +8258,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46181</v>
+        <v>46059</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8269,7 +8274,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8312,7 +8317,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8326,10 +8331,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45593</v>
+        <v>46059</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8342,7 +8347,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8385,7 +8390,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8399,10 +8404,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45112</v>
+        <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8415,7 +8420,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8458,7 +8463,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8472,10 +8477,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46093</v>
+        <v>44938</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8488,7 +8493,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8531,7 +8536,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8545,10 +8550,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46098</v>
+        <v>44930</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8560,13 +8565,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8609,7 +8609,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8623,10 +8623,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45614</v>
+        <v>46203</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8638,8 +8638,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8682,7 +8687,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8696,10 +8701,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8712,7 +8717,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8755,7 +8760,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8769,10 +8774,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46195</v>
+        <v>46098</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8790,7 +8795,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>23.6</v>
+        <v>7.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8833,7 +8838,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8847,10 +8852,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46196</v>
+        <v>46100</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8863,7 +8868,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8906,7 +8911,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8920,10 +8925,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45372</v>
+        <v>46111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8941,7 +8946,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8984,7 +8989,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8998,10 +9003,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44728</v>
+        <v>46203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9013,8 +9018,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9057,7 +9067,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9071,10 +9081,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45708</v>
+        <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9086,8 +9096,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9130,7 +9145,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9144,10 +9159,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46111</v>
+        <v>46128</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9161,11 +9176,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>14.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9208,7 +9223,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9222,10 +9237,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46244</v>
+        <v>45593</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9238,7 +9253,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9281,7 +9296,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9291,14 +9306,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46128</v>
+        <v>46209</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9312,11 +9327,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>14.1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9359,7 +9374,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9373,10 +9388,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46203</v>
+        <v>45112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9388,13 +9403,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9437,7 +9447,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9451,10 +9461,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45174</v>
+        <v>46255</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9472,7 +9482,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>51.6</v>
+        <v>24.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9515,7 +9525,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9529,10 +9539,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45468</v>
+        <v>45614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,13 +9554,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9593,7 +9598,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9603,14 +9608,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9624,11 +9629,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9671,7 +9676,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9685,10 +9690,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45711</v>
+        <v>46258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9701,7 +9706,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9744,7 +9749,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9758,10 +9763,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45174</v>
+        <v>45372</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9779,7 +9784,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9827,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9832,14 +9837,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46209</v>
+        <v>44728</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9849,11 +9854,6 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -9900,7 +9900,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45204</v>
+        <v>45708</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,13 +9929,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9978,7 +9973,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9992,10 +9987,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10013,7 +10008,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>24.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10056,7 +10051,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10066,14 +10061,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46199</v>
+        <v>46220</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10087,11 +10082,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10134,7 +10129,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10148,10 +10143,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44897</v>
+        <v>46205</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10164,7 +10159,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10207,7 +10202,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10221,10 +10216,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45163</v>
+        <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10238,11 +10233,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10285,7 +10280,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10299,10 +10294,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10314,8 +10309,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10358,7 +10358,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10389,11 +10389,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44747</v>
+        <v>46227</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10465,8 +10465,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10509,7 +10514,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10523,10 +10528,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46220</v>
+        <v>45174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10544,7 +10549,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.8</v>
+        <v>51.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10587,7 +10592,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10601,10 +10606,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46205</v>
+        <v>45468</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10616,8 +10621,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10660,7 +10670,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10674,10 +10684,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46265</v>
+        <v>45711</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10689,13 +10699,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10738,7 +10743,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10752,10 +10757,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45614</v>
+        <v>46232</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10768,7 +10773,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10811,7 +10816,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10825,10 +10830,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45453</v>
+        <v>45174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10840,8 +10845,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10884,7 +10894,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10898,10 +10908,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46268</v>
+        <v>46280</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10913,13 +10923,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10962,7 +10967,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10976,10 +10981,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10993,11 +10998,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.6</v>
+        <v>35.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11040,7 +11045,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11054,10 +11059,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46227</v>
+        <v>45204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11075,7 +11080,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11118,7 +11123,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11132,10 +11137,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45146</v>
+        <v>44897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11147,13 +11152,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46232</v>
+        <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11225,8 +11225,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11283,10 +11288,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45615</v>
+        <v>44747</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11299,7 +11304,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11342,7 +11347,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11356,10 +11361,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46280</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11372,7 +11377,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11415,7 +11420,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11429,10 +11434,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45596</v>
+        <v>45614</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11444,13 +11449,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46281</v>
+        <v>45453</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11522,13 +11522,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>35.1</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11571,7 +11566,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11585,10 +11580,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45396</v>
+        <v>45146</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11602,11 +11597,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11649,7 +11644,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11663,10 +11658,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45660</v>
+        <v>45615</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11679,7 +11674,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11722,7 +11717,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11736,10 +11731,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45799</v>
+        <v>45596</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11757,7 +11752,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11800,7 +11795,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11814,10 +11809,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45818</v>
+        <v>45396</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11829,8 +11824,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>9.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11873,7 +11873,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45468</v>
+        <v>45660</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11902,13 +11902,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11951,7 +11946,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +11960,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45355</v>
+        <v>45799</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11982,11 +11977,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12029,7 +12024,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12043,10 +12038,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45840</v>
+        <v>45818</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12058,13 +12053,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12107,7 +12097,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12121,10 +12111,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45840</v>
+        <v>45468</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12142,7 +12132,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12185,7 +12175,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12199,10 +12189,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45875</v>
+        <v>45355</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12214,8 +12204,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12258,24 +12253,24 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>S 4139-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45881</v>
+        <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12287,8 +12282,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>S 4141-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12409,7 +12409,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>S 733-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12423,10 +12423,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45247</v>
+        <v>45716</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12440,11 +12440,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>20.6</v>
+        <v>33.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>S 98-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12501,10 +12501,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45716</v>
+        <v>46036</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>33.7</v>
+        <v>72.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12562,10 +12562,10 @@
       </c>
       <c r="V157" s="2" t="inlineStr"/>
     </row>
-    <row r="158" ht="15" customHeight="1">
+    <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S 98-2026</t>
+          <t>S 1683-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12575,14 +12575,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46036</v>
+        <v>46182</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12594,13 +12594,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>72.5</v>
+        <v>37.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12639,79 +12634,6 @@
         <v>0</v>
       </c>
       <c r="V158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>S 1683-2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D159" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E159" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43407-2022</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44834</v>
+        <v>45197</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,26 +845,21 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -875,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -891,362 +886,367 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 43407-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Orre</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 57209-2022</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>44895</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>6.3</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44536</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45203</v>
+        <v>45329</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45669</v>
+        <v>45596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45072</v>
+        <v>45396</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2165,8 +2170,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2209,7 +2219,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2223,10 +2233,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45688</v>
+        <v>45028</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2239,7 +2249,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2282,7 +2292,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2296,10 +2306,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45545</v>
+        <v>45203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2312,7 +2322,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2355,7 +2365,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2369,10 +2379,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45686</v>
+        <v>45669</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2385,7 +2395,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2428,7 +2438,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2442,10 +2452,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45232</v>
+        <v>45660</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2458,7 +2468,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2501,7 +2511,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2515,10 +2525,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44692</v>
+        <v>45680</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2531,7 +2541,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2574,7 +2584,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2588,10 +2598,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45560</v>
+        <v>45468</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2605,11 +2615,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2652,7 +2662,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2666,10 +2676,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45104</v>
+        <v>45890</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2682,7 +2692,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2725,7 +2735,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2739,10 +2749,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44658</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45588</v>
+        <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2828,7 +2838,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2871,7 +2881,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2885,10 +2895,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45700</v>
+        <v>45520</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2900,13 +2910,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2949,7 +2954,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2963,10 +2968,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45153</v>
+        <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2978,13 +2983,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>45799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3056,8 +3056,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3100,7 +3105,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3114,10 +3119,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45840</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3131,11 +3136,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3178,7 +3183,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45840</v>
+        <v>44536</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3207,13 +3212,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45875</v>
+        <v>45453</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45058</v>
+        <v>45153</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3360,11 +3360,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>14.9</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45881</v>
+        <v>45104</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3511,11 +3511,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45680</v>
+        <v>44939</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3587,8 +3587,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3636,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,10 +3650,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45890</v>
+        <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3661,7 +3666,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3704,7 +3709,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3723,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45468</v>
+        <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,13 +3738,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>25.4</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3782,7 +3782,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3855,7 +3855,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44969</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3884,13 +3884,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3928,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3942,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45226</v>
+        <v>45700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3964,11 +3959,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4011,7 +4006,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4025,10 +4020,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45726</v>
+        <v>45681</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4041,7 +4036,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4084,7 +4079,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4098,10 +4093,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45386</v>
+        <v>45072</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4113,13 +4108,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4162,7 +4152,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4176,10 +4166,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46139</v>
+        <v>45614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4191,13 +4181,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4240,7 +4225,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4254,10 +4239,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45390</v>
+        <v>45818</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4270,7 +4255,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4313,7 +4298,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4323,14 +4308,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46140</v>
+        <v>45588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4342,13 +4327,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>16.1</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4391,7 +4371,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4405,10 +4385,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45168</v>
+        <v>45588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4421,7 +4401,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4464,7 +4444,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4478,10 +4458,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46140</v>
+        <v>45957</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4493,13 +4473,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4542,7 +4517,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4556,10 +4531,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46140</v>
+        <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4571,13 +4546,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4620,7 +4590,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4634,10 +4604,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46140</v>
+        <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4649,13 +4619,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4698,7 +4663,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4712,10 +4677,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45236</v>
+        <v>45168</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4727,13 +4692,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4776,7 +4736,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4790,10 +4750,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46140</v>
+        <v>45961</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4807,11 +4767,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4854,7 +4814,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4868,10 +4828,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46141</v>
+        <v>45203</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4885,11 +4845,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4932,7 +4892,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4946,10 +4906,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46140</v>
+        <v>45708</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4961,13 +4921,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5010,7 +4965,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5024,10 +4979,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46146</v>
+        <v>45560</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5039,8 +4994,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>9.1</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5083,7 +5043,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5097,10 +5057,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44900</v>
+        <v>45711</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5112,13 +5072,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5161,7 +5116,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5171,14 +5126,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46002</v>
+        <v>45968</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5196,7 +5151,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5239,7 +5194,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5253,10 +5208,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44938</v>
+        <v>45686</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5269,7 +5224,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5312,7 +5267,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5326,10 +5281,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44900</v>
+        <v>45236</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5341,8 +5296,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5385,7 +5345,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5399,10 +5359,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45985</v>
+        <v>45972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5414,13 +5374,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>14.1</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5463,7 +5418,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5477,10 +5432,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45681</v>
+        <v>45975</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5492,8 +5447,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5536,7 +5496,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5550,10 +5510,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45957</v>
+        <v>45174</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5565,8 +5525,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5609,7 +5574,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5623,10 +5588,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45329</v>
+        <v>44747</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5639,7 +5604,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5682,7 +5647,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5696,10 +5661,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45961</v>
+        <v>45058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5713,11 +5678,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>14.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5760,7 +5725,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5774,10 +5739,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45957</v>
+        <v>44930</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5790,7 +5755,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5833,7 +5798,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5847,10 +5812,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45968</v>
+        <v>45204</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5868,7 +5833,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5911,7 +5876,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5925,10 +5890,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45972</v>
+        <v>45995</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5941,7 +5906,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5984,7 +5949,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5994,14 +5959,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45975</v>
+        <v>45229</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6013,13 +5978,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6062,7 +6022,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6076,10 +6036,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44747</v>
+        <v>46000</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6091,8 +6051,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6135,7 +6100,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6149,10 +6114,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45520</v>
+        <v>46000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6164,8 +6129,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6178,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6218,14 +6188,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45588</v>
+        <v>45468</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6237,8 +6207,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>25.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6256,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6291,14 +6266,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46169</v>
+        <v>45726</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6310,13 +6285,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6359,7 +6329,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6373,10 +6343,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45203</v>
+        <v>45372</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6390,11 +6360,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6407,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6421,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46170</v>
+        <v>46048</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6467,7 +6437,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>10.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6480,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6494,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45995</v>
+        <v>46045</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6510,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6553,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6567,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6614,11 +6584,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6631,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6645,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44939</v>
+        <v>46009</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6692,11 +6662,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6739,7 +6709,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6753,10 +6723,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6774,7 +6744,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6817,7 +6787,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6831,10 +6801,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45068</v>
+        <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6846,8 +6816,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6890,7 +6865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6904,10 +6879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44907</v>
+        <v>45988</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6919,8 +6894,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>9.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6963,7 +6943,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6977,10 +6957,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45037</v>
+        <v>45939</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6992,8 +6972,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>8.1</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7036,7 +7021,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7050,10 +7035,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45028</v>
+        <v>45037</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7066,7 +7051,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7109,7 +7094,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7123,10 +7108,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46013</v>
+        <v>44747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7138,13 +7123,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7187,7 +7167,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7201,10 +7181,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46009</v>
+        <v>46057</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7216,13 +7196,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7265,7 +7240,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7279,10 +7254,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45988</v>
+        <v>44969</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7300,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>9.9</v>
+        <v>5.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7343,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7357,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45939</v>
+        <v>46059</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7372,13 +7347,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7421,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7435,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46009</v>
+        <v>46059</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7450,13 +7420,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7499,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7513,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45915</v>
+        <v>46059</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7528,13 +7493,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>10.6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7577,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7591,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46181</v>
+        <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7606,8 +7566,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7650,7 +7615,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7660,14 +7625,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45229</v>
+        <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7680,7 +7645,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7723,7 +7688,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7737,10 +7702,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46181</v>
+        <v>46244</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7753,7 +7718,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7796,7 +7761,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7810,10 +7775,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45635</v>
+        <v>45468</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7831,7 +7796,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7874,7 +7839,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7888,10 +7853,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46045</v>
+        <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7904,7 +7869,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7947,7 +7912,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7961,10 +7926,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46048</v>
+        <v>46093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7977,7 +7942,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>10.8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8020,7 +7985,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8034,10 +7999,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46195</v>
+        <v>46098</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8055,7 +8020,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>23.6</v>
+        <v>7.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8098,7 +8063,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8112,10 +8077,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46057</v>
+        <v>46100</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8128,7 +8093,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8171,7 +8136,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8185,10 +8150,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46059</v>
+        <v>45355</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8200,8 +8165,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8244,7 +8214,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8258,10 +8228,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46059</v>
+        <v>46111</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8273,8 +8243,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8317,7 +8292,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8331,10 +8306,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46059</v>
+        <v>45007</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8346,8 +8321,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8390,7 +8370,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8404,10 +8384,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46196</v>
+        <v>44692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8420,7 +8400,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8463,7 +8443,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8477,10 +8457,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44938</v>
+        <v>45840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8492,8 +8472,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8536,7 +8521,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8550,10 +8535,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44930</v>
+        <v>45840</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8565,8 +8550,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8609,7 +8599,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8623,10 +8613,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46203</v>
+        <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8640,11 +8630,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.1</v>
+        <v>14.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8687,7 +8677,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8701,10 +8691,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46093</v>
+        <v>44900</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8717,7 +8707,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8760,7 +8750,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8774,10 +8764,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46098</v>
+        <v>45875</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8789,13 +8779,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8838,7 +8823,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8852,10 +8837,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46100</v>
+        <v>44907</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8911,7 +8896,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8925,10 +8910,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46111</v>
+        <v>45881</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8940,13 +8925,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8989,7 +8969,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9003,10 +8983,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46203</v>
+        <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9020,11 +9000,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9067,7 +9047,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9081,10 +9061,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44938</v>
+        <v>45226</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9098,11 +9078,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9145,7 +9125,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9159,10 +9139,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46128</v>
+        <v>46140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9176,11 +9156,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>14.1</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9223,7 +9203,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9237,10 +9217,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45593</v>
+        <v>46140</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9252,8 +9232,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9296,7 +9281,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9306,14 +9291,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46209</v>
+        <v>45390</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9325,13 +9310,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9374,7 +9354,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9388,10 +9368,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45112</v>
+        <v>46139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9403,8 +9383,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9447,7 +9432,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9461,10 +9446,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46255</v>
+        <v>44658</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9476,13 +9461,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>24.1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9525,7 +9505,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9539,10 +9519,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45614</v>
+        <v>46140</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9554,8 +9534,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>16.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9598,7 +9583,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9608,14 +9593,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46199</v>
+        <v>46140</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9629,11 +9614,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9676,7 +9661,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9690,10 +9675,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46258</v>
+        <v>45174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9705,8 +9690,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>51.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9749,7 +9739,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9763,10 +9753,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45372</v>
+        <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9780,11 +9770,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9827,7 +9817,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9841,10 +9831,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44728</v>
+        <v>46140</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9856,8 +9846,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9900,7 +9895,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9914,10 +9909,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45708</v>
+        <v>45386</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,8 +9924,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9973,7 +9973,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46261</v>
+        <v>44938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10002,13 +10002,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10051,7 +10046,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46220</v>
+        <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10086,7 +10081,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10129,7 +10124,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10143,10 +10138,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46205</v>
+        <v>46146</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10159,7 +10154,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10202,7 +10197,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10216,10 +10211,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46265</v>
+        <v>45615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10231,13 +10226,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10280,7 +10270,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10294,10 +10284,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46268</v>
+        <v>45146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10315,7 +10305,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10358,7 +10348,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10372,10 +10362,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46268</v>
+        <v>44938</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10387,13 +10377,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10436,7 +10421,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10450,10 +10435,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46227</v>
+        <v>45985</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10471,7 +10456,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>14.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10514,7 +10499,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10524,14 +10509,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45174</v>
+        <v>46002</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10549,7 +10534,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>51.6</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10592,7 +10577,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10602,14 +10587,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45468</v>
+        <v>46169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10623,11 +10608,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10670,7 +10655,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10684,10 +10669,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45711</v>
+        <v>46170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10700,7 +10685,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10743,7 +10728,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10757,10 +10742,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46232</v>
+        <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10773,7 +10758,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10816,7 +10801,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10830,10 +10815,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45174</v>
+        <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10845,13 +10830,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10894,7 +10874,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10908,10 +10888,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46280</v>
+        <v>46195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10923,8 +10903,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>23.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10967,7 +10952,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10981,10 +10966,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46281</v>
+        <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10996,13 +10981,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>35.1</v>
+        <v>4.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11045,7 +11025,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11059,10 +11039,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45204</v>
+        <v>46203</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11076,11 +11056,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11123,7 +11103,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11137,10 +11117,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44897</v>
+        <v>46203</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11152,8 +11132,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11196,7 +11181,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11206,14 +11191,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45163</v>
+        <v>46209</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11231,7 +11216,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11274,7 +11259,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11284,14 +11269,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44747</v>
+        <v>46199</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11303,8 +11288,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11347,7 +11337,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11361,10 +11351,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11377,7 +11367,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11420,7 +11410,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11434,10 +11424,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45614</v>
+        <v>46255</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11449,8 +11439,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>24.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11493,7 +11488,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11507,10 +11502,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45453</v>
+        <v>46261</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11522,8 +11517,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45146</v>
+        <v>46205</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11595,13 +11595,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11644,7 +11639,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11658,10 +11653,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45615</v>
+        <v>46220</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11673,8 +11668,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45596</v>
+        <v>46265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45396</v>
+        <v>46268</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11826,11 +11826,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11873,7 +11873,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45660</v>
+        <v>46227</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11902,8 +11902,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11946,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11960,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45799</v>
+        <v>46268</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11977,7 +11982,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -12024,7 +12029,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12038,10 +12043,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45818</v>
+        <v>46232</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12054,7 +12059,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12097,7 +12102,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12111,10 +12116,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45468</v>
+        <v>46280</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12126,13 +12131,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12175,7 +12175,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45355</v>
+        <v>46281</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12206,11 +12206,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.5</v>
+        <v>35.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12270,7 +12270,7 @@
         <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45716</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>46036</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46182</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE158"/>
+  <dimension ref="A1:AE159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 46376-2023</t>
+          <t>A 43407-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45197</v>
+        <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,11 +845,16 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -858,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -870,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -886,367 +891,362 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Knölspindel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 21111-2025</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>1.9</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Korallblylav</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 43407-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 57209-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knölspindel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44797</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>44490</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44512</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44797</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>44484</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45329</v>
+        <v>44536</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45596</v>
+        <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45396</v>
+        <v>45669</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2170,13 +2165,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2219,7 +2209,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2233,10 +2223,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45028</v>
+        <v>45688</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2249,7 +2239,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2292,7 +2282,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2306,10 +2296,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45203</v>
+        <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2322,7 +2312,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2365,7 +2355,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2379,10 +2369,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45669</v>
+        <v>45686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2395,7 +2385,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2438,7 +2428,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45660</v>
+        <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2468,7 +2458,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2501,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2525,10 +2515,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45680</v>
+        <v>44692</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2541,7 +2531,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2584,7 +2574,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2598,10 +2588,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45468</v>
+        <v>45560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2615,11 +2605,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2662,7 +2652,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2676,10 +2666,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45890</v>
+        <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2692,7 +2682,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2735,7 +2725,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2749,10 +2739,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>44658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2808,7 +2798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2822,10 +2812,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45593</v>
+        <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2838,7 +2828,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2881,7 +2871,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,10 +2885,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45520</v>
+        <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2910,8 +2900,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2954,7 +2949,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2968,10 +2963,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45545</v>
+        <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2983,8 +2978,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45799</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3056,13 +3056,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3105,7 +3100,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3119,10 +3114,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3136,11 +3131,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3183,7 +3178,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44536</v>
+        <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3212,8 +3207,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45453</v>
+        <v>45875</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45153</v>
+        <v>45058</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3360,11 +3360,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>14.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45104</v>
+        <v>45881</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45635</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3511,11 +3511,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44939</v>
+        <v>45890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3587,13 +3587,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3636,7 +3631,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45068</v>
+        <v>45680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3666,7 +3661,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3709,7 +3704,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3723,10 +3718,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45401</v>
+        <v>45468</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3738,8 +3733,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>25.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3782,7 +3782,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>44969</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3811,8 +3811,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3855,7 +3860,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3869,10 +3874,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45232</v>
+        <v>45726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3885,7 +3890,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3928,7 +3933,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3942,10 +3947,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45700</v>
+        <v>44938</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3957,13 +3962,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45681</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45072</v>
+        <v>45168</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45614</v>
+        <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4181,8 +4181,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4225,7 +4230,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4239,10 +4244,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45818</v>
+        <v>44900</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4254,8 +4259,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4298,7 +4308,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4308,14 +4318,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45588</v>
+        <v>45226</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4327,8 +4337,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4371,7 +4386,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4385,10 +4400,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45588</v>
+        <v>44900</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4401,7 +4416,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4444,7 +4459,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4458,10 +4473,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45957</v>
+        <v>45681</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4474,7 +4489,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4517,7 +4532,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4531,10 +4546,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45614</v>
+        <v>45386</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4544,6 +4559,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4590,7 +4610,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4604,10 +4624,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>45329</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4620,7 +4640,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4663,7 +4683,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4677,10 +4697,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45168</v>
+        <v>46139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4692,8 +4712,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4736,7 +4761,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4750,10 +4775,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45961</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4765,13 +4790,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4814,7 +4834,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4828,10 +4848,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45203</v>
+        <v>46140</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,11 +4865,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>16.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4892,7 +4912,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4906,10 +4926,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45708</v>
+        <v>45961</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4921,8 +4941,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4965,7 +4990,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4979,10 +5004,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45560</v>
+        <v>45957</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4994,13 +5019,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5043,7 +5063,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5057,10 +5077,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45711</v>
+        <v>46140</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5072,8 +5092,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5116,7 +5141,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5130,10 +5155,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45968</v>
+        <v>46140</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5151,7 +5176,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5194,7 +5219,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5208,10 +5233,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45686</v>
+        <v>46140</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5223,8 +5248,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5267,7 +5297,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5281,10 +5311,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45236</v>
+        <v>45968</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5298,11 +5328,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5345,7 +5375,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5359,10 +5389,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45972</v>
+        <v>46140</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5374,8 +5404,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5418,7 +5453,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5432,10 +5467,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45975</v>
+        <v>46141</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5453,7 +5488,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5496,7 +5531,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5510,10 +5545,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45174</v>
+        <v>44747</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5525,13 +5560,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5574,7 +5604,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5588,10 +5618,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44747</v>
+        <v>45972</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5604,7 +5634,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5647,7 +5677,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5661,10 +5691,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45058</v>
+        <v>46140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5682,7 +5712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>14.9</v>
+        <v>5.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5725,7 +5755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5739,10 +5769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44930</v>
+        <v>45520</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5755,7 +5785,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5798,7 +5828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5808,14 +5838,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45204</v>
+        <v>45588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5827,13 +5857,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5876,7 +5901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5890,10 +5915,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45995</v>
+        <v>45975</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5905,8 +5930,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5949,7 +5979,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5959,14 +5989,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45229</v>
+        <v>45203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5978,8 +6008,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6022,7 +6057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6036,10 +6071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46000</v>
+        <v>46146</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6051,13 +6086,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>9.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6100,7 +6130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6114,10 +6144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46000</v>
+        <v>44939</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6131,11 +6161,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6178,7 +6208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6192,10 +6222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45468</v>
+        <v>45068</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6207,13 +6237,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>25.4</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6256,7 +6281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6270,10 +6295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45726</v>
+        <v>44907</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6286,7 +6311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6329,7 +6354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6343,10 +6368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45372</v>
+        <v>45995</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6358,13 +6383,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6407,7 +6427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6417,14 +6437,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46048</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6436,8 +6456,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>10.8</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6480,7 +6505,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6494,10 +6519,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46045</v>
+        <v>44938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6510,7 +6535,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6553,7 +6578,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6567,10 +6592,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6584,11 +6609,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6631,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6645,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46009</v>
+        <v>45985</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6662,11 +6687,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>14.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6709,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6723,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46009</v>
+        <v>45037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6738,13 +6763,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6787,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6801,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45915</v>
+        <v>46000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6818,11 +6838,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10.6</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6865,7 +6885,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6879,10 +6899,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45988</v>
+        <v>45028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6894,13 +6914,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>9.9</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6943,7 +6958,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6957,10 +6972,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45939</v>
+        <v>46013</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6974,11 +6989,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7021,7 +7036,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7031,14 +7046,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45037</v>
+        <v>45229</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7051,7 +7066,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7094,7 +7109,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7108,10 +7123,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44747</v>
+        <v>46009</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7123,8 +7138,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7167,7 +7187,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7181,10 +7201,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46057</v>
+        <v>45988</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7196,8 +7216,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>9.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7240,7 +7265,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7254,10 +7279,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44969</v>
+        <v>45939</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7300,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7343,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7357,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46059</v>
+        <v>46009</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7347,8 +7372,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7421,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7435,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46059</v>
+        <v>45915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7420,8 +7450,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7499,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7513,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46059</v>
+        <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7493,8 +7528,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7577,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7591,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44900</v>
+        <v>46045</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7566,13 +7606,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7615,7 +7650,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7629,10 +7664,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44728</v>
+        <v>46048</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7645,7 +7680,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>10.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7688,7 +7723,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7702,10 +7737,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46244</v>
+        <v>46057</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7718,7 +7753,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7761,7 +7796,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7775,10 +7810,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45468</v>
+        <v>46059</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7790,13 +7825,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7839,7 +7869,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7849,14 +7879,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44938</v>
+        <v>46169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7868,8 +7898,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7912,7 +7947,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7926,10 +7961,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46093</v>
+        <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7942,7 +7977,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7985,7 +8020,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7999,10 +8034,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46098</v>
+        <v>46059</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8014,13 +8049,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8063,7 +8093,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8077,10 +8107,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46100</v>
+        <v>44938</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8093,7 +8123,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8136,7 +8166,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8150,10 +8180,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45355</v>
+        <v>44930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8165,13 +8195,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8214,7 +8239,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8228,10 +8253,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46111</v>
+        <v>46170</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8243,13 +8268,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8292,7 +8312,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8306,10 +8326,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45007</v>
+        <v>46093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8321,13 +8341,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8370,7 +8385,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8384,10 +8399,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44692</v>
+        <v>46098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8399,8 +8414,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8443,7 +8463,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8457,10 +8477,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45840</v>
+        <v>46100</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8472,13 +8492,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8521,7 +8536,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8535,10 +8550,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45840</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8550,13 +8565,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8599,7 +8609,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8613,10 +8623,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46128</v>
+        <v>46181</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8628,13 +8638,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>14.1</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8677,7 +8682,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8691,10 +8696,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44900</v>
+        <v>46111</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8706,8 +8711,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8750,7 +8760,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8764,10 +8774,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45875</v>
+        <v>44938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8779,8 +8789,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8823,7 +8838,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8837,10 +8852,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44907</v>
+        <v>46128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8852,8 +8867,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>14.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8896,7 +8916,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8910,10 +8930,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45881</v>
+        <v>45593</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8926,7 +8946,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8969,7 +8989,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8983,10 +9003,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46140</v>
+        <v>46195</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9004,7 +9024,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>23.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9047,7 +9067,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9061,10 +9081,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45226</v>
+        <v>46196</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9076,13 +9096,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9125,7 +9140,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9139,10 +9154,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46140</v>
+        <v>45112</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9154,13 +9169,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9203,7 +9213,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9217,10 +9227,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46140</v>
+        <v>45614</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9232,13 +9242,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9281,7 +9286,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9295,10 +9300,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45390</v>
+        <v>46203</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9310,8 +9315,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9354,7 +9364,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9368,10 +9378,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46139</v>
+        <v>46203</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9385,11 +9395,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9432,7 +9442,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9446,10 +9456,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44658</v>
+        <v>45372</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9461,8 +9471,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9505,7 +9520,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9519,10 +9534,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46140</v>
+        <v>44728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9534,13 +9549,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>16.1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9583,7 +9593,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9597,10 +9607,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46140</v>
+        <v>45708</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9612,13 +9622,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>10.7</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9661,7 +9666,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9671,14 +9676,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45174</v>
+        <v>46209</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9692,11 +9697,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>51.6</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9739,7 +9744,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9753,10 +9758,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45163</v>
+        <v>46255</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9770,11 +9775,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>24.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9817,7 +9822,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9827,14 +9832,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46140</v>
+        <v>46199</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9848,11 +9853,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9895,7 +9900,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9909,10 +9914,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45386</v>
+        <v>45174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9926,11 +9931,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>51.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9973,7 +9978,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9987,10 +9992,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44938</v>
+        <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10002,8 +10007,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10046,7 +10056,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10060,10 +10070,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46141</v>
+        <v>46261</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10081,7 +10091,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10124,7 +10134,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10138,10 +10148,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46146</v>
+        <v>46220</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10153,8 +10163,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>9.1</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10197,7 +10212,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10211,10 +10226,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45615</v>
+        <v>45711</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10227,7 +10242,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10270,7 +10285,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10284,10 +10299,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45146</v>
+        <v>46205</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10299,13 +10314,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10348,7 +10358,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10362,10 +10372,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44938</v>
+        <v>46265</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10377,8 +10387,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10421,7 +10436,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10435,10 +10450,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45985</v>
+        <v>45174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10456,7 +10471,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>14.1</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10499,7 +10514,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10509,14 +10524,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46002</v>
+        <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10530,11 +10545,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10577,7 +10592,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10587,14 +10602,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46169</v>
+        <v>46268</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10612,7 +10627,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10655,7 +10670,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10669,10 +10684,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46170</v>
+        <v>45204</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10684,8 +10699,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10728,7 +10748,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10742,10 +10762,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46181</v>
+        <v>46227</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10757,8 +10777,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10801,7 +10826,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10815,10 +10840,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46181</v>
+        <v>44897</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10831,7 +10856,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10874,7 +10899,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10888,10 +10913,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46195</v>
+        <v>45163</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10905,11 +10930,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>23.6</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10952,7 +10977,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10966,10 +10991,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46196</v>
+        <v>46232</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10982,7 +11007,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11025,7 +11050,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11039,10 +11064,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46203</v>
+        <v>44747</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11054,13 +11079,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11103,7 +11123,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11117,10 +11137,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46203</v>
+        <v>46281</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11138,7 +11158,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.1</v>
+        <v>35.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11181,7 +11201,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11191,14 +11211,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46209</v>
+        <v>45614</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11210,13 +11230,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11259,7 +11274,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11269,14 +11284,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46199</v>
+        <v>45453</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11288,13 +11303,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11337,7 +11347,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11351,10 +11361,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46258</v>
+        <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11366,8 +11376,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11410,7 +11425,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11424,10 +11439,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46255</v>
+        <v>45615</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11439,13 +11454,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>24.1</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11488,7 +11498,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11502,10 +11512,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46261</v>
+        <v>46244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11517,13 +11527,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11566,7 +11571,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11580,10 +11585,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46205</v>
+        <v>45596</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11595,8 +11600,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11639,7 +11649,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11653,10 +11663,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46220</v>
+        <v>46289</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11674,7 +11684,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.8</v>
+        <v>28.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11717,7 +11727,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11731,10 +11741,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46265</v>
+        <v>45396</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11752,7 +11762,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11795,7 +11805,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11809,10 +11819,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46268</v>
+        <v>45660</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11824,13 +11834,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11873,7 +11878,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11887,10 +11892,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11902,13 +11907,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11951,7 +11951,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +11965,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46268</v>
+        <v>46280</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11980,13 +11980,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12029,7 +12024,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12043,10 +12038,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46232</v>
+        <v>45799</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12058,8 +12053,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12102,7 +12102,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12116,10 +12116,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46280</v>
+        <v>45818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12175,7 +12175,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46281</v>
+        <v>45468</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>35.1</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12253,24 +12253,24 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45247</v>
+        <v>45355</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12284,11 +12284,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>S 4139-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12348,7 +12348,7 @@
         <v>45247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12409,7 +12409,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>S 4141-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12423,10 +12423,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45716</v>
+        <v>45247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12440,11 +12440,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>33.7</v>
+        <v>20.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12487,153 +12487,231 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
+          <t>S 733-2025</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>S 98-2026</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D157" s="1" t="n">
+      <c r="D158" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E157" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
+      <c r="E158" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I157" t="n">
+      <c r="I158" t="n">
         <v>72.5</v>
       </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>S 1683-2026</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D158" s="1" t="n">
+      <c r="D159" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="E158" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I158" t="n">
+      <c r="E159" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
         <v>37.1</v>
       </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="2" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE159"/>
+  <dimension ref="A1:AE161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 57209-2022</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44895</v>
+        <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -959,13 +959,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -974,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -992,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1001,329 +996,371 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 39769-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 39769-2026 artfynd.xlsx", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 39769-2026 karta.png", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 39769-2026 georefererad karta.tif", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 39769-2026 FSC-klagomål.docx", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 39769-2026 FSC-klagomål mail.docx", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 39769-2026 tillsynsbegäran.docx", "A 39769-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 39769-2026 tillsynsbegäran mail.docx", "A 39769-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Korallblylav</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 35089-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44797</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr"/>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59084-2021</t>
+          <t>A 35089-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1337,10 +1374,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44490</v>
+        <v>44797</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,13 +1389,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1401,7 +1433,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 64815-2021</t>
+          <t>A 59084-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1415,10 +1447,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44512</v>
+        <v>44490</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1430,8 +1462,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1474,7 +1511,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 35084-2022</t>
+          <t>A 64815-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1488,10 +1525,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44797</v>
+        <v>44512</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1504,7 +1541,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1547,7 +1584,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 33307-2022</t>
+          <t>A 35084-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1557,14 +1594,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44788</v>
+        <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1577,7 +1614,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1620,7 +1657,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44802-2022</t>
+          <t>A 33307-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1630,14 +1667,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44841</v>
+        <v>44788</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1650,7 +1687,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1693,7 +1730,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 64814-2021</t>
+          <t>A 44802-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1707,10 +1744,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44512</v>
+        <v>44841</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1723,7 +1760,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1766,7 +1803,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57734-2021</t>
+          <t>A 64814-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1780,10 +1817,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44484</v>
+        <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,13 +1832,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1844,7 +1876,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44783-2022</t>
+          <t>A 57734-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1858,10 +1890,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44841</v>
+        <v>44484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1873,8 +1905,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1917,7 +1954,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 44783-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1931,10 +1968,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45072</v>
+        <v>44841</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1947,7 +1984,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1990,7 +2027,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2004,10 +2041,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44536</v>
+        <v>45329</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2020,7 +2057,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2063,7 +2100,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2077,10 +2114,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45203</v>
+        <v>45688</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2093,7 +2130,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2136,7 +2173,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2150,10 +2187,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45669</v>
+        <v>45468</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2165,8 +2202,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2209,7 +2251,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2223,10 +2265,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45688</v>
+        <v>45396</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2238,8 +2280,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>9.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2282,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2296,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45545</v>
+        <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,8 +2358,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2355,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2369,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45686</v>
+        <v>45593</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2385,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2428,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2442,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45232</v>
+        <v>45520</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2458,7 +2510,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2501,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2515,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44692</v>
+        <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2530,8 +2582,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2574,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2588,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45560</v>
+        <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2609,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2652,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2666,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45104</v>
+        <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2681,8 +2738,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2725,7 +2787,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2739,10 +2801,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44658</v>
+        <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2754,8 +2816,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>9.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2798,7 +2865,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2812,10 +2879,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45588</v>
+        <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2825,6 +2892,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2871,7 +2943,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2885,10 +2957,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45700</v>
+        <v>45545</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2900,13 +2972,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2949,7 +3016,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2963,10 +3030,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45153</v>
+        <v>45660</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2978,13 +3045,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3027,7 +3089,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3041,10 +3103,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>44938</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3056,8 +3118,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3100,7 +3167,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3114,10 +3181,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45840</v>
+        <v>45680</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3129,13 +3196,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3178,7 +3240,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3192,10 +3254,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45840</v>
+        <v>45890</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3207,13 +3269,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3256,7 +3313,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,10 +3327,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45875</v>
+        <v>45453</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3286,7 +3343,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3329,7 +3386,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3343,10 +3400,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45058</v>
+        <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3364,7 +3421,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>14.9</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3407,7 +3464,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3421,10 +3478,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45881</v>
+        <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3437,7 +3494,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>10.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3480,7 +3537,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3494,10 +3551,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>46045</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3509,13 +3566,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3558,7 +3610,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3572,10 +3624,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45890</v>
+        <v>44939</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3587,8 +3639,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3688,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,10 +3702,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45680</v>
+        <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3661,7 +3718,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3704,7 +3761,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3718,10 +3775,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45468</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,13 +3790,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>25.4</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3782,7 +3834,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3796,10 +3848,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44969</v>
+        <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3811,13 +3863,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3860,7 +3907,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3874,10 +3921,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45726</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3890,7 +3937,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3980,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3947,10 +3994,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44938</v>
+        <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3963,7 +4010,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4006,7 +4053,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4020,10 +4067,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4036,7 +4083,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4079,7 +4126,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4089,14 +4136,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45168</v>
+        <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4109,7 +4156,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4152,7 +4199,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4166,10 +4213,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45236</v>
+        <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4181,13 +4228,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4230,7 +4272,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4244,10 +4286,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44900</v>
+        <v>46093</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4259,13 +4301,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4308,7 +4345,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4322,10 +4359,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45226</v>
+        <v>46098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4343,7 +4380,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4386,7 +4423,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4400,10 +4437,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44900</v>
+        <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4416,7 +4453,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4459,7 +4496,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4473,10 +4510,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45681</v>
+        <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4489,7 +4526,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4532,7 +4569,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4546,10 +4583,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45386</v>
+        <v>45168</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4561,13 +4598,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4610,7 +4642,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4624,10 +4656,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45329</v>
+        <v>46111</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4639,8 +4671,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4683,7 +4720,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4697,10 +4734,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46139</v>
+        <v>45711</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4712,13 +4749,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4810,7 @@
         <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4834,7 +4866,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4848,10 +4880,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46140</v>
+        <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4863,13 +4895,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4956,7 @@
         <v>45961</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4990,7 +5017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5004,10 +5031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45957</v>
+        <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5020,7 +5047,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5063,7 +5090,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5077,10 +5104,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46140</v>
+        <v>45968</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5098,7 +5125,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5141,7 +5168,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5155,10 +5182,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46140</v>
+        <v>45058</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5176,7 +5203,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>14.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5219,7 +5246,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5233,10 +5260,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46140</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5248,13 +5275,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5297,7 +5319,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5311,10 +5333,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5332,7 +5354,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5375,7 +5397,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5389,10 +5411,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46140</v>
+        <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5406,11 +5428,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.7</v>
+        <v>14.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5453,7 +5475,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5467,10 +5489,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46141</v>
+        <v>44930</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5482,13 +5504,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5531,7 +5548,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5545,10 +5562,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44747</v>
+        <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5560,8 +5577,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5604,7 +5626,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5618,10 +5640,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45972</v>
+        <v>45818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5634,7 +5656,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5677,7 +5699,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5694,7 +5716,7 @@
         <v>46140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5712,7 +5734,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5755,7 +5777,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5769,10 +5791,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45520</v>
+        <v>45995</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5828,7 +5850,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5838,14 +5860,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45588</v>
+        <v>45226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5857,8 +5879,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5901,7 +5928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5915,10 +5942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5932,11 +5959,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5979,7 +6006,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5993,10 +6020,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45203</v>
+        <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6010,11 +6037,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6057,7 +6084,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6071,10 +6098,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6086,8 +6113,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>9.1</v>
+        <v>3.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6130,7 +6162,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6144,10 +6176,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44939</v>
+        <v>46140</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,11 +6193,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6208,7 +6240,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6222,10 +6254,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45068</v>
+        <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6237,8 +6269,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6281,7 +6318,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6295,10 +6332,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44907</v>
+        <v>46140</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6310,8 +6347,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>16.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6354,7 +6396,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6368,10 +6410,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45995</v>
+        <v>46140</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6383,8 +6425,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>10.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6427,7 +6474,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6437,14 +6484,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>46140</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6462,7 +6509,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6505,7 +6552,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6519,10 +6566,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44938</v>
+        <v>45386</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6534,8 +6581,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6578,7 +6630,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6592,10 +6644,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46000</v>
+        <v>44938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6607,13 +6659,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6703,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6717,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45985</v>
+        <v>46141</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6738,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>14.1</v>
+        <v>5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6781,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6795,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45037</v>
+        <v>46146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6811,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6854,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6868,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46000</v>
+        <v>45028</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6836,13 +6883,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6885,7 +6927,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6899,10 +6941,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45028</v>
+        <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6915,7 +6957,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6958,7 +7000,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6972,10 +7014,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46013</v>
+        <v>45669</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6987,13 +7029,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7036,7 +7073,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7046,14 +7083,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45229</v>
+        <v>44938</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7066,7 +7103,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7109,7 +7146,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7123,10 +7160,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46009</v>
+        <v>45985</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7140,11 +7177,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>14.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7187,7 +7224,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7197,14 +7234,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45988</v>
+        <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7222,7 +7259,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>9.9</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7265,7 +7302,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7279,10 +7316,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45939</v>
+        <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7294,13 +7331,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7343,7 +7375,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7357,10 +7389,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46009</v>
+        <v>45468</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7374,11 +7406,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7421,7 +7453,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7435,10 +7467,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45915</v>
+        <v>45355</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7452,11 +7484,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>10.6</v>
+        <v>5.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7499,7 +7531,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7509,14 +7541,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45635</v>
+        <v>46169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7530,11 +7562,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7577,7 +7609,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7591,10 +7623,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46045</v>
+        <v>44536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7607,7 +7639,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7650,7 +7682,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7664,10 +7696,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46048</v>
+        <v>46170</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7680,7 +7712,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>10.8</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7723,7 +7755,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7737,10 +7769,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46057</v>
+        <v>45840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7752,8 +7784,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7796,7 +7833,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7810,10 +7847,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46059</v>
+        <v>45153</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7825,8 +7862,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7869,7 +7911,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7879,14 +7921,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46169</v>
+        <v>46181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7898,13 +7940,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7947,7 +7984,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7961,10 +7998,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46059</v>
+        <v>45104</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7977,7 +8014,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8020,7 +8057,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8034,10 +8071,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46059</v>
+        <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8050,7 +8087,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8093,7 +8130,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8107,10 +8144,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44938</v>
+        <v>45635</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8122,8 +8159,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8166,7 +8208,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8180,10 +8222,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44930</v>
+        <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8196,7 +8238,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8239,7 +8281,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8253,10 +8295,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46170</v>
+        <v>45401</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8269,7 +8311,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8312,7 +8354,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8326,10 +8368,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46093</v>
+        <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8341,8 +8383,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8385,7 +8432,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8399,10 +8446,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46098</v>
+        <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8414,13 +8461,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8463,7 +8505,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8477,10 +8519,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46100</v>
+        <v>46195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8492,8 +8534,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>23.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8536,7 +8583,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8550,10 +8597,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>45700</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8565,8 +8612,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8609,7 +8661,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8623,10 +8675,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46181</v>
+        <v>46196</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8639,7 +8691,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8682,7 +8734,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8696,10 +8748,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46111</v>
+        <v>45681</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8711,13 +8763,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8760,7 +8807,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8774,10 +8821,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44938</v>
+        <v>45072</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8789,13 +8836,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8838,7 +8880,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8852,10 +8894,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46128</v>
+        <v>45614</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8867,13 +8909,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>14.1</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8916,7 +8953,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8930,10 +8967,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45593</v>
+        <v>46203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8945,8 +8982,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8989,7 +9031,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9003,10 +9045,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46195</v>
+        <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9018,13 +9060,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>23.6</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9067,7 +9104,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9081,10 +9118,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9096,8 +9133,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9140,7 +9182,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9150,14 +9192,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45112</v>
+        <v>46209</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9169,8 +9211,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9213,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9227,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45614</v>
+        <v>45203</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9242,8 +9289,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9286,7 +9338,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9300,10 +9352,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46203</v>
+        <v>45708</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9315,13 +9367,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9364,7 +9411,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9378,10 +9425,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46203</v>
+        <v>45560</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9399,7 +9446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9442,7 +9489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9452,14 +9499,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45372</v>
+        <v>46199</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9473,11 +9520,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9520,7 +9567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9534,10 +9581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44728</v>
+        <v>45686</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9550,7 +9597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9593,7 +9640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9607,10 +9654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45708</v>
+        <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9622,8 +9669,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9666,7 +9718,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9676,14 +9728,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46209</v>
+        <v>46255</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9697,11 +9749,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>24.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9744,7 +9796,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9758,10 +9810,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46255</v>
+        <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9779,7 +9831,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>24.1</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9874,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9832,14 +9884,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46199</v>
+        <v>46261</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9853,11 +9905,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9900,7 +9952,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9914,10 +9966,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45174</v>
+        <v>46205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9929,13 +9981,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>51.6</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9978,7 +10025,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9988,14 +10035,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45468</v>
+        <v>45229</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10007,13 +10054,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10056,7 +10098,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10070,10 +10112,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46261</v>
+        <v>46220</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10091,7 +10133,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10134,7 +10176,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10148,10 +10190,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46220</v>
+        <v>46265</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10169,7 +10211,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10212,7 +10254,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10226,10 +10268,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45711</v>
+        <v>45468</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10241,8 +10283,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>25.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10285,7 +10332,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10299,10 +10346,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46205</v>
+        <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10315,7 +10362,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10358,7 +10405,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10372,10 +10419,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10389,11 +10436,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10436,7 +10483,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10450,10 +10497,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45174</v>
+        <v>46227</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10471,7 +10518,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10514,7 +10561,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10531,7 +10578,7 @@
         <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10549,7 +10596,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10592,7 +10639,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10606,10 +10653,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46268</v>
+        <v>45372</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10623,11 +10670,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10670,7 +10717,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10684,10 +10731,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45204</v>
+        <v>46232</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10699,13 +10746,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10748,7 +10790,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10762,10 +10804,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46227</v>
+        <v>45037</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10777,13 +10819,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10826,7 +10863,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10840,10 +10877,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44897</v>
+        <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10856,7 +10893,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10899,7 +10936,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10913,10 +10950,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45163</v>
+        <v>44969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10930,11 +10967,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10977,7 +11014,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10991,10 +11028,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46232</v>
+        <v>46281</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11006,8 +11043,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>35.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11050,7 +11092,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11064,10 +11106,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44747</v>
+        <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11079,8 +11121,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11123,7 +11170,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11137,10 +11184,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46281</v>
+        <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11152,13 +11199,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>35.1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11201,7 +11243,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11215,10 +11257,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45614</v>
+        <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11231,7 +11273,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11274,7 +11316,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11288,10 +11330,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45453</v>
+        <v>44938</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11304,7 +11346,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11347,7 +11389,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11361,10 +11403,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45146</v>
+        <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11376,13 +11418,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11425,7 +11462,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11439,10 +11476,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45615</v>
+        <v>46289</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11454,8 +11491,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>28.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11498,7 +11540,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11512,10 +11554,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46244</v>
+        <v>46290</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11527,8 +11569,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>19.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11571,7 +11618,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11585,10 +11632,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45596</v>
+        <v>46258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11600,13 +11647,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11649,7 +11691,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11663,10 +11705,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46289</v>
+        <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11680,11 +11722,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>28.9</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11727,7 +11769,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11741,10 +11783,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45396</v>
+        <v>44692</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11756,13 +11798,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11805,7 +11842,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11819,10 +11856,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45660</v>
+        <v>44900</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11835,7 +11872,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11878,7 +11915,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11892,10 +11929,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46258</v>
+        <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11908,7 +11945,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11951,7 +11988,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11965,10 +12002,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46280</v>
+        <v>45390</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11981,7 +12018,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12024,7 +12061,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12038,10 +12075,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45799</v>
+        <v>44658</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12053,13 +12090,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12102,7 +12134,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12116,10 +12148,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45818</v>
+        <v>45174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12131,8 +12163,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>51.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12175,7 +12212,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12189,10 +12226,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45468</v>
+        <v>45163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12206,11 +12243,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12253,7 +12290,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12267,10 +12304,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45355</v>
+        <v>45615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12282,13 +12319,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12331,24 +12363,24 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45247</v>
+        <v>45146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12362,11 +12394,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12409,24 +12441,24 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45247</v>
+        <v>45596</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12440,11 +12472,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>20.6</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12487,7 +12519,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>S 4139-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12501,10 +12533,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45716</v>
+        <v>45247</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12522,7 +12554,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>33.7</v>
+        <v>20</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12565,153 +12597,309 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
+          <t>S 4141-2023</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>45247</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159" ht="15" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>S 733-2025</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>S 98-2026</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D158" s="1" t="n">
+      <c r="D160" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E158" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
+      <c r="E160" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I158" t="n">
+      <c r="I160" t="n">
         <v>72.5</v>
       </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>S 1683-2026</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D159" s="1" t="n">
+      <c r="D161" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="E159" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
+      <c r="E161" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
         <v>37.1</v>
       </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="2" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>46290</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44797</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44490</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44512</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44788</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44841</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44841</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45329</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45688</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45468</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45396</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45593</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45520</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45545</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45660</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44938</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45680</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45890</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45453</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>46045</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44939</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>46093</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>46098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45168</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>46111</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45711</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>45961</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45968</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45058</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44930</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>46140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45995</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>46140</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>46140</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>46140</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>46140</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>46140</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45386</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>46141</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>46146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45028</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>45669</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44938</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>45985</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45468</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45355</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>46169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>44536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>46170</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45153</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>46181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45104</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45635</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45401</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>46195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45700</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46196</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45681</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45072</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45614</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>46203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>46203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>46209</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45203</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45708</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45560</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>46199</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45686</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>46255</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>46261</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45229</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>46220</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>46265</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45468</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46227</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45372</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>46232</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45037</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46281</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44938</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>46289</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>46290</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44692</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44900</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45390</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44658</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45596</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45247</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45247</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45716</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>46182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 39769-2026</t>
+          <t>A 37716-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46290</v>
+        <v>45881</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1064,13 +1064,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>10.9</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1097,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1106,334 +1101,371 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 37716-2025 artfynd.xlsx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 37716-2025 karta.png", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 37716-2025 georefererad karta.tif", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 37716-2025 FSC-klagomål.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 37716-2025 FSC-klagomål mail.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 37716-2025 tillsynsbegäran.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 37716-2025 tillsynsbegäran mail.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 39769-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 39769-2026 artfynd.xlsx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 39769-2026 karta.png", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 39769-2026 georefererad karta.tif", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 39769-2026 FSC-klagomål.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 39769-2026 FSC-klagomål mail.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 39769-2026 tillsynsbegäran.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 39769-2026 tillsynsbegäran mail.docx", "A 39769-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 57209-2022</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>44895</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>6.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 21111-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Korallblylav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 35089-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44797</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr"/>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59084-2021</t>
+          <t>A 35089-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1447,10 +1479,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44490</v>
+        <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1462,13 +1494,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1511,7 +1538,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 64815-2021</t>
+          <t>A 59084-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1525,10 +1552,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44512</v>
+        <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1540,8 +1567,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1584,7 +1616,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35084-2022</t>
+          <t>A 64815-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1598,10 +1630,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44797</v>
+        <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1614,7 +1646,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1657,7 +1689,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33307-2022</t>
+          <t>A 35084-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1667,14 +1699,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44788</v>
+        <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1687,7 +1719,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1730,7 +1762,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44802-2022</t>
+          <t>A 33307-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1740,14 +1772,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44841</v>
+        <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1760,7 +1792,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1803,7 +1835,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 64814-2021</t>
+          <t>A 44802-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1817,10 +1849,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44512</v>
+        <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1865,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1876,7 +1908,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57734-2021</t>
+          <t>A 64814-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1890,10 +1922,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44484</v>
+        <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1905,13 +1937,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1954,7 +1981,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44783-2022</t>
+          <t>A 57734-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1968,10 +1995,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44841</v>
+        <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,8 +2010,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2027,7 +2059,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 44783-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2041,10 +2073,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45329</v>
+        <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2057,7 +2089,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2100,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2114,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45688</v>
+        <v>45329</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2130,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2173,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2187,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45468</v>
+        <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2202,13 +2234,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2251,7 +2278,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2265,10 +2292,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45396</v>
+        <v>45468</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2313,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2356,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2370,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46013</v>
+        <v>45396</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2360,11 +2387,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2434,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2448,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45593</v>
+        <v>46013</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2436,8 +2463,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2512,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2526,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45520</v>
+        <v>45593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2542,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2553,7 +2585,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2599,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46009</v>
+        <v>45520</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,13 +2614,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2658,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2648,7 +2675,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2693,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2736,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2750,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45915</v>
+        <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2740,11 +2767,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2787,7 +2814,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2801,10 +2828,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45988</v>
+        <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2822,7 +2849,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2865,7 +2892,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2879,10 +2906,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45939</v>
+        <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2900,7 +2927,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>9.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2943,7 +2970,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2957,10 +2984,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45545</v>
+        <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2972,8 +2999,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3016,7 +3048,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3030,10 +3062,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45660</v>
+        <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3046,7 +3078,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3089,7 +3121,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3103,10 +3135,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44938</v>
+        <v>45660</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3118,13 +3150,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3167,7 +3194,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3181,10 +3208,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45680</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3196,8 +3223,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3240,7 +3272,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3254,10 +3286,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45890</v>
+        <v>45680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3270,7 +3302,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3313,7 +3345,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3327,10 +3359,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45453</v>
+        <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3343,7 +3375,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3386,7 +3418,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3400,10 +3432,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45799</v>
+        <v>45453</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3415,13 +3447,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3464,7 +3491,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3478,10 +3505,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46048</v>
+        <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3493,8 +3520,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3537,7 +3569,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3551,10 +3583,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3567,7 +3599,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>10.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3610,7 +3642,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3624,10 +3656,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44939</v>
+        <v>46045</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3639,13 +3671,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3688,7 +3715,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3702,10 +3729,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46057</v>
+        <v>44939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3715,6 +3742,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3761,7 +3793,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3775,10 +3807,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>46057</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3791,7 +3823,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3834,7 +3866,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3848,10 +3880,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46059</v>
+        <v>44897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3864,7 +3896,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3907,7 +3939,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3924,7 +3956,7 @@
         <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3937,7 +3969,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3980,7 +4012,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3997,7 +4029,7 @@
         <v>46059</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4010,7 +4042,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4053,7 +4085,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4067,10 +4099,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45232</v>
+        <v>46059</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4083,7 +4115,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4126,7 +4158,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4136,14 +4168,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45588</v>
+        <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4156,7 +4188,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4199,7 +4231,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4209,14 +4241,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
         <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4229,7 +4261,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4272,7 +4304,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4286,10 +4318,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46093</v>
+        <v>45588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4302,7 +4334,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4345,7 +4377,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4359,10 +4391,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4374,13 +4406,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4423,7 +4450,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4437,10 +4464,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4452,8 +4479,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4496,7 +4528,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4510,10 +4542,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45614</v>
+        <v>46100</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4526,7 +4558,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4569,7 +4601,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4583,10 +4615,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45168</v>
+        <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4599,7 +4631,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4642,7 +4674,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4656,10 +4688,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46111</v>
+        <v>45168</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4671,13 +4703,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4720,7 +4747,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4734,10 +4761,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45711</v>
+        <v>46111</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4749,8 +4776,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4793,7 +4825,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4807,10 +4839,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>45711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4823,7 +4855,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4866,7 +4898,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4883,7 +4915,7 @@
         <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4896,7 +4928,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4939,7 +4971,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4953,10 +4985,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45961</v>
+        <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4968,13 +5000,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5017,7 +5044,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5031,10 +5058,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44747</v>
+        <v>45961</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5046,8 +5073,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5090,7 +5122,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5104,10 +5136,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45968</v>
+        <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5119,13 +5151,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5168,7 +5195,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5182,10 +5209,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45058</v>
+        <v>45968</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5203,7 +5230,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>14.9</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5246,7 +5273,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5260,10 +5287,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>45058</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5275,8 +5302,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>14.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5319,7 +5351,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5333,10 +5365,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45975</v>
+        <v>45972</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5348,13 +5380,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5397,7 +5424,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5411,10 +5438,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46128</v>
+        <v>45975</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5428,11 +5455,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>14.1</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5475,7 +5502,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5489,10 +5516,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44930</v>
+        <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5504,8 +5531,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>14.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5548,7 +5580,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5562,10 +5594,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45204</v>
+        <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5577,13 +5609,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5626,7 +5653,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5640,10 +5667,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45818</v>
+        <v>45204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5655,8 +5682,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5699,7 +5731,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5713,10 +5745,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46140</v>
+        <v>45818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5728,13 +5760,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5777,7 +5804,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5791,10 +5818,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45995</v>
+        <v>46140</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5806,8 +5833,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5850,7 +5882,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5864,10 +5896,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45226</v>
+        <v>45995</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5879,13 +5911,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5928,7 +5955,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5942,10 +5969,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46000</v>
+        <v>45226</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5959,11 +5986,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6006,7 +6033,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6023,7 +6050,7 @@
         <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6041,7 +6068,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6084,7 +6111,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6098,10 +6125,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46140</v>
+        <v>46000</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6115,11 +6142,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6162,7 +6189,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6179,7 +6206,7 @@
         <v>46140</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6197,7 +6224,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6240,7 +6267,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6254,10 +6281,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6271,11 +6298,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6318,7 +6345,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6332,10 +6359,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6349,11 +6376,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>16.1</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6396,7 +6423,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6413,7 +6440,7 @@
         <v>46140</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6458,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.7</v>
+        <v>16.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6474,7 +6501,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6491,7 +6518,7 @@
         <v>46140</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6509,7 +6536,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>10.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6552,7 +6579,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6566,10 +6593,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45386</v>
+        <v>46140</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6583,11 +6610,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6630,7 +6657,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6644,10 +6671,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44938</v>
+        <v>45386</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6659,8 +6686,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6703,7 +6735,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6717,10 +6749,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46141</v>
+        <v>44938</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6732,13 +6764,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6781,7 +6808,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6795,10 +6822,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46146</v>
+        <v>46141</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6810,8 +6837,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6854,7 +6886,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6868,10 +6900,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45028</v>
+        <v>46146</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6884,7 +6916,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6927,7 +6959,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6941,10 +6973,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45203</v>
+        <v>45028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6957,7 +6989,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7000,7 +7032,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7014,10 +7046,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45669</v>
+        <v>45203</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7030,7 +7062,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7073,7 +7105,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7087,10 +7119,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44938</v>
+        <v>45669</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7103,7 +7135,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7146,7 +7178,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7160,10 +7192,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45985</v>
+        <v>44938</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7175,13 +7207,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>14.1</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7224,7 +7251,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7234,14 +7261,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46002</v>
+        <v>45985</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7259,7 +7286,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>14.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7302,7 +7329,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7312,14 +7339,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45112</v>
+        <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7331,8 +7358,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7375,7 +7407,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7389,10 +7421,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45468</v>
+        <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7404,13 +7436,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7453,7 +7480,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7467,10 +7494,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45355</v>
+        <v>45468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7484,11 +7511,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7531,7 +7558,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7541,14 +7568,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46169</v>
+        <v>45355</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7566,7 +7593,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7609,7 +7636,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7619,14 +7646,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44536</v>
+        <v>46169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7638,8 +7665,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7682,7 +7714,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7696,10 +7728,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46170</v>
+        <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7712,7 +7744,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7755,7 +7787,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7769,10 +7801,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45840</v>
+        <v>46170</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7784,13 +7816,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7833,7 +7860,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,10 +7874,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45153</v>
+        <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7864,11 +7891,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7911,7 +7938,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7925,10 +7952,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46181</v>
+        <v>45153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7940,8 +7967,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7984,7 +8016,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7998,10 +8030,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45104</v>
+        <v>46181</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8014,7 +8046,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8057,7 +8089,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8071,10 +8103,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46181</v>
+        <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8087,7 +8119,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8130,7 +8162,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8144,10 +8176,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45635</v>
+        <v>46181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8159,13 +8191,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8208,7 +8235,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8222,10 +8249,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45068</v>
+        <v>45635</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8237,8 +8264,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8281,7 +8313,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8295,10 +8327,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45401</v>
+        <v>45068</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8311,7 +8343,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8354,7 +8386,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8368,10 +8400,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45840</v>
+        <v>45401</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8383,13 +8415,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8432,7 +8459,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8446,10 +8473,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45875</v>
+        <v>45840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8461,8 +8488,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8505,7 +8537,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8519,10 +8551,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46195</v>
+        <v>45875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8534,13 +8566,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>23.6</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8583,7 +8610,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8597,10 +8624,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45700</v>
+        <v>46195</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8614,11 +8641,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>23.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8661,7 +8688,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8675,10 +8702,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46196</v>
+        <v>45700</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8690,8 +8717,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8734,7 +8766,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8748,10 +8780,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45681</v>
+        <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8796,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8807,7 +8839,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8821,10 +8853,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45072</v>
+        <v>45681</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8869,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8880,7 +8912,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8894,10 +8926,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45614</v>
+        <v>45072</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8942,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8953,7 +8985,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8967,10 +8999,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46203</v>
+        <v>45614</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8982,13 +9014,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9031,7 +9058,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37716-2025</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9045,10 +9072,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45881</v>
+        <v>46203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9060,8 +9087,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9121,7 +9153,7 @@
         <v>46203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9199,7 +9231,7 @@
         <v>46209</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9277,7 +9309,7 @@
         <v>45203</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9355,7 +9387,7 @@
         <v>45708</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9428,7 +9460,7 @@
         <v>45560</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9506,7 +9538,7 @@
         <v>46199</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9616,7 @@
         <v>45686</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9689,7 @@
         <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9735,7 +9767,7 @@
         <v>46255</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9813,7 +9845,7 @@
         <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9891,7 +9923,7 @@
         <v>46261</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9969,7 +10001,7 @@
         <v>46205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10042,7 +10074,7 @@
         <v>45229</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10115,7 +10147,7 @@
         <v>46220</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10193,7 +10225,7 @@
         <v>46265</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10271,7 +10303,7 @@
         <v>45468</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10349,7 +10381,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10422,7 +10454,7 @@
         <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10500,7 +10532,7 @@
         <v>46227</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10578,7 +10610,7 @@
         <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10656,7 +10688,7 @@
         <v>45372</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10734,7 +10766,7 @@
         <v>46232</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10807,7 +10839,7 @@
         <v>45037</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10880,7 +10912,7 @@
         <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10953,7 +10985,7 @@
         <v>44969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11031,7 +11063,7 @@
         <v>46281</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11109,7 +11141,7 @@
         <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11187,7 +11219,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11260,7 +11292,7 @@
         <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11333,7 +11365,7 @@
         <v>44938</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11406,7 +11438,7 @@
         <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11479,7 +11511,7 @@
         <v>46289</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11557,7 +11589,7 @@
         <v>46290</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11635,7 +11667,7 @@
         <v>46258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11708,7 +11740,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11786,7 +11818,7 @@
         <v>44692</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11859,7 +11891,7 @@
         <v>44900</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11932,7 +11964,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12005,7 +12037,7 @@
         <v>45390</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12078,7 +12110,7 @@
         <v>44658</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12151,7 +12183,7 @@
         <v>45174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12229,7 +12261,7 @@
         <v>45163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12307,7 +12339,7 @@
         <v>45615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12380,7 +12412,7 @@
         <v>45146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12458,7 +12490,7 @@
         <v>45596</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12536,7 +12568,7 @@
         <v>45247</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12614,7 +12646,7 @@
         <v>45247</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12692,7 +12724,7 @@
         <v>45716</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12770,7 +12802,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12848,7 +12880,7 @@
         <v>46182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE161"/>
+  <dimension ref="A1:AE165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43407-2022</t>
+          <t>A 21111-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44834</v>
+        <v>45777</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,19 +845,14 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -887,151 +882,156 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 43407-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Orre</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45881</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 39769-2026</t>
+          <t>A 57209-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46290</v>
+        <v>44895</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>10.9</v>
+        <v>6.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1215,253 +1215,253 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Knölspindel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39769-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 39769-2026 artfynd.xlsx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 39769-2026 karta.png", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 39769-2026 georefererad karta.tif", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 39769-2026 FSC-klagomål.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 39769-2026 FSC-klagomål mail.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 39769-2026 tillsynsbegäran.docx", "A 39769-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 39769-2026 tillsynsbegäran mail.docx", "A 39769-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 57209-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knölspindel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45329</v>
+        <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45688</v>
+        <v>44536</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45468</v>
+        <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2307,13 +2307,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2356,7 +2351,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45396</v>
+        <v>45669</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2385,13 +2380,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2434,7 +2424,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2448,10 +2438,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46013</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2465,11 +2455,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2512,7 +2502,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45593</v>
+        <v>45396</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2541,8 +2531,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2585,7 +2580,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2599,10 +2594,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45520</v>
+        <v>45660</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2615,7 +2610,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2658,7 +2653,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2672,10 +2667,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46009</v>
+        <v>45688</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2687,13 +2682,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2736,7 +2726,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2750,10 +2740,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46009</v>
+        <v>45890</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2765,13 +2755,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2814,7 +2799,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2828,10 +2813,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45915</v>
+        <v>45799</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2849,7 +2834,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.6</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2892,7 +2877,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2906,10 +2891,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45988</v>
+        <v>45545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2921,13 +2906,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>9.9</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2970,7 +2950,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2984,10 +2964,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45939</v>
+        <v>45818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2999,13 +2979,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3048,7 +3023,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3062,10 +3037,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45545</v>
+        <v>46013</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3077,8 +3052,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3121,7 +3101,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3135,10 +3115,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45660</v>
+        <v>45686</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3151,7 +3131,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3194,7 +3174,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3208,10 +3188,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>45232</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3223,13 +3203,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3272,7 +3247,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3286,10 +3261,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45680</v>
+        <v>44692</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3302,7 +3277,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3345,7 +3320,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,10 +3334,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45890</v>
+        <v>45468</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3374,8 +3349,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3418,7 +3398,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3432,10 +3412,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45453</v>
+        <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3447,8 +3427,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3491,7 +3476,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3505,10 +3490,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45799</v>
+        <v>45988</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3526,7 +3511,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>9.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3569,7 +3554,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3583,10 +3568,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46048</v>
+        <v>45560</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3598,8 +3583,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3642,7 +3632,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3656,10 +3646,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46045</v>
+        <v>45939</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3671,8 +3661,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3715,7 +3710,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44939</v>
+        <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3746,11 +3741,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3793,7 +3788,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3807,10 +3802,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46057</v>
+        <v>45104</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3823,7 +3818,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3866,7 +3861,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3880,10 +3875,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44897</v>
+        <v>45915</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3895,8 +3890,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>10.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46059</v>
+        <v>44658</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46059</v>
+        <v>45355</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4041,8 +4041,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4085,7 +4090,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4099,10 +4104,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46059</v>
+        <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4115,7 +4120,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4158,7 +4163,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45232</v>
+        <v>45957</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4188,7 +4193,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4231,7 +4236,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4241,14 +4246,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45588</v>
+        <v>45840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4260,8 +4265,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4304,7 +4314,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4318,10 +4328,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45588</v>
+        <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4333,8 +4343,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4377,7 +4392,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4391,10 +4406,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46093</v>
+        <v>45961</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4406,8 +4421,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4450,7 +4470,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4464,10 +4484,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46098</v>
+        <v>45957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4479,13 +4499,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4528,7 +4543,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4542,10 +4557,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46100</v>
+        <v>45875</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4558,7 +4573,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4601,7 +4616,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4615,10 +4630,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45614</v>
+        <v>45700</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4630,8 +4645,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4674,7 +4694,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4688,10 +4708,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45168</v>
+        <v>45968</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4703,8 +4723,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4747,7 +4772,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4761,10 +4786,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46111</v>
+        <v>45680</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4776,13 +4801,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4825,7 +4845,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4839,10 +4859,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45711</v>
+        <v>45972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4855,7 +4875,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4898,7 +4918,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4912,10 +4932,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45957</v>
+        <v>45153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4925,6 +4945,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4971,7 +4996,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4985,10 +5010,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5000,8 +5025,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5044,7 +5074,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5058,10 +5088,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45961</v>
+        <v>46045</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5073,13 +5103,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5122,7 +5147,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5136,10 +5161,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44747</v>
+        <v>45401</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5152,7 +5177,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5195,7 +5220,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5209,10 +5234,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45968</v>
+        <v>45058</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5230,7 +5255,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>14.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5273,7 +5298,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5287,10 +5312,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45058</v>
+        <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5302,13 +5327,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>14.9</v>
+        <v>10.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5351,7 +5371,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5365,10 +5385,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45972</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5380,8 +5400,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5424,7 +5449,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5438,10 +5463,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45975</v>
+        <v>45995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5453,13 +5478,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5502,7 +5522,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5516,10 +5536,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46128</v>
+        <v>45468</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5533,11 +5553,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>14.1</v>
+        <v>25.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5580,7 +5600,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5594,10 +5614,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44930</v>
+        <v>46000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5609,8 +5629,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5653,7 +5678,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5667,10 +5692,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45204</v>
+        <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5684,11 +5709,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5731,7 +5756,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5745,10 +5770,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45818</v>
+        <v>46057</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5761,7 +5786,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5804,7 +5829,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5818,10 +5843,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46140</v>
+        <v>44969</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5839,7 +5864,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5882,7 +5907,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5896,10 +5921,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45995</v>
+        <v>46059</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5955,7 +5980,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5969,10 +5994,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45226</v>
+        <v>46059</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5984,13 +6009,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6033,7 +6053,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6047,10 +6067,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46000</v>
+        <v>46059</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6062,13 +6082,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6111,7 +6126,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6125,10 +6140,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46000</v>
+        <v>45726</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6140,13 +6155,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6189,7 +6199,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6203,10 +6213,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46140</v>
+        <v>45390</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6218,13 +6228,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6267,7 +6272,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6281,10 +6286,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46140</v>
+        <v>45168</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6296,13 +6301,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46139</v>
+        <v>45236</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6376,11 +6376,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46140</v>
+        <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6454,11 +6454,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>16.1</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46140</v>
+        <v>44900</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6530,13 +6530,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>10.7</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6579,7 +6574,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6593,10 +6588,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46140</v>
+        <v>46093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6608,13 +6603,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6657,7 +6647,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6671,10 +6661,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45386</v>
+        <v>45681</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6686,13 +6676,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6735,7 +6720,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6749,10 +6734,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44938</v>
+        <v>46098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6764,8 +6749,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6808,7 +6798,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6822,10 +6812,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46141</v>
+        <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6837,13 +6827,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6886,7 +6871,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6900,10 +6885,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46146</v>
+        <v>45329</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6916,7 +6901,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6959,7 +6944,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6973,10 +6958,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45028</v>
+        <v>46111</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6988,8 +6973,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7032,7 +7022,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7046,10 +7036,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45203</v>
+        <v>44747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7062,7 +7052,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7105,7 +7095,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7119,10 +7109,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45669</v>
+        <v>45520</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7135,7 +7125,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7178,7 +7168,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7188,14 +7178,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44938</v>
+        <v>45588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7208,7 +7198,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7251,7 +7241,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7265,10 +7255,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45985</v>
+        <v>45203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,11 +7272,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>14.1</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7329,7 +7319,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7339,14 +7329,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46002</v>
+        <v>46128</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7360,11 +7350,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>14.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7407,7 +7397,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7421,10 +7411,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45112</v>
+        <v>44939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7436,8 +7426,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7480,7 +7475,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7494,10 +7489,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45468</v>
+        <v>45068</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7509,13 +7504,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7558,7 +7548,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7572,10 +7562,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45355</v>
+        <v>44907</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7587,13 +7577,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7636,7 +7621,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7646,14 +7631,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46169</v>
+        <v>45037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7665,13 +7650,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7714,7 +7694,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7728,10 +7708,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44536</v>
+        <v>45028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7744,7 +7724,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7787,7 +7767,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7801,10 +7781,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46170</v>
+        <v>44938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7817,7 +7797,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7860,7 +7840,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7874,10 +7854,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45840</v>
+        <v>45226</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7895,7 +7875,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7938,7 +7918,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7952,10 +7932,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45153</v>
+        <v>45386</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7973,7 +7953,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8016,7 +7996,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8026,14 +8006,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46181</v>
+        <v>45229</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8046,7 +8026,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8089,7 +8069,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8103,10 +8083,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45104</v>
+        <v>46139</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8118,8 +8098,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8162,7 +8147,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8176,10 +8161,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46181</v>
+        <v>46140</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8191,8 +8176,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>16.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8235,7 +8225,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8249,10 +8239,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45635</v>
+        <v>46140</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8270,7 +8260,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8313,7 +8303,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8327,10 +8317,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45068</v>
+        <v>46140</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8342,8 +8332,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8386,7 +8381,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8400,10 +8395,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45401</v>
+        <v>46140</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8415,8 +8410,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45840</v>
+        <v>45635</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45875</v>
+        <v>46140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8566,8 +8566,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>10.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8610,7 +8615,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8624,10 +8629,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46195</v>
+        <v>46141</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8645,7 +8650,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>23.6</v>
+        <v>5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8688,7 +8693,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8702,10 +8707,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45700</v>
+        <v>46140</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8719,11 +8724,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8766,7 +8771,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8780,10 +8785,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46196</v>
+        <v>46146</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8796,7 +8801,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8839,7 +8844,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8849,14 +8854,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45681</v>
+        <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8868,8 +8873,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8912,7 +8922,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8926,10 +8936,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45072</v>
+        <v>44938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8942,7 +8952,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8985,7 +8995,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8999,10 +9009,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45614</v>
+        <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9014,8 +9024,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>14.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9058,7 +9073,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9072,10 +9087,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46203</v>
+        <v>44938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9087,13 +9102,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9136,7 +9146,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9150,10 +9160,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46203</v>
+        <v>44930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9165,13 +9175,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9214,7 +9219,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9228,10 +9233,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46209</v>
+        <v>46169</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9249,7 +9254,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9292,7 +9297,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9306,10 +9311,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45203</v>
+        <v>46170</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9321,13 +9326,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45708</v>
+        <v>44938</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9399,8 +9399,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9443,7 +9448,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9457,10 +9462,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45560</v>
+        <v>46181</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9472,13 +9477,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9521,7 +9521,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46199</v>
+        <v>45593</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9550,13 +9550,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9599,7 +9594,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9613,10 +9608,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45686</v>
+        <v>46181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9629,7 +9624,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9672,7 +9667,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9686,10 +9681,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45236</v>
+        <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9701,13 +9696,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9750,7 +9740,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9764,10 +9754,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46255</v>
+        <v>45614</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9779,13 +9769,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>24.1</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9828,7 +9813,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9842,10 +9827,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45174</v>
+        <v>46195</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9863,7 +9848,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>23.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9906,7 +9891,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9920,10 +9905,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46261</v>
+        <v>46196</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9935,13 +9920,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9984,7 +9964,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9998,10 +9978,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46205</v>
+        <v>45372</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10013,8 +9993,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10057,7 +10042,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10067,14 +10052,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45229</v>
+        <v>44728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10087,7 +10072,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10130,7 +10115,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10144,10 +10129,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46220</v>
+        <v>45708</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10159,13 +10144,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10208,7 +10188,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10222,10 +10202,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10243,7 +10223,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10286,7 +10266,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10300,10 +10280,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45468</v>
+        <v>46203</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10317,11 +10297,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>25.4</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10364,7 +10344,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10374,14 +10354,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45726</v>
+        <v>46209</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10393,8 +10373,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10437,7 +10422,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10451,10 +10436,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10468,11 +10453,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.9</v>
+        <v>24.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10515,7 +10500,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10525,14 +10510,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46227</v>
+        <v>46199</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10546,11 +10531,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10593,7 +10578,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10607,10 +10592,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46268</v>
+        <v>45174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10624,11 +10609,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.6</v>
+        <v>51.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10671,7 +10656,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10685,10 +10670,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45372</v>
+        <v>45468</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10706,7 +10691,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10734,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10748,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46232</v>
+        <v>45711</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10779,7 +10764,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10822,7 +10807,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10836,10 +10821,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45037</v>
+        <v>46261</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10851,8 +10836,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10895,7 +10885,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10909,10 +10899,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44747</v>
+        <v>45174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10924,8 +10914,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10968,7 +10963,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10982,10 +10977,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44969</v>
+        <v>46220</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11003,7 +10998,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11046,7 +11041,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11060,10 +11055,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46281</v>
+        <v>46205</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11075,13 +11070,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>35.1</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11124,7 +11114,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11138,10 +11128,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44900</v>
+        <v>46265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11155,11 +11145,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11202,7 +11192,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11216,10 +11206,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44728</v>
+        <v>45204</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11231,8 +11221,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11275,7 +11270,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11289,10 +11284,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46244</v>
+        <v>46268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11304,8 +11299,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11348,7 +11348,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44938</v>
+        <v>44897</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11421,7 +11421,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11450,8 +11450,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11494,7 +11499,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11508,10 +11513,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46289</v>
+        <v>45163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11525,11 +11530,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>28.9</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11572,7 +11577,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 39804-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11586,10 +11591,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46290</v>
+        <v>46227</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11607,7 +11612,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>19.5</v>
+        <v>2.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11650,7 +11655,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11664,10 +11669,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46258</v>
+        <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11680,7 +11685,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11723,7 +11728,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11737,10 +11742,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45007</v>
+        <v>46232</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11752,13 +11757,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11801,7 +11801,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44692</v>
+        <v>45614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11874,7 +11874,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44900</v>
+        <v>45453</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44907</v>
+        <v>46281</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11976,8 +11976,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>35.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12020,7 +12025,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12034,10 +12039,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45390</v>
+        <v>45146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12049,8 +12054,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12093,7 +12103,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12107,10 +12117,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44658</v>
+        <v>45615</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12123,7 +12133,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12166,7 +12176,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12180,10 +12190,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45174</v>
+        <v>46244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12195,13 +12205,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>51.6</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12244,7 +12249,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12258,10 +12263,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45163</v>
+        <v>46289</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12275,11 +12280,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>28.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12322,7 +12327,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12336,10 +12341,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45615</v>
+        <v>46258</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12352,7 +12357,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12395,7 +12400,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12409,10 +12414,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45146</v>
+        <v>46280</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12424,13 +12429,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12473,7 +12473,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 40058-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45596</v>
+        <v>46293</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12551,24 +12551,24 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S 4139-2023</t>
+          <t>A 39988-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45247</v>
+        <v>46293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12629,24 +12629,24 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S 4141-2023</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45247</v>
+        <v>46290</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12660,11 +12660,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12707,24 +12707,24 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S 733-2025</t>
+          <t>A 40009-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45716</v>
+        <v>46293</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>33.7</v>
+        <v>10.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12785,153 +12785,465 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
+          <t>A 40098-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161" ht="15" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>S 4139-2023</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>45247</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>20</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>S 4141-2023</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>45247</v>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>S 733-2025</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>S 98-2026</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D160" s="1" t="n">
+      <c r="D164" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E160" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
+      <c r="E164" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I160" t="n">
+      <c r="I164" t="n">
         <v>72.5</v>
       </c>
-      <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>S 1683-2026</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D161" s="1" t="n">
+      <c r="D165" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="E161" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
+      <c r="E165" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
         <v>37.1</v>
       </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" s="2" t="inlineStr"/>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 21111-2025</t>
+          <t>A 43407-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45777</v>
+        <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,14 +845,19 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -882,156 +887,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Korallblylav</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 43407-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45881</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57209-2022</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44895</v>
+        <v>45197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,13 +1169,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1184,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1202,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1211,147 +1206,152 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45072</v>
+        <v>45329</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44536</v>
+        <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45203</v>
+        <v>45468</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2307,8 +2307,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2351,7 +2356,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45669</v>
+        <v>45596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2380,8 +2385,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2424,7 +2434,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2438,10 +2448,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>46013</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2455,11 +2465,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2519,7 +2529,7 @@
         <v>45396</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2580,7 +2590,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2594,10 +2604,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45660</v>
+        <v>45593</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2610,7 +2620,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2653,7 +2663,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2667,10 +2677,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45688</v>
+        <v>45520</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2683,7 +2693,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2726,7 +2736,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2740,10 +2750,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45890</v>
+        <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2755,8 +2765,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2799,7 +2814,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2813,10 +2828,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45799</v>
+        <v>46009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2830,11 +2845,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2877,7 +2892,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2891,10 +2906,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45545</v>
+        <v>45915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2906,8 +2921,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>10.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2950,7 +2970,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2964,10 +2984,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45818</v>
+        <v>45988</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2979,8 +2999,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3023,7 +3048,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3037,10 +3062,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46013</v>
+        <v>45939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3054,11 +3079,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3101,7 +3126,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3115,10 +3140,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45686</v>
+        <v>45660</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3131,7 +3156,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3174,7 +3199,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3188,10 +3213,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45232</v>
+        <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3204,7 +3229,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3247,7 +3272,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3261,10 +3286,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44692</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3276,8 +3301,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3320,7 +3350,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3334,10 +3364,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45468</v>
+        <v>45680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3349,13 +3379,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3398,7 +3423,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3412,10 +3437,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46009</v>
+        <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3427,13 +3452,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3476,7 +3496,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3490,10 +3510,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45988</v>
+        <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3511,7 +3531,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.9</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3554,7 +3574,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3568,10 +3588,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45560</v>
+        <v>45453</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3583,13 +3603,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3632,7 +3647,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3646,10 +3661,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45939</v>
+        <v>44939</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3663,11 +3678,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3710,7 +3725,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3724,10 +3739,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46009</v>
+        <v>45818</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3739,13 +3754,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3788,7 +3798,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3802,10 +3812,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45104</v>
+        <v>44897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3818,7 +3828,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3861,7 +3871,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3875,10 +3885,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45915</v>
+        <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3890,13 +3900,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>10.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3939,7 +3944,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3953,10 +3958,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44658</v>
+        <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3968,8 +3973,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4012,7 +4022,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4022,14 +4032,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45355</v>
+        <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4041,13 +4051,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4107,7 +4112,7 @@
         <v>45588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4163,7 +4168,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4177,10 +4182,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45957</v>
+        <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,7 +4198,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4236,7 +4241,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45840</v>
+        <v>45355</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,11 +4272,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4314,7 +4319,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4328,10 +4333,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45840</v>
+        <v>46045</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4343,13 +4348,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45961</v>
+        <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4421,13 +4421,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4470,7 +4465,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4484,10 +4479,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45957</v>
+        <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4499,8 +4494,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45875</v>
+        <v>45168</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45700</v>
+        <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4694,7 +4694,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45968</v>
+        <v>45711</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4723,13 +4723,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4772,7 +4767,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4786,10 +4781,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45680</v>
+        <v>45875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4802,7 +4797,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4845,7 +4840,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4859,10 +4854,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45972</v>
+        <v>46057</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4875,7 +4870,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4918,7 +4913,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4932,10 +4927,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45153</v>
+        <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4945,11 +4940,6 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4996,7 +4986,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5010,10 +5000,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45975</v>
+        <v>46059</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5025,13 +5015,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5074,7 +5059,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5088,10 +5073,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46045</v>
+        <v>46059</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5104,7 +5089,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5147,7 +5132,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5161,10 +5146,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45401</v>
+        <v>46059</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5177,7 +5162,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5220,7 +5205,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5234,10 +5219,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45058</v>
+        <v>45957</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5249,13 +5234,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>14.9</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5298,7 +5278,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5312,10 +5292,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46048</v>
+        <v>45961</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5327,8 +5307,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5371,7 +5356,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5385,10 +5370,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45968</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5402,11 +5387,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5449,7 +5434,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5463,10 +5448,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45995</v>
+        <v>44747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5479,7 +5464,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5522,7 +5507,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5536,10 +5521,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45468</v>
+        <v>45972</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5551,13 +5536,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>25.4</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5600,7 +5580,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5614,10 +5594,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46000</v>
+        <v>45058</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5631,11 +5611,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>14.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5678,7 +5658,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5692,10 +5672,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46000</v>
+        <v>45975</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,11 +5689,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5756,7 +5736,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5770,10 +5750,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46057</v>
+        <v>44930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5786,7 +5766,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5829,7 +5809,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5843,10 +5823,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44969</v>
+        <v>45204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5864,7 +5844,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5907,7 +5887,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5921,10 +5901,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46059</v>
+        <v>45995</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5980,7 +5960,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5994,10 +5974,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46059</v>
+        <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6009,8 +5989,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6053,7 +6038,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6067,10 +6052,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46059</v>
+        <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6082,8 +6067,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6126,7 +6116,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6140,10 +6130,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45726</v>
+        <v>46093</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6156,7 +6146,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6199,7 +6189,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6213,10 +6203,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45390</v>
+        <v>46098</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6228,8 +6218,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6272,7 +6267,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6286,10 +6281,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45168</v>
+        <v>46100</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6302,7 +6297,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6345,7 +6340,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6359,10 +6354,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45236</v>
+        <v>46111</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6376,11 +6371,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6423,7 +6418,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6437,10 +6432,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44900</v>
+        <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6452,13 +6447,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6501,7 +6491,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6515,10 +6505,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44900</v>
+        <v>45203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6531,7 +6521,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6574,7 +6564,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6588,10 +6578,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46093</v>
+        <v>45669</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6604,7 +6594,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6647,7 +6637,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6661,10 +6651,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45681</v>
+        <v>46128</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6676,8 +6666,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>14.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6720,7 +6715,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6734,10 +6729,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46098</v>
+        <v>45112</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6749,13 +6744,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6798,7 +6788,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6812,10 +6802,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46100</v>
+        <v>46140</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6827,8 +6817,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6871,7 +6866,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6885,10 +6880,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45329</v>
+        <v>45226</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6900,8 +6895,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6944,7 +6944,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46111</v>
+        <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44747</v>
+        <v>44536</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45520</v>
+        <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7124,8 +7124,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7168,7 +7173,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7178,14 +7183,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45588</v>
+        <v>46139</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7197,8 +7202,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7241,7 +7251,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7255,10 +7265,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45203</v>
+        <v>45153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7276,7 +7286,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7319,7 +7329,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7333,10 +7343,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46128</v>
+        <v>46140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7350,11 +7360,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7397,7 +7407,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7411,10 +7421,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44939</v>
+        <v>46140</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,11 +7438,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>10.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7475,7 +7485,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7489,10 +7499,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45068</v>
+        <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7505,7 +7515,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7548,7 +7558,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7562,10 +7572,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44907</v>
+        <v>46140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7577,8 +7587,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7621,7 +7636,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7635,10 +7650,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45037</v>
+        <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7650,8 +7665,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7694,7 +7714,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7708,10 +7728,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45028</v>
+        <v>45386</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7723,8 +7743,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7767,7 +7792,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7781,10 +7806,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44938</v>
+        <v>45068</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7797,7 +7822,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7840,7 +7865,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7854,10 +7879,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45226</v>
+        <v>45401</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7869,13 +7894,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7918,7 +7938,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7932,10 +7952,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45386</v>
+        <v>44938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7947,13 +7967,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7996,7 +8011,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8006,14 +8021,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45229</v>
+        <v>46141</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8025,8 +8040,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8069,7 +8089,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8083,10 +8103,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8098,13 +8118,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8147,7 +8162,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8161,10 +8176,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46140</v>
+        <v>45700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8178,11 +8193,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>16.1</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8225,7 +8240,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8239,10 +8254,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46140</v>
+        <v>45681</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8254,13 +8269,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8303,7 +8313,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8317,10 +8327,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46140</v>
+        <v>45072</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8332,13 +8342,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8381,7 +8386,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8395,10 +8400,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46140</v>
+        <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8410,13 +8415,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45635</v>
+        <v>44938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8488,13 +8488,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8537,7 +8532,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8551,10 +8546,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46140</v>
+        <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8572,7 +8567,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>10.7</v>
+        <v>14.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8615,7 +8610,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8625,14 +8620,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46141</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8650,7 +8645,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8693,7 +8688,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8707,10 +8702,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46140</v>
+        <v>45203</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8724,11 +8719,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8771,7 +8766,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8785,10 +8780,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46146</v>
+        <v>45708</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8801,7 +8796,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9.1</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8844,7 +8839,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8854,14 +8849,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>45560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8875,11 +8870,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8922,7 +8917,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8936,10 +8931,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44938</v>
+        <v>45686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8952,7 +8947,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8995,7 +8990,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9009,10 +9004,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45985</v>
+        <v>45236</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9026,11 +9021,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>14.1</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9073,7 +9068,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9087,10 +9082,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44938</v>
+        <v>45174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9102,8 +9097,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9156,14 +9156,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44930</v>
+        <v>46169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9175,8 +9175,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9219,7 +9224,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9229,14 +9234,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9248,13 +9253,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9297,7 +9297,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9307,14 +9307,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46170</v>
+        <v>45229</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44938</v>
+        <v>45468</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>25.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>46181</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45593</v>
+        <v>45726</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
         <v>46181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45112</v>
+        <v>45372</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9696,8 +9696,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9740,7 +9745,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9754,10 +9759,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45614</v>
+        <v>46195</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9769,8 +9774,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>23.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9813,7 +9823,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9827,10 +9837,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46195</v>
+        <v>45037</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9842,13 +9852,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>23.6</v>
+        <v>8.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9891,7 +9896,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9905,10 +9910,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46196</v>
+        <v>44747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9921,7 +9926,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9964,7 +9969,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9978,10 +9983,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45372</v>
+        <v>46196</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9993,13 +9998,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10042,7 +10042,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44728</v>
+        <v>44969</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10071,8 +10071,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10115,7 +10120,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10129,10 +10134,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45708</v>
+        <v>46203</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10144,8 +10149,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10188,7 +10198,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10202,10 +10212,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46203</v>
+        <v>44900</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10219,11 +10229,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10266,7 +10276,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10283,7 +10293,7 @@
         <v>46203</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10297,11 +10307,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10344,7 +10354,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10354,14 +10364,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46209</v>
+        <v>44728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10371,11 +10381,6 @@
       <c r="G128" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -10422,7 +10427,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10432,14 +10437,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46255</v>
+        <v>46209</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10453,11 +10458,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>24.1</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10500,7 +10505,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10510,14 +10515,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46199</v>
+        <v>44938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10529,13 +10534,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10578,7 +10578,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10588,14 +10588,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45174</v>
+        <v>46199</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10609,11 +10609,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>51.6</v>
+        <v>4.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45468</v>
+        <v>46255</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>24.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10748,10 +10748,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45711</v>
+        <v>45007</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10763,8 +10763,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10807,7 +10812,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10821,10 +10826,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46261</v>
+        <v>44692</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10836,13 +10841,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10885,7 +10885,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10899,10 +10899,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45174</v>
+        <v>46261</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10963,7 +10963,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10977,10 +10977,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46220</v>
+        <v>46205</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10992,13 +10992,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11041,7 +11036,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11055,10 +11050,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11070,8 +11065,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11131,7 +11131,7 @@
         <v>46265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45204</v>
+        <v>46268</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11223,11 +11223,11 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46268</v>
+        <v>44900</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11299,13 +11299,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11348,7 +11343,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,10 +11357,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44897</v>
+        <v>46227</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11377,8 +11372,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
         <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45163</v>
+        <v>44907</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11528,13 +11528,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11577,7 +11572,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11591,10 +11586,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11606,13 +11601,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11655,7 +11645,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11669,10 +11659,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44747</v>
+        <v>45390</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11685,7 +11675,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11728,7 +11718,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11742,10 +11732,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46232</v>
+        <v>44658</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11801,7 +11791,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11815,10 +11805,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45614</v>
+        <v>46281</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11830,8 +11820,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>35.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11874,7 +11869,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11888,10 +11883,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45453</v>
+        <v>45174</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11903,8 +11898,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>51.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46281</v>
+        <v>45163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11978,11 +11978,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>35.1</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12039,10 +12039,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45146</v>
+        <v>46244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12054,13 +12054,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12103,7 +12098,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12117,10 +12112,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45615</v>
+        <v>46280</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12133,7 +12128,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12176,7 +12171,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12190,10 +12185,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46244</v>
+        <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12206,7 +12201,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12249,7 +12244,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12263,10 +12258,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46289</v>
+        <v>45146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12280,11 +12275,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>28.9</v>
+        <v>5.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12327,7 +12322,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12341,10 +12336,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46258</v>
+        <v>46289</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12356,8 +12351,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>28.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12414,10 +12414,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12429,8 +12429,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>19.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12473,7 +12478,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 40058-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12487,10 +12492,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46293</v>
+        <v>46258</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12502,13 +12507,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>12.5</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12551,7 +12551,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39988-2026</t>
+          <t>A 40098-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12568,7 +12568,7 @@
         <v>46293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39804-2026</t>
+          <t>A 39988-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>46293</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 40098-2026</t>
+          <t>A 40058-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12802,7 +12802,7 @@
         <v>46293</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>45247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43407-2022</t>
+          <t>A 57209-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44834</v>
+        <v>44895</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -847,21 +847,21 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -887,471 +887,471 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knölspindel</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 43407-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Orre</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 37716-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45881</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 37716-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45881</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ullticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 37716-2025 artfynd.xlsx", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 37716-2025 karta.png", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 37716-2025 georefererad karta.tif", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 37716-2025 FSC-klagomål.docx", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 37716-2025 FSC-klagomål mail.docx", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 37716-2025 tillsynsbegäran.docx", "A 37716-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 37716-2025 tillsynsbegäran mail.docx", "A 37716-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 57209-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knölspindel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64814-2021</t>
+          <t>A 57734-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44512</v>
+        <v>44484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1937,8 +1937,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57734-2021</t>
+          <t>A 64814-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1995,10 +2000,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44484</v>
+        <v>44512</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2010,13 +2015,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45329</v>
+        <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45688</v>
+        <v>45700</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2234,8 +2234,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2278,7 +2283,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45468</v>
+        <v>45711</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2307,13 +2312,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45596</v>
+        <v>45174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46013</v>
+        <v>45153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45396</v>
+        <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2541,13 +2541,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2590,7 +2585,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45593</v>
+        <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2620,7 +2615,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2663,7 +2658,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2677,10 +2672,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45520</v>
+        <v>44938</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2693,7 +2688,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2736,7 +2731,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2750,10 +2745,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46009</v>
+        <v>45058</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2767,11 +2762,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>14.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2814,7 +2809,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2828,10 +2823,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46009</v>
+        <v>44930</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2843,13 +2838,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2892,7 +2882,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2906,10 +2896,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45915</v>
+        <v>45204</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2927,7 +2917,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2970,7 +2960,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2984,10 +2974,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45988</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3001,11 +2991,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3048,7 +3038,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3062,10 +3052,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45939</v>
+        <v>44897</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3077,13 +3067,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3126,7 +3111,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3140,10 +3125,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45660</v>
+        <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3155,8 +3140,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3199,7 +3189,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3213,10 +3203,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45545</v>
+        <v>45468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3228,8 +3218,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>25.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3272,7 +3267,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3286,10 +3281,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44938</v>
+        <v>45203</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3301,13 +3296,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3350,7 +3340,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3364,10 +3354,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45680</v>
+        <v>44969</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3379,8 +3369,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3423,7 +3418,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45890</v>
+        <v>44747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3453,7 +3448,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3496,7 +3491,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3510,10 +3505,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45799</v>
+        <v>45726</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3525,13 +3520,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3574,7 +3564,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3588,10 +3578,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45453</v>
+        <v>45390</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3604,7 +3594,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3647,7 +3637,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3661,10 +3651,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44939</v>
+        <v>45669</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3676,13 +3666,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3725,7 +3710,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3739,10 +3724,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45818</v>
+        <v>44938</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3754,8 +3739,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3798,7 +3788,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3812,10 +3802,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44897</v>
+        <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3828,7 +3818,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3871,7 +3861,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3885,10 +3875,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45232</v>
+        <v>45168</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3901,7 +3891,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3944,7 +3934,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3958,10 +3948,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45468</v>
+        <v>45236</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,11 +3965,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4022,7 +4012,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,14 +4022,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45588</v>
+        <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4052,7 +4042,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4095,7 +4085,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45588</v>
+        <v>44900</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4124,8 +4114,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4168,7 +4163,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4182,10 +4177,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46048</v>
+        <v>44900</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4198,7 +4193,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10.8</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4241,7 +4236,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8613-2024</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45355</v>
+        <v>45593</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4270,13 +4265,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4319,7 +4309,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4333,10 +4323,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46045</v>
+        <v>45681</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4349,7 +4339,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4392,7 +4382,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4406,10 +4396,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45614</v>
+        <v>45146</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4421,8 +4411,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4465,7 +4460,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4479,10 +4474,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45840</v>
+        <v>45615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4494,13 +4489,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4543,7 +4533,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4557,10 +4547,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45168</v>
+        <v>45329</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4573,7 +4563,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4616,7 +4606,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4630,10 +4620,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45840</v>
+        <v>45112</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4645,13 +4635,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4694,7 +4679,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4708,10 +4693,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45711</v>
+        <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4723,8 +4708,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4767,7 +4757,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4781,10 +4771,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45875</v>
+        <v>45688</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4797,7 +4787,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4840,7 +4830,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4854,10 +4844,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46057</v>
+        <v>45396</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4869,8 +4859,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4913,7 +4908,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4927,10 +4922,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45957</v>
+        <v>45660</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4943,7 +4938,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4986,7 +4981,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5000,10 +4995,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46059</v>
+        <v>45614</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5016,7 +5011,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5059,7 +5054,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5073,10 +5068,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46059</v>
+        <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5088,8 +5083,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46059</v>
+        <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45957</v>
+        <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45961</v>
+        <v>45372</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5309,11 +5309,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5356,7 +5356,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45968</v>
+        <v>45520</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5385,13 +5385,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5434,7 +5429,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5448,10 +5443,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44747</v>
+        <v>44728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5464,7 +5459,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5507,7 +5502,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5517,14 +5512,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45972</v>
+        <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5537,7 +5532,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5580,7 +5575,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5594,10 +5589,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45058</v>
+        <v>45708</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5609,13 +5604,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>14.9</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5658,7 +5648,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5672,10 +5662,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45975</v>
+        <v>45203</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5689,11 +5679,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5736,7 +5726,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5750,10 +5740,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44930</v>
+        <v>45818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5766,7 +5756,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5809,7 +5799,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5823,10 +5813,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45204</v>
+        <v>45686</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5838,13 +5828,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5887,7 +5872,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5901,10 +5886,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45995</v>
+        <v>44939</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5916,8 +5901,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5960,7 +5950,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5974,10 +5964,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46000</v>
+        <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5989,13 +5979,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6038,7 +6023,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6052,10 +6037,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46000</v>
+        <v>44907</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6067,13 +6052,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6116,7 +6096,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6130,10 +6110,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46093</v>
+        <v>45232</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6146,7 +6126,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6189,7 +6169,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6203,10 +6183,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46098</v>
+        <v>45037</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6218,13 +6198,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6267,7 +6242,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6281,10 +6256,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46100</v>
+        <v>45028</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6297,7 +6272,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6340,7 +6315,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6354,10 +6329,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46111</v>
+        <v>45174</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6375,7 +6350,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>51.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6418,7 +6393,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6432,10 +6407,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45028</v>
+        <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6447,8 +6422,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6491,7 +6471,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6505,10 +6485,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45203</v>
+        <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6521,7 +6501,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6564,7 +6544,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6578,10 +6558,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45669</v>
+        <v>45468</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6593,8 +6573,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6637,7 +6622,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6647,14 +6632,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46128</v>
+        <v>45229</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6666,13 +6651,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>14.1</v>
+        <v>7.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6715,7 +6695,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 8613-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6729,10 +6709,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45112</v>
+        <v>45355</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6744,8 +6724,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6788,7 +6773,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6802,10 +6787,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46140</v>
+        <v>45560</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6819,11 +6804,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6866,7 +6851,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6880,10 +6865,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45226</v>
+        <v>45104</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6895,13 +6880,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6944,7 +6924,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6958,10 +6938,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>45635</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6979,7 +6959,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7022,7 +7002,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7036,10 +7016,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44536</v>
+        <v>44658</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7052,7 +7032,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7095,7 +7075,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7109,10 +7089,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46140</v>
+        <v>45840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7130,7 +7110,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7173,7 +7153,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7187,10 +7167,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46139</v>
+        <v>45840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7204,11 +7184,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7251,7 +7231,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7265,10 +7245,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45153</v>
+        <v>45588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7280,13 +7260,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7329,7 +7304,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7343,10 +7318,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46140</v>
+        <v>45875</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7358,13 +7333,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>16.1</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7407,7 +7377,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7421,10 +7391,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46140</v>
+        <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7436,13 +7406,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>10.7</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7485,7 +7450,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7499,10 +7464,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45104</v>
+        <v>45680</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7515,7 +7480,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7558,7 +7523,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7572,10 +7537,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46140</v>
+        <v>45957</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7587,13 +7552,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7636,7 +7596,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7650,10 +7610,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45635</v>
+        <v>45961</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7667,11 +7627,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7714,7 +7674,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7728,10 +7688,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45386</v>
+        <v>45957</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,13 +7703,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7792,7 +7747,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7806,10 +7761,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45068</v>
+        <v>45968</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7821,8 +7776,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7865,7 +7825,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7879,10 +7839,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45401</v>
+        <v>45972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7938,7 +7898,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7952,10 +7912,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44938</v>
+        <v>45975</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7967,8 +7927,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8011,7 +7976,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8025,10 +7990,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46141</v>
+        <v>45995</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8040,13 +8005,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8089,7 +8049,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8103,10 +8063,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46146</v>
+        <v>46000</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8118,8 +8078,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8162,7 +8127,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8176,10 +8141,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>46000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8193,11 +8158,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8240,7 +8205,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8254,10 +8219,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45681</v>
+        <v>46013</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8269,8 +8234,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8313,7 +8283,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8327,10 +8297,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45072</v>
+        <v>46009</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8342,8 +8312,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8386,7 +8361,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8400,10 +8375,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45614</v>
+        <v>45988</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8415,8 +8390,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8459,7 +8439,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8473,10 +8453,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44938</v>
+        <v>45939</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8488,8 +8468,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8532,7 +8517,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8546,10 +8531,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45985</v>
+        <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8563,11 +8548,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>14.1</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8610,7 +8595,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8620,14 +8605,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>45915</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8645,7 +8630,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.2</v>
+        <v>10.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8688,7 +8673,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8702,10 +8687,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45203</v>
+        <v>46045</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8717,13 +8702,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8766,7 +8746,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8780,10 +8760,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45708</v>
+        <v>46048</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8796,7 +8776,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8839,7 +8819,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8853,10 +8833,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45560</v>
+        <v>46057</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8868,13 +8848,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8917,7 +8892,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8931,10 +8906,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45686</v>
+        <v>46059</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8947,7 +8922,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8990,7 +8965,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9004,10 +8979,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45236</v>
+        <v>46059</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9019,13 +8994,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9068,7 +9038,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9082,10 +9052,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45174</v>
+        <v>46059</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9097,13 +9067,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9146,7 +9111,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9156,14 +9121,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46169</v>
+        <v>46093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9175,13 +9140,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9224,7 +9184,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9238,10 +9198,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46170</v>
+        <v>46098</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9253,8 +9213,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9297,7 +9262,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9307,14 +9272,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45229</v>
+        <v>46100</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9327,7 +9292,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9370,7 +9335,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9384,10 +9349,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45468</v>
+        <v>46111</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9405,7 +9370,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>25.4</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9448,7 +9413,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9462,10 +9427,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46181</v>
+        <v>46128</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9477,8 +9442,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>14.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9521,7 +9491,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9535,10 +9505,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45726</v>
+        <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9551,7 +9521,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9594,7 +9564,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9608,10 +9578,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46181</v>
+        <v>45226</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9623,8 +9593,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9667,7 +9642,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9681,10 +9656,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45372</v>
+        <v>45386</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9698,11 +9673,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9745,7 +9720,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9759,10 +9734,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46195</v>
+        <v>46139</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9776,11 +9751,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>23.6</v>
+        <v>6.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9823,7 +9798,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9837,10 +9812,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45037</v>
+        <v>46140</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9852,8 +9827,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>8.1</v>
+        <v>16.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9896,7 +9876,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9910,10 +9890,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44747</v>
+        <v>46140</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9925,8 +9905,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9969,7 +9954,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9983,10 +9968,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46196</v>
+        <v>46140</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9998,8 +9983,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10042,7 +10032,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10056,10 +10046,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44969</v>
+        <v>46140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10077,7 +10067,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10120,7 +10110,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10134,10 +10124,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46203</v>
+        <v>46140</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10151,11 +10141,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.2</v>
+        <v>10.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10198,7 +10188,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10212,10 +10202,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44900</v>
+        <v>46141</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10229,11 +10219,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10276,7 +10266,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10290,10 +10280,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46203</v>
+        <v>46140</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10311,7 +10301,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10354,7 +10344,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10368,10 +10358,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44728</v>
+        <v>46146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10384,7 +10374,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>9.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10427,7 +10417,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10441,10 +10431,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46209</v>
+        <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10458,11 +10448,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10505,7 +10495,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10522,7 +10512,7 @@
         <v>44938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10535,7 +10525,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10578,7 +10568,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10588,14 +10578,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46199</v>
+        <v>45985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10609,11 +10599,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.1</v>
+        <v>14.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10656,7 +10646,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10666,14 +10656,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46255</v>
+        <v>46169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10687,11 +10677,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>24.1</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10734,7 +10724,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10748,10 +10738,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45007</v>
+        <v>46170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10763,13 +10753,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10812,7 +10797,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10826,10 +10811,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44692</v>
+        <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10842,7 +10827,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10885,7 +10870,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10899,10 +10884,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46261</v>
+        <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10914,13 +10899,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10963,7 +10943,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10977,10 +10957,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46205</v>
+        <v>46195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10992,8 +10972,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>23.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11036,7 +11021,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11050,10 +11035,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46220</v>
+        <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11065,13 +11050,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11114,7 +11094,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11128,10 +11108,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11149,7 +11129,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11192,7 +11172,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11206,10 +11186,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46268</v>
+        <v>46203</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11223,11 +11203,11 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11270,7 +11250,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11280,14 +11260,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44900</v>
+        <v>46209</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11299,8 +11279,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11343,7 +11328,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11357,10 +11342,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46227</v>
+        <v>46255</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11378,7 +11363,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.8</v>
+        <v>24.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11421,7 +11406,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11431,14 +11416,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46268</v>
+        <v>46199</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11456,7 +11441,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11499,7 +11484,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11513,10 +11498,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44907</v>
+        <v>46261</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11528,8 +11513,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11572,7 +11562,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11586,10 +11576,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46232</v>
+        <v>46220</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11601,8 +11591,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11645,7 +11640,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11659,10 +11654,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45390</v>
+        <v>46205</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11675,7 +11670,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11718,7 +11713,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11732,10 +11727,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44658</v>
+        <v>46265</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11747,8 +11742,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46281</v>
+        <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11822,11 +11822,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>35.1</v>
+        <v>3.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11883,10 +11883,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45174</v>
+        <v>46268</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11900,11 +11900,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>51.6</v>
+        <v>6.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45163</v>
+        <v>46227</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11978,11 +11978,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12039,10 +12039,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12098,7 +12098,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12127,8 +12127,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>35.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12171,7 +12176,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12185,10 +12190,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45615</v>
+        <v>46244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12201,7 +12206,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12244,7 +12249,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12258,10 +12263,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45146</v>
+        <v>46289</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12275,11 +12280,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.4</v>
+        <v>28.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12322,7 +12327,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12336,10 +12341,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46289</v>
+        <v>46258</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12351,13 +12356,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>28.9</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39804-2026</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12414,10 +12414,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12429,13 +12429,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>19.5</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12478,7 +12473,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 40058-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12492,10 +12487,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46258</v>
+        <v>46293</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12507,8 +12502,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>12.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12551,7 +12551,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 40098-2026</t>
+          <t>A 39988-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12568,7 +12568,7 @@
         <v>46293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39988-2026</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>46293</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 40058-2026</t>
+          <t>A 40098-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12802,7 +12802,7 @@
         <v>46293</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>45247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 57209-2022</t>
+          <t>A 43407-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -887,471 +887,471 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 21111-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 46376-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 37716-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45881</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 37716-2025 artfynd.xlsx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 37716-2025 karta.png", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 37716-2025 georefererad karta.tif", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 37716-2025 FSC-klagomål.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 37716-2025 FSC-klagomål mail.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 37716-2025 tillsynsbegäran.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 37716-2025 tillsynsbegäran mail.docx", "A 37716-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 57209-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Knölspindel</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 46376-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45197</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 43407-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 37716-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45881</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 37716-2025 artfynd.xlsx", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 37716-2025 karta.png", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 37716-2025 georefererad karta.tif", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 37716-2025 FSC-klagomål.docx", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 37716-2025 FSC-klagomål mail.docx", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 37716-2025 tillsynsbegäran.docx", "A 37716-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 37716-2025 tillsynsbegäran mail.docx", "A 37716-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57734-2021</t>
+          <t>A 64814-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44484</v>
+        <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1937,13 +1937,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64814-2021</t>
+          <t>A 57734-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2000,10 +1995,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44512</v>
+        <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2015,8 +2010,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45072</v>
+        <v>45688</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45700</v>
+        <v>45329</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2234,13 +2234,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2283,7 +2278,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45711</v>
+        <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2312,8 +2307,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45174</v>
+        <v>45468</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45153</v>
+        <v>46009</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2465,11 +2465,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44536</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2541,8 +2541,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2585,7 +2590,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2599,10 +2604,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2614,8 +2619,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2658,7 +2668,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2672,10 +2682,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44938</v>
+        <v>45915</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2687,8 +2697,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>10.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2731,7 +2746,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 59146-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2745,10 +2760,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45058</v>
+        <v>45988</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2766,7 +2781,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>14.9</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2809,7 +2824,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 49580-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2823,10 +2838,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44930</v>
+        <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2838,8 +2853,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2882,7 +2902,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2896,10 +2916,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45204</v>
+        <v>45396</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2917,7 +2937,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2960,7 +2980,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2974,10 +2994,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2989,13 +3009,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3038,7 +3053,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3052,10 +3067,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44897</v>
+        <v>45520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3068,7 +3083,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3111,7 +3126,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 38176-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3125,10 +3140,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45163</v>
+        <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3140,13 +3155,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3189,7 +3199,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3203,10 +3213,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45468</v>
+        <v>45660</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3218,13 +3228,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>25.4</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3267,7 +3272,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3281,10 +3286,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45203</v>
+        <v>45680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3340,7 +3345,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3354,10 +3359,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44969</v>
+        <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3369,13 +3374,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44747</v>
+        <v>44938</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3447,8 +3447,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3491,7 +3496,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3505,10 +3510,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45726</v>
+        <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3521,7 +3526,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>10.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3564,7 +3569,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3578,10 +3583,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45390</v>
+        <v>46045</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3594,7 +3599,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3637,7 +3642,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45669</v>
+        <v>45453</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3667,7 +3672,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3710,7 +3715,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 7028-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3724,10 +3729,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44938</v>
+        <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3739,13 +3744,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3788,7 +3788,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 7427-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45614</v>
+        <v>46059</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 7444-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45168</v>
+        <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 7447-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45236</v>
+        <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3963,13 +3963,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4012,7 +4007,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4026,10 +4021,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45453</v>
+        <v>45799</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4041,8 +4036,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44900</v>
+        <v>44939</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,11 +4116,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44900</v>
+        <v>44897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4236,7 +4236,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45593</v>
+        <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4309,7 +4309,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45681</v>
+        <v>46093</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45146</v>
+        <v>46098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,11 +4413,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.4</v>
+        <v>7.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,14 +4470,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45615</v>
+        <v>45588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45329</v>
+        <v>45588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45112</v>
+        <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45596</v>
+        <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4708,13 +4708,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4757,7 +4752,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4771,10 +4766,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45688</v>
+        <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4787,7 +4782,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4830,7 +4825,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45396</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4859,13 +4854,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4908,7 +4898,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4922,10 +4912,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45660</v>
+        <v>45961</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4937,8 +4927,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4981,7 +4976,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4995,10 +4990,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45614</v>
+        <v>46111</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5010,8 +5005,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45799</v>
+        <v>45168</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5083,13 +5083,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5132,7 +5127,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44747</v>
+        <v>45968</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5161,8 +5156,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38176-2024</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45545</v>
+        <v>45711</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45372</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5307,13 +5307,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5356,7 +5351,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5370,10 +5365,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45520</v>
+        <v>45975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5385,8 +5380,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5429,7 +5429,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44728</v>
+        <v>45818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5512,14 +5512,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45588</v>
+        <v>44747</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45708</v>
+        <v>46128</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5604,8 +5604,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>14.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5648,7 +5653,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5662,10 +5667,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45203</v>
+        <v>45058</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5679,11 +5684,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>14.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5726,7 +5731,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5740,10 +5745,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45818</v>
+        <v>44930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5756,7 +5761,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5799,7 +5804,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5813,10 +5818,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45686</v>
+        <v>45204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5828,8 +5833,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5872,7 +5882,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5886,10 +5896,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44939</v>
+        <v>46140</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5903,11 +5913,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5950,7 +5960,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5964,10 +5974,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45068</v>
+        <v>45995</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5980,7 +5990,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6023,7 +6033,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6037,10 +6047,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44907</v>
+        <v>45226</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6052,8 +6062,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6096,7 +6111,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6110,10 +6125,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45232</v>
+        <v>46000</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6125,8 +6140,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6169,7 +6189,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6183,10 +6203,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45037</v>
+        <v>46000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6198,8 +6218,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6242,7 +6267,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6256,10 +6281,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45028</v>
+        <v>46140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6271,8 +6296,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6315,7 +6345,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6329,10 +6359,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45174</v>
+        <v>46140</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6350,7 +6380,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>51.6</v>
+        <v>5.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6393,7 +6423,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6407,10 +6437,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45468</v>
+        <v>46139</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6424,11 +6454,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6471,7 +6501,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6485,10 +6515,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44692</v>
+        <v>45468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6500,8 +6530,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6544,7 +6579,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6558,10 +6593,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45468</v>
+        <v>46140</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6579,7 +6614,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>16.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6622,7 +6657,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6632,14 +6667,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45229</v>
+        <v>46140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6651,8 +6686,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>7.6</v>
+        <v>10.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6712,7 +6752,7 @@
         <v>45355</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6773,7 +6813,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6787,10 +6827,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45560</v>
+        <v>45840</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6804,11 +6844,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6851,7 +6891,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6865,10 +6905,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45104</v>
+        <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6880,8 +6920,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6924,7 +6969,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6938,10 +6983,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45635</v>
+        <v>45840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6959,7 +7004,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7002,7 +7047,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7016,10 +7061,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44658</v>
+        <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7031,8 +7076,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7075,7 +7125,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7089,10 +7139,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45840</v>
+        <v>45875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7104,13 +7154,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7153,7 +7198,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7167,10 +7212,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45840</v>
+        <v>44938</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7182,13 +7227,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7231,7 +7271,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7245,10 +7285,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45588</v>
+        <v>46141</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7260,8 +7300,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7304,7 +7349,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7318,10 +7363,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45875</v>
+        <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7334,7 +7379,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7377,7 +7422,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7391,10 +7436,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45890</v>
+        <v>45203</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7407,7 +7452,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7450,7 +7495,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7464,10 +7509,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45680</v>
+        <v>46146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7480,7 +7525,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7523,7 +7568,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7537,10 +7582,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45957</v>
+        <v>45669</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7553,7 +7598,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7596,7 +7641,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7610,10 +7655,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45961</v>
+        <v>44938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7625,13 +7670,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7674,7 +7714,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7688,10 +7728,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45957</v>
+        <v>45985</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7703,8 +7743,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7747,7 +7792,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7757,14 +7802,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45968</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7782,7 +7827,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7825,7 +7870,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7839,10 +7884,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45972</v>
+        <v>45112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,7 +7943,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7912,10 +7957,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45975</v>
+        <v>44536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7927,13 +7972,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7976,7 +8016,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7986,14 +8026,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45995</v>
+        <v>46169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8005,8 +8045,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8049,7 +8094,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8063,10 +8108,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46000</v>
+        <v>45153</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8080,11 +8125,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8127,7 +8172,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8141,10 +8186,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46000</v>
+        <v>46170</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8156,13 +8201,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8205,7 +8245,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8219,10 +8259,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46013</v>
+        <v>45104</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8234,13 +8274,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8283,7 +8318,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8297,10 +8332,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46009</v>
+        <v>45635</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,11 +8349,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8361,7 +8396,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59146-2025</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8375,10 +8410,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45988</v>
+        <v>45068</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8390,13 +8425,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>9.9</v>
+        <v>6.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8439,7 +8469,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49580-2025</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8453,10 +8483,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45939</v>
+        <v>45401</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8468,13 +8498,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8517,7 +8542,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8531,10 +8556,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46009</v>
+        <v>45700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8548,11 +8573,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8595,7 +8620,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8609,10 +8634,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45915</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8624,13 +8649,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>10.6</v>
+        <v>4.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8673,7 +8693,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8687,10 +8707,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46045</v>
+        <v>45681</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8703,7 +8723,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8746,7 +8766,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8760,10 +8780,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46048</v>
+        <v>45072</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8776,7 +8796,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8819,7 +8839,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7028-2026</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8833,10 +8853,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46057</v>
+        <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8849,7 +8869,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8892,7 +8912,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7427-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8906,10 +8926,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46059</v>
+        <v>46181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8922,7 +8942,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8965,7 +8985,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7444-2026</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8979,10 +8999,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46059</v>
+        <v>46195</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8994,8 +9014,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>23.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9038,7 +9063,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7447-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9052,10 +9077,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46059</v>
+        <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9067,8 +9092,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9111,7 +9141,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9125,10 +9155,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46093</v>
+        <v>45708</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9141,7 +9171,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9184,7 +9214,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9198,10 +9228,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46098</v>
+        <v>45560</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9215,11 +9245,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9262,7 +9292,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9276,10 +9306,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46100</v>
+        <v>46196</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9292,7 +9322,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9335,7 +9365,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9349,10 +9379,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46111</v>
+        <v>45686</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9364,13 +9394,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9413,7 +9438,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9427,10 +9452,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46128</v>
+        <v>45236</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9448,7 +9473,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>14.1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9491,7 +9516,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9505,10 +9530,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44938</v>
+        <v>46203</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9520,8 +9545,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9564,7 +9594,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9578,10 +9608,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45226</v>
+        <v>45174</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9599,7 +9629,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9642,7 +9672,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 29426-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9656,10 +9686,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45386</v>
+        <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9673,11 +9703,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9720,7 +9750,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9730,14 +9760,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46139</v>
+        <v>46209</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9755,7 +9785,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9798,7 +9828,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9808,14 +9838,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46140</v>
+        <v>46199</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9829,11 +9859,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>16.1</v>
+        <v>4.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9876,7 +9906,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9890,10 +9920,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46140</v>
+        <v>46255</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9911,7 +9941,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.8</v>
+        <v>24.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9954,7 +9984,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9964,14 +9994,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46140</v>
+        <v>45229</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9983,13 +10013,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10032,7 +10057,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10046,10 +10071,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46140</v>
+        <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10067,7 +10092,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>25.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10110,7 +10135,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10124,10 +10149,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46140</v>
+        <v>45726</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10139,13 +10164,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>10.7</v>
+        <v>4.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10188,7 +10208,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10202,10 +10222,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46141</v>
+        <v>46261</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10223,7 +10243,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10266,7 +10286,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10280,10 +10300,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46140</v>
+        <v>46205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10295,13 +10315,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10344,7 +10359,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10358,10 +10373,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46146</v>
+        <v>46220</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10373,8 +10388,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>9.1</v>
+        <v>4.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10417,7 +10437,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10427,14 +10447,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46002</v>
+        <v>46265</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10452,7 +10472,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10495,7 +10515,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10509,10 +10529,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44938</v>
+        <v>45372</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10524,8 +10544,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10568,7 +10593,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10582,10 +10607,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45985</v>
+        <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10599,11 +10624,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>14.1</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10646,7 +10671,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10656,14 +10681,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46169</v>
+        <v>46227</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10677,11 +10702,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10724,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10738,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46170</v>
+        <v>46268</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10753,8 +10778,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10797,7 +10827,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10811,10 +10841,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46181</v>
+        <v>45037</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10827,7 +10857,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10870,7 +10900,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10884,10 +10914,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46181</v>
+        <v>44747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10900,7 +10930,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10943,7 +10973,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10957,10 +10987,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46195</v>
+        <v>44969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10978,7 +11008,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>23.6</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11021,7 +11051,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11035,10 +11065,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46196</v>
+        <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11050,8 +11080,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11094,7 +11129,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29426-2026</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11108,10 +11143,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46203</v>
+        <v>44728</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11123,13 +11158,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11172,7 +11202,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11186,10 +11216,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46203</v>
+        <v>46232</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11201,13 +11231,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11250,7 +11275,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11260,14 +11285,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46209</v>
+        <v>44938</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11279,13 +11304,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11328,7 +11348,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11342,10 +11362,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46255</v>
+        <v>46281</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11363,7 +11383,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>24.1</v>
+        <v>35.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11406,7 +11426,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11416,14 +11436,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46199</v>
+        <v>45007</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11441,7 +11461,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11484,7 +11504,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11498,10 +11518,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46261</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11513,13 +11533,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11562,7 +11577,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11576,10 +11591,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46220</v>
+        <v>44692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11591,13 +11606,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11640,7 +11650,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11654,10 +11664,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46205</v>
+        <v>46280</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11670,7 +11680,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11713,7 +11723,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11727,10 +11737,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11748,7 +11758,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>28.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11791,7 +11801,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11805,10 +11815,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46268</v>
+        <v>46290</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11822,11 +11832,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.9</v>
+        <v>19.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11869,7 +11879,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11883,10 +11893,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11898,13 +11908,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11947,7 +11952,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11961,10 +11966,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46227</v>
+        <v>44900</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11976,13 +11981,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 40098-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12039,10 +12039,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46232</v>
+        <v>46293</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12054,8 +12054,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12098,7 +12103,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 39988-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12112,10 +12117,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12133,7 +12138,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>35.1</v>
+        <v>6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12176,7 +12181,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 40009-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12190,10 +12195,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46244</v>
+        <v>46293</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12205,8 +12210,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>10.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12249,7 +12259,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 40058-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12263,10 +12273,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12284,7 +12294,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>28.9</v>
+        <v>12.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12327,7 +12337,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12341,10 +12351,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46258</v>
+        <v>44907</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12357,7 +12367,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12400,7 +12410,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12414,10 +12424,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46280</v>
+        <v>45390</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12430,7 +12440,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12473,7 +12483,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 40058-2026</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12487,10 +12497,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46293</v>
+        <v>44658</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12502,13 +12512,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12551,7 +12556,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39988-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12565,10 +12570,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46293</v>
+        <v>45174</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12586,7 +12591,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>51.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12629,7 +12634,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39804-2026</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12643,10 +12648,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46290</v>
+        <v>45163</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12660,11 +12665,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>19.5</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12707,7 +12712,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 40009-2026</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12721,10 +12726,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46293</v>
+        <v>45615</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12736,13 +12741,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>10.6</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12785,7 +12785,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 40098-2026</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12799,10 +12799,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46293</v>
+        <v>45146</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12816,11 +12816,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>45247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 43407-2022</t>
+          <t>A 21111-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44834</v>
+        <v>45777</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,19 +845,14 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -887,155 +882,160 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 43407-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Orre</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 43407-2022 artfynd.xlsx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 43407-2022 karta.png", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 43407-2022 georefererad karta.tif", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 43407-2022 FSC-klagomål.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 43407-2022 FSC-klagomål mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 43407-2022 tillsynsbegäran.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 43407-2022 tillsynsbegäran mail.docx", "A 43407-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1760/fåglar/A 43407-2022 prioriterade fågelarter.docx", "A 43407-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 21111-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 21111-2025 artfynd.xlsx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 21111-2025 karta.png", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 21111-2025 georefererad karta.tif", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 21111-2025 FSC-klagomål.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 21111-2025 FSC-klagomål mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 21111-2025 tillsynsbegäran.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 21111-2025 tillsynsbegäran mail.docx", "A 21111-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 46376-2023</t>
+          <t>A 57209-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45197</v>
+        <v>44895</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1064,8 +1064,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1074,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1092,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1101,39 +1106,39 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Knölspindel</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1162,7 @@
         <v>45881</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1250,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57209-2022</t>
+          <t>A 46376-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44895</v>
+        <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1274,13 +1279,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1316,39 +1316,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Knölspindel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 57209-2022 artfynd.xlsx", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/artfynd/A 46376-2023 artfynd.xlsx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 57209-2022 karta.png", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor/A 46376-2023 karta.png", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 57209-2022 georefererad karta.tif", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/kartor_geotiff/A 46376-2023 georefererad karta.tif", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 57209-2022 FSC-klagomål.docx", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomål/A 46376-2023 FSC-klagomål.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 57209-2022 FSC-klagomål mail.docx", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/klagomålsmail/A 46376-2023 FSC-klagomål mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 57209-2022 tillsynsbegäran.docx", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsyn/A 46376-2023 tillsynsbegäran.docx", "A 46376-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 57209-2022 tillsynsbegäran mail.docx", "A 57209-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1760/tillsynsmail/A 46376-2023 tillsynsbegäran mail.docx", "A 46376-2023")</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4744-2025</t>
+          <t>A 22935-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45688</v>
+        <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4998-2024</t>
+          <t>A 70761-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45329</v>
+        <v>44536</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63572-2025</t>
+          <t>A 47728-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46013</v>
+        <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2305,11 +2305,6 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2356,7 +2351,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26230-2024</t>
+          <t>A 1431-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45468</v>
+        <v>45669</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2385,13 +2380,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2434,7 +2424,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62987-2025</t>
+          <t>A 4744-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2448,10 +2438,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46009</v>
+        <v>45688</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2463,13 +2453,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2512,7 +2497,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49596-2024</t>
+          <t>A 63572-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2526,10 +2511,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2543,11 +2528,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2590,7 +2575,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63080-2025</t>
+          <t>A 49596-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2604,10 +2589,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46009</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2621,11 +2606,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2668,7 +2653,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44178-2025</t>
+          <t>A 62987-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2682,10 +2667,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45915</v>
+        <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2699,11 +2684,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2763,7 +2748,7 @@
         <v>45988</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2841,7 +2826,7 @@
         <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2902,7 +2887,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14605-2024</t>
+          <t>A 63080-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2916,10 +2901,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45396</v>
+        <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2933,11 +2918,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2980,7 +2965,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 48591-2024</t>
+          <t>A 44178-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2994,10 +2979,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45593</v>
+        <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3009,8 +2994,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>10.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3053,7 +3043,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33806-2024</t>
+          <t>A 39623-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3067,10 +3057,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45520</v>
+        <v>45890</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3083,7 +3073,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3143,7 +3133,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3199,7 +3189,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 213-2025</t>
+          <t>A 14605-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3213,10 +3203,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45660</v>
+        <v>45396</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3228,8 +3218,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3272,7 +3267,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3452-2025</t>
+          <t>A 4455-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3286,10 +3281,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45680</v>
+        <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3302,7 +3297,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3345,7 +3340,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39623-2025</t>
+          <t>A 213-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45890</v>
+        <v>45660</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3375,7 +3370,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3418,7 +3413,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1840-2023</t>
+          <t>A 4868-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3432,10 +3427,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44938</v>
+        <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3447,13 +3442,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>10.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3496,7 +3486,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4868-2026</t>
+          <t>A 24820-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3510,10 +3500,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46048</v>
+        <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3525,8 +3515,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3569,7 +3564,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4455-2026</t>
+          <t>A 4494-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3583,10 +3578,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46045</v>
+        <v>45686</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3599,7 +3594,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3642,7 +3637,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23279-2024</t>
+          <t>A 54190-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45453</v>
+        <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3672,7 +3667,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3732,7 +3727,7 @@
         <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3805,7 +3800,7 @@
         <v>46059</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
         <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3951,7 +3946,7 @@
         <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4007,7 +4002,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24820-2025</t>
+          <t>A 19324-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4021,10 +4016,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45799</v>
+        <v>44692</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4036,13 +4031,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4085,7 +4075,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2037-2023</t>
+          <t>A 41479-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4099,10 +4089,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44939</v>
+        <v>45560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,11 +4106,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4163,7 +4153,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57792-2022</t>
+          <t>A 29002-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4177,10 +4167,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44897</v>
+        <v>45104</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,7 +4183,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4236,7 +4226,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54190-2023</t>
+          <t>A 15152-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4250,10 +4240,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45232</v>
+        <v>44658</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4266,7 +4256,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4309,7 +4299,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13185-2026</t>
+          <t>A 47732-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4323,10 +4313,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46093</v>
+        <v>45588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4339,7 +4329,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4382,7 +4372,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13960-2026</t>
+          <t>A 6856-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4396,10 +4386,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46098</v>
+        <v>45700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,11 +4403,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4460,7 +4450,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47713-2024</t>
+          <t>A 52905-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,14 +4460,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45588</v>
+        <v>45957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4490,7 +4480,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4533,7 +4523,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47732-2024</t>
+          <t>A 53990-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45588</v>
+        <v>45961</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4562,8 +4552,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4606,7 +4601,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14435-2026</t>
+          <t>A 52922-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4620,10 +4615,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46100</v>
+        <v>45957</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4636,7 +4631,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4679,7 +4674,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52905-2025</t>
+          <t>A 13185-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4693,10 +4688,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>46093</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4709,7 +4704,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4752,7 +4747,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53388-2024</t>
+          <t>A 36697-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4766,10 +4761,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45614</v>
+        <v>45153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4781,8 +4776,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52922-2025</t>
+          <t>A 55234-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4854,8 +4854,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4898,7 +4903,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 53990-2025</t>
+          <t>A 13960-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4912,10 +4917,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45961</v>
+        <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,11 +4934,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4976,7 +4981,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16421-2026</t>
+          <t>A 14435-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4990,10 +4995,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46111</v>
+        <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5005,13 +5010,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39998-2023</t>
+          <t>A 15442-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45168</v>
+        <v>45401</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55234-2025</t>
+          <t>A 55818-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5156,13 +5156,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5205,7 +5200,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8639-2025</t>
+          <t>A 56525-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5219,10 +5214,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45711</v>
+        <v>45975</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5234,8 +5229,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55818-2025</t>
+          <t>A 28255-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>45818</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56525-2025</t>
+          <t>A 20725-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45975</v>
+        <v>45058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>14.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5429,7 +5429,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28255-2025</t>
+          <t>A 13795-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45818</v>
+        <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5458,8 +5458,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5502,7 +5507,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28466-2022</t>
+          <t>A 16421-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5516,10 +5521,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44747</v>
+        <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5529,6 +5534,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>STORFORS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5575,7 +5585,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18757-2026</t>
+          <t>A 26201-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5589,10 +5599,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46128</v>
+        <v>45468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5606,11 +5616,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>14.1</v>
+        <v>25.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5653,7 +5663,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20725-2023</t>
+          <t>A 7072-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5667,10 +5677,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45058</v>
+        <v>44969</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5688,7 +5698,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>14.9</v>
+        <v>5.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5731,7 +5741,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 487-2023</t>
+          <t>A 60511-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5745,10 +5755,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5761,7 +5771,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5804,7 +5814,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47894-2023</t>
+          <t>A 11290-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5818,10 +5828,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45204</v>
+        <v>45726</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5833,13 +5843,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20533-2026</t>
+          <t>A 18757-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46140</v>
+        <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5913,11 +5918,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>14.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60511-2025</t>
+          <t>A 61149-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5989,8 +5994,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6033,7 +6043,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52834-2023</t>
+          <t>A 61123-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6047,10 +6057,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45226</v>
+        <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6064,11 +6074,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6111,7 +6121,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61123-2025</t>
+          <t>A 13636-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6125,10 +6135,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46000</v>
+        <v>45390</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6140,13 +6150,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6189,7 +6194,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61149-2025</t>
+          <t>A 39998-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6203,10 +6208,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46000</v>
+        <v>45168</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6218,13 +6223,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20527-2026</t>
+          <t>A 54738-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46140</v>
+        <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6298,11 +6298,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20449-2026</t>
+          <t>A 57981-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46140</v>
+        <v>44900</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6376,11 +6376,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20311-2026</t>
+          <t>A 26189-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46139</v>
+        <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6454,11 +6454,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26189-2024</t>
+          <t>A 2363-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45468</v>
+        <v>44938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6530,13 +6530,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6579,7 +6574,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20453-2026</t>
+          <t>A 58125-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6593,10 +6588,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46140</v>
+        <v>44900</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6608,13 +6603,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>16.1</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6657,7 +6647,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20465-2026</t>
+          <t>A 3721-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6671,10 +6661,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46140</v>
+        <v>45681</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6686,13 +6676,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.7</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6752,7 +6737,7 @@
         <v>45355</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6813,7 +6798,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33143-2025</t>
+          <t>A 52834-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6827,10 +6812,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45840</v>
+        <v>45226</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6848,7 +6833,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6891,7 +6876,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20543-2026</t>
+          <t>A 13288-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6905,10 +6890,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46140</v>
+        <v>45386</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6922,11 +6907,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6969,7 +6954,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33273-2025</t>
+          <t>A 4998-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6983,10 +6968,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45840</v>
+        <v>45329</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6998,13 +6983,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7047,7 +7027,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13288-2024</t>
+          <t>A 20311-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7061,10 +7041,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45386</v>
+        <v>46139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7082,7 +7062,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7125,7 +7105,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37145-2025</t>
+          <t>A 20453-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7139,10 +7119,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45875</v>
+        <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7154,8 +7134,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>16.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7198,7 +7183,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2363-2023</t>
+          <t>A 20527-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7212,10 +7197,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44938</v>
+        <v>46140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7227,8 +7212,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7271,7 +7261,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20749-2026</t>
+          <t>A 20533-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7285,10 +7275,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7306,7 +7296,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7349,7 +7339,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16359-2023</t>
+          <t>A 20543-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7363,10 +7353,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45028</v>
+        <v>46140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,8 +7368,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7422,7 +7417,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47728-2023</t>
+          <t>A 28466-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45203</v>
+        <v>44747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7452,7 +7447,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7495,7 +7490,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21035-2026</t>
+          <t>A 20465-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,8 +7519,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1431-2025</t>
+          <t>A 20749-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45669</v>
+        <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,8 +7597,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7641,7 +7646,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2352-2023</t>
+          <t>A 20449-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7655,10 +7660,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44938</v>
+        <v>46140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,8 +7675,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7714,7 +7724,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58451-2025</t>
+          <t>A 33806-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7728,10 +7738,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45985</v>
+        <v>45520</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,13 +7753,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7792,7 +7797,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61586-2025</t>
+          <t>A 47713-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7802,14 +7807,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46002</v>
+        <v>45588</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7821,13 +7826,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30587-2023</t>
+          <t>A 33273-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45112</v>
+        <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7899,8 +7899,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7943,7 +7948,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 70761-2021</t>
+          <t>A 33143-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7957,10 +7962,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44536</v>
+        <v>45840</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7972,8 +7977,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8016,7 +8026,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24406-2026</t>
+          <t>A 47624-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8026,14 +8036,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46169</v>
+        <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8051,7 +8061,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8094,7 +8104,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36697-2023</t>
+          <t>A 21035-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8108,10 +8118,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45153</v>
+        <v>46146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8123,13 +8133,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>9.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8172,7 +8177,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24442-2026</t>
+          <t>A 2037-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8186,10 +8191,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46170</v>
+        <v>44939</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8201,8 +8206,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8245,7 +8255,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29002-2023</t>
+          <t>A 21929-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8259,10 +8269,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45104</v>
+        <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8275,7 +8285,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8318,7 +8328,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58586-2024</t>
+          <t>A 59449-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8332,10 +8342,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45635</v>
+        <v>44907</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8345,11 +8355,6 @@
       <c r="G101" t="inlineStr">
         <is>
           <t>STORFORS</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -8396,7 +8401,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21929-2023</t>
+          <t>A 61586-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8406,14 +8411,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45068</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8425,8 +8430,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8469,7 +8479,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15442-2024</t>
+          <t>A 2352-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8483,10 +8493,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45401</v>
+        <v>44938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8499,7 +8509,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8542,7 +8552,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6856-2025</t>
+          <t>A 58451-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8556,10 +8566,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45700</v>
+        <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8573,11 +8583,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>14.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8620,7 +8630,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26067-2026</t>
+          <t>A 17756-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8634,10 +8644,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>45037</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8650,7 +8660,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8693,7 +8703,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3721-2025</t>
+          <t>A 37145-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8707,10 +8717,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45681</v>
+        <v>45875</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8723,7 +8733,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8766,7 +8776,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22935-2023</t>
+          <t>A 16359-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8780,10 +8790,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45072</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8796,7 +8806,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8839,7 +8849,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53353-2024</t>
+          <t>A 53202-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8849,14 +8859,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45614</v>
+        <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8869,7 +8879,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8912,7 +8922,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26075-2026</t>
+          <t>A 24406-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8922,14 +8932,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46181</v>
+        <v>46169</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8941,8 +8951,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8985,7 +9000,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28148-2026</t>
+          <t>A 24442-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8999,10 +9014,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46195</v>
+        <v>46170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9014,13 +9029,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>23.6</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9063,7 +9073,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47624-2023</t>
+          <t>A 58586-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9077,10 +9087,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45203</v>
+        <v>45635</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9094,11 +9104,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9141,7 +9151,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8269-2025</t>
+          <t>A 3452-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9155,10 +9165,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45708</v>
+        <v>45680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9171,7 +9181,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9214,7 +9224,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41479-2024</t>
+          <t>A 26067-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9228,10 +9238,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45560</v>
+        <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9243,13 +9253,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9292,7 +9297,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28218-2026</t>
+          <t>A 26075-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9306,10 +9311,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46196</v>
+        <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9322,7 +9327,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9365,7 +9370,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4494-2025</t>
+          <t>A 28148-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9379,10 +9384,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45686</v>
+        <v>46195</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9394,8 +9399,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9438,7 +9448,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54738-2023</t>
+          <t>A 28218-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9452,10 +9462,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45236</v>
+        <v>46196</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9467,13 +9477,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9516,7 +9521,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29444-2026</t>
+          <t>A 2342-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9530,10 +9535,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46203</v>
+        <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9545,13 +9550,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9594,7 +9594,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 41325-2023</t>
+          <t>A 487-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45174</v>
+        <v>44930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9623,13 +9623,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9689,7 +9684,7 @@
         <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9750,7 +9745,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30425-2026</t>
+          <t>A 29444-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9760,14 +9755,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46209</v>
+        <v>46203</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9781,11 +9776,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9828,7 +9823,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28979-2026</t>
+          <t>A 30425-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9842,10 +9837,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46199</v>
+        <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9863,7 +9858,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9906,7 +9901,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34627-2026</t>
+          <t>A 28979-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9916,14 +9911,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46255</v>
+        <v>46199</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9937,11 +9932,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>24.1</v>
+        <v>4.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9984,7 +9979,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53202-2023</t>
+          <t>A 35321-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9994,14 +9989,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45229</v>
+        <v>46261</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10013,8 +10008,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10057,7 +10057,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26201-2024</t>
+          <t>A 31441-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10071,10 +10071,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45468</v>
+        <v>46220</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>25.4</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11290-2025</t>
+          <t>A 1840-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45726</v>
+        <v>44938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10164,8 +10164,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10208,7 +10213,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 35321-2026</t>
+          <t>A 29829-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46261</v>
+        <v>46205</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10237,13 +10242,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10286,7 +10286,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29829-2026</t>
+          <t>A 35672-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10300,10 +10300,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46205</v>
+        <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10315,8 +10315,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10359,7 +10364,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31441-2026</t>
+          <t>A 36310-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10373,10 +10378,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46220</v>
+        <v>46268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10390,11 +10395,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10437,7 +10442,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35672-2026</t>
+          <t>A 36417-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10451,10 +10456,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10468,11 +10473,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10515,7 +10520,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11452-2024</t>
+          <t>A 48591-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10529,10 +10534,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45372</v>
+        <v>45593</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10544,13 +10549,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10593,7 +10593,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36310-2026</t>
+          <t>A 31738-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46268</v>
+        <v>46227</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10624,11 +10624,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10671,7 +10671,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31738-2026</t>
+          <t>A 31992-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10700,13 +10700,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10744,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36417-2026</t>
+          <t>A 30587-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10758,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46268</v>
+        <v>45112</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10778,13 +10773,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10827,7 +10817,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17756-2023</t>
+          <t>A 38275-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10841,10 +10831,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45037</v>
+        <v>46281</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10856,8 +10846,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>8.1</v>
+        <v>35.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10900,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28467-2022</t>
+          <t>A 53388-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10914,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44747</v>
+        <v>45614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10930,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10973,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7072-2023</t>
+          <t>A 11452-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10987,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44969</v>
+        <v>45372</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11008,7 +11003,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11051,7 +11046,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 57981-2022</t>
+          <t>A 24846-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11065,10 +11060,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44900</v>
+        <v>44728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11080,13 +11075,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11129,7 +11119,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24846-2022</t>
+          <t>A 8269-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11143,10 +11133,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44728</v>
+        <v>45708</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11159,7 +11149,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11202,7 +11192,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31992-2026</t>
+          <t>A 32964-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11216,10 +11206,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11232,7 +11222,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11275,7 +11265,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2342-2023</t>
+          <t>A 39537-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11289,10 +11279,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44938</v>
+        <v>46289</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11304,8 +11294,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>28.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11348,7 +11343,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38275-2026</t>
+          <t>A 34718-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,10 +11357,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46281</v>
+        <v>46258</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11377,13 +11372,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>35.1</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11426,7 +11416,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13795-2023</t>
+          <t>A 37968-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11440,10 +11430,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45007</v>
+        <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11455,13 +11445,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11504,7 +11489,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32964-2026</t>
+          <t>A 40058-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11518,10 +11503,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46244</v>
+        <v>46293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11533,8 +11518,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>12.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11577,7 +11567,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 19324-2022</t>
+          <t>A 39988-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11591,10 +11581,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44692</v>
+        <v>46293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11606,8 +11596,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11650,7 +11645,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37968-2026</t>
+          <t>A 39804-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11664,10 +11659,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11679,8 +11674,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>19.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11723,7 +11723,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39537-2026</t>
+          <t>A 40009-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11737,10 +11737,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>28.9</v>
+        <v>10.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11801,7 +11801,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39804-2026</t>
+          <t>A 40098-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11879,7 +11879,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34718-2026</t>
+          <t>A 41214-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46258</v>
+        <v>45174</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11908,8 +11908,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>51.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11952,7 +11957,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58125-2022</t>
+          <t>A 26230-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11966,10 +11971,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44900</v>
+        <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11981,8 +11986,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12025,7 +12035,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 40098-2026</t>
+          <t>A 8639-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12039,10 +12049,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46293</v>
+        <v>45711</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12054,13 +12064,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12103,7 +12108,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39988-2026</t>
+          <t>A 34627-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46293</v>
+        <v>46255</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12138,7 +12143,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>24.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12181,7 +12186,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 40009-2026</t>
+          <t>A 41325-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12195,10 +12200,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46293</v>
+        <v>45174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12216,7 +12221,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>10.6</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12259,7 +12264,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 40058-2026</t>
+          <t>A 47894-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12273,10 +12278,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46293</v>
+        <v>45204</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12294,7 +12299,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12337,7 +12342,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59449-2022</t>
+          <t>A 57792-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12351,10 +12356,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44907</v>
+        <v>44897</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12367,7 +12372,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12410,7 +12415,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 13636-2024</t>
+          <t>A 39025-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12424,10 +12429,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45390</v>
+        <v>45163</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12439,8 +12444,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12483,7 +12493,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15152-2022</t>
+          <t>A 28467-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12497,10 +12507,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44658</v>
+        <v>44747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12513,7 +12523,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12556,7 +12566,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 41214-2023</t>
+          <t>A 53353-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12570,10 +12580,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45174</v>
+        <v>45614</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12585,13 +12595,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>51.6</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12634,7 +12639,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39025-2023</t>
+          <t>A 23279-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12648,10 +12653,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45163</v>
+        <v>45453</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12663,13 +12668,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12712,7 +12712,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53912-2024</t>
+          <t>A 35370-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45615</v>
+        <v>45146</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12741,8 +12741,13 @@
           <t>STORFORS</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12785,7 +12790,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35370-2023</t>
+          <t>A 53912-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12799,10 +12804,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45146</v>
+        <v>45615</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12814,13 +12819,8 @@
           <t>STORFORS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>45247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45777</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44834</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44895</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45881</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44536</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45669</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45688</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45988</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45890</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45396</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45660</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45686</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46059</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>44692</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45104</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44658</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45961</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45957</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>46093</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45401</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45975</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45818</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44969</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45726</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45390</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>45168</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44900</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44900</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45681</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45355</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45226</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>45386</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45329</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>46139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>46140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>46140</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>46140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45520</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45588</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45840</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>44939</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44907</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45037</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45875</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>46169</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45635</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>46195</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>46196</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>46203</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>46199</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>46261</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46220</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46205</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>46268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>46268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45593</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>46227</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>46232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45112</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>46281</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45372</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45708</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>46289</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>46258</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>46280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>46293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46290</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>46293</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>46293</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45174</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45711</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>46255</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45204</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44897</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45163</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45614</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45453</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45146</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45615</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45247</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/Översikt STORFORS.xlsx
+++ b/Översikt STORFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45777</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44834</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44895</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45881</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44797</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44490</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44512</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>44788</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44512</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44536</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45669</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45688</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45988</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>45915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45890</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45396</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45660</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45686</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45232</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46057</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46059</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46059</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>46059</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>44692</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45104</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44658</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45588</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45961</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45957</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>46093</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45401</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45975</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45818</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>46111</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44969</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45726</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>46000</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6060,7 +6060,